--- a/METRADO_PLANTILLA_5.xlsx
+++ b/METRADO_PLANTILLA_5.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C5F395B4-3253-40AA-A06E-357A600C8D4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DEDBFF0-72A5-447C-BB69-2EB7CE7B7B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/METRADO_PLANTILLA_5.xlsx
+++ b/METRADO_PLANTILLA_5.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0DEDBFF0-72A5-447C-BB69-2EB7CE7B7B82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB1C214E-7327-4962-A689-3CA59CB7B9E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -735,7 +735,7 @@
     <numFmt numFmtId="169" formatCode="dd/mm/yyyy&quot;  &quot;hh&quot;:&quot;mm&quot;:&quot;ss\ AM/PM"/>
     <numFmt numFmtId="170" formatCode="dd/mm/yy;@"/>
   </numFmts>
-  <fonts count="26" x14ac:knownFonts="1">
+  <fonts count="27" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -903,6 +903,12 @@
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="8"/>
+      <name val="Arial Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1044,7 +1050,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="149">
+  <cellXfs count="150">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1429,6 +1435,9 @@
     </xf>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="26" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -30412,7 +30421,7 @@
     <col min="23" max="23" width="8" style="25" customWidth="1"/>
     <col min="24" max="24" width="5.796875" style="25" customWidth="1"/>
     <col min="25" max="25" width="10.3984375" customWidth="1"/>
-    <col min="26" max="26" width="32.3984375" customWidth="1"/>
+    <col min="26" max="26" width="49.59765625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:26" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -30745,7 +30754,7 @@
       <c r="Q10" s="87"/>
       <c r="R10" s="87"/>
       <c r="S10" s="87"/>
-      <c r="T10" s="87"/>
+      <c r="T10" s="149"/>
       <c r="U10" s="87"/>
       <c r="V10" s="84"/>
       <c r="W10" s="38"/>

--- a/METRADO_PLANTILLA_5.xlsx
+++ b/METRADO_PLANTILLA_5.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{551A8B84-0E1B-464F-8F76-9E5DA84B15DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{285187D0-EFC9-4912-BE97-9980BFBBBC26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1289,6 +1289,22 @@
     <xf numFmtId="2" fontId="22" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1311,22 +1327,6 @@
     </xf>
     <xf numFmtId="2" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1364,54 +1364,6 @@
         <vertical/>
         <horizontal/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <color rgb="FFC00000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <color auto="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <color auto="1"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -1454,6 +1406,27 @@
         <shadow val="0"/>
         <vertAlign val="baseline"/>
         <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color rgb="FFC00000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <color rgb="FFC00000"/>
       </font>
     </dxf>
     <dxf>
@@ -1668,6 +1641,33 @@
       </font>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1770,33 +1770,33 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="B7:AA419" headerRowCount="0" headerRowDxfId="5" dataDxfId="3" totalsRowDxfId="4">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="B7:AA419" headerRowCount="0" headerRowDxfId="28" dataDxfId="27" totalsRowDxfId="26">
   <tableColumns count="26">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="GRADO" dataDxfId="28"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="FECHA" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ESPECIALIDAD" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="FRENTE" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="BLOQUE" dataDxfId="24"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="NIVEL (PISO)" dataDxfId="23"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="CUADRILLA" dataDxfId="22"/>
-    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="GRADO 1" dataDxfId="21"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="GRADO 2" dataDxfId="20"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="GRADO 3" dataDxfId="19"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="GRADO 4" dataDxfId="18"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="PARTIDA" dataDxfId="17"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="DESCRIPCIÓN" dataDxfId="16"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="CANTIDAD" dataDxfId="15"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="LONGITUD/AREA" dataDxfId="14"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="ANCHO / EMPAME" dataDxfId="13"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="ALTURA / L.GANCHO" dataDxfId="12"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="PARCIAL" dataDxfId="11"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="N° VECES" dataDxfId="10"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="ACERO" dataDxfId="9"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="TOTAL" dataDxfId="8"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="TOTAL 2" dataDxfId="2"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="UNIDAD" dataDxfId="1"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="MODIF." dataDxfId="7"/>
-    <tableColumn id="25" xr3:uid="{3865C319-53D6-41C8-9C4C-31FA4F4E0948}" name="Columna1" dataDxfId="6"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="GRADO" dataDxfId="25"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="FECHA" dataDxfId="24"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="ESPECIALIDAD" dataDxfId="23"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="FRENTE" dataDxfId="22"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="BLOQUE" dataDxfId="21"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="NIVEL (PISO)" dataDxfId="20"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="CUADRILLA" dataDxfId="19"/>
+    <tableColumn id="8" xr3:uid="{00000000-0010-0000-0000-000008000000}" name="GRADO 1" dataDxfId="18"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="GRADO 2" dataDxfId="17"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="GRADO 3" dataDxfId="16"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="GRADO 4" dataDxfId="15"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="PARTIDA" dataDxfId="14"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="DESCRIPCIÓN" dataDxfId="13"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="CANTIDAD" dataDxfId="12"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="LONGITUD/AREA" dataDxfId="11"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="ANCHO / EMPAME" dataDxfId="10"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="ALTURA / L.GANCHO" dataDxfId="9"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="PARCIAL" dataDxfId="8"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="N° VECES" dataDxfId="7"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="ACERO" dataDxfId="6"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="TOTAL" dataDxfId="5"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="TOTAL 2" dataDxfId="4"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="UNIDAD" dataDxfId="3"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="MODIF." dataDxfId="2"/>
+    <tableColumn id="25" xr3:uid="{3865C319-53D6-41C8-9C4C-31FA4F4E0948}" name="Columna1" dataDxfId="1"/>
     <tableColumn id="26" xr3:uid="{F0183D40-AE54-4413-976E-0B00C7B637A5}" name="Columna2" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
@@ -2027,19 +2027,19 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="96" t="s">
+      <c r="H1" s="102" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="97"/>
-      <c r="J1" s="97"/>
-      <c r="K1" s="97"/>
-      <c r="L1" s="97"/>
-      <c r="M1" s="97"/>
-      <c r="N1" s="97"/>
-      <c r="O1" s="97"/>
-      <c r="P1" s="97"/>
-      <c r="Q1" s="97"/>
-      <c r="R1" s="97"/>
+      <c r="I1" s="103"/>
+      <c r="J1" s="103"/>
+      <c r="K1" s="103"/>
+      <c r="L1" s="103"/>
+      <c r="M1" s="103"/>
+      <c r="N1" s="103"/>
+      <c r="O1" s="103"/>
+      <c r="P1" s="103"/>
+      <c r="Q1" s="103"/>
+      <c r="R1" s="103"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
@@ -2109,25 +2109,25 @@
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="98">
+      <c r="B4" s="104">
         <v>45809</v>
       </c>
-      <c r="C4" s="99"/>
-      <c r="D4" s="99"/>
-      <c r="E4" s="99"/>
-      <c r="F4" s="99"/>
-      <c r="G4" s="99"/>
-      <c r="H4" s="99"/>
-      <c r="I4" s="99"/>
-      <c r="J4" s="99"/>
-      <c r="K4" s="99"/>
-      <c r="L4" s="99"/>
-      <c r="M4" s="99"/>
-      <c r="N4" s="99"/>
-      <c r="O4" s="99"/>
-      <c r="P4" s="99"/>
-      <c r="Q4" s="99"/>
-      <c r="R4" s="99"/>
+      <c r="C4" s="105"/>
+      <c r="D4" s="105"/>
+      <c r="E4" s="105"/>
+      <c r="F4" s="105"/>
+      <c r="G4" s="105"/>
+      <c r="H4" s="105"/>
+      <c r="I4" s="105"/>
+      <c r="J4" s="105"/>
+      <c r="K4" s="105"/>
+      <c r="L4" s="105"/>
+      <c r="M4" s="105"/>
+      <c r="N4" s="105"/>
+      <c r="O4" s="105"/>
+      <c r="P4" s="105"/>
+      <c r="Q4" s="105"/>
+      <c r="R4" s="105"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
@@ -2139,38 +2139,38 @@
     </row>
     <row r="5" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="103" t="s">
+      <c r="B5" s="109" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="105" t="s">
+      <c r="C5" s="111" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="103" t="s">
+      <c r="D5" s="109" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="106" t="s">
+      <c r="E5" s="112" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="106" t="s">
+      <c r="F5" s="112" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="106" t="s">
+      <c r="G5" s="112" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="106" t="s">
+      <c r="H5" s="112" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="106" t="s">
+      <c r="I5" s="112" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="100" t="s">
+      <c r="J5" s="106" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="101"/>
-      <c r="L5" s="101"/>
-      <c r="M5" s="101"/>
-      <c r="N5" s="101"/>
-      <c r="O5" s="102"/>
+      <c r="K5" s="107"/>
+      <c r="L5" s="107"/>
+      <c r="M5" s="107"/>
+      <c r="N5" s="107"/>
+      <c r="O5" s="108"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="5"/>
       <c r="R5" s="6"/>
@@ -2185,14 +2185,14 @@
     </row>
     <row r="6" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
-      <c r="B6" s="104"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
-      <c r="F6" s="104"/>
-      <c r="G6" s="104"/>
-      <c r="H6" s="104"/>
-      <c r="I6" s="104"/>
+      <c r="B6" s="110"/>
+      <c r="C6" s="110"/>
+      <c r="D6" s="110"/>
+      <c r="E6" s="110"/>
+      <c r="F6" s="110"/>
+      <c r="G6" s="110"/>
+      <c r="H6" s="110"/>
+      <c r="I6" s="110"/>
       <c r="J6" s="7" t="s">
         <v>11</v>
       </c>
@@ -30387,13 +30387,13 @@
     <col min="23" max="23" width="8" style="25" customWidth="1"/>
     <col min="24" max="24" width="5.796875" style="25" customWidth="1"/>
     <col min="25" max="25" width="10.3984375" style="80" customWidth="1"/>
-    <col min="26" max="26" width="49.59765625" style="80" customWidth="1"/>
-    <col min="27" max="27" width="9.59765625" style="80" customWidth="1"/>
+    <col min="26" max="26" width="55.09765625" style="80" customWidth="1"/>
+    <col min="27" max="27" width="19.59765625" style="80" customWidth="1"/>
     <col min="28" max="16384" width="12.69921875" style="80"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="107"/>
+      <c r="A1" s="96"/>
       <c r="B1" s="48"/>
       <c r="C1" s="82"/>
       <c r="D1" s="49"/>
@@ -30415,16 +30415,16 @@
       <c r="T1" s="27"/>
       <c r="U1" s="27"/>
       <c r="V1" s="27"/>
-      <c r="W1" s="112"/>
+      <c r="W1" s="101"/>
       <c r="X1" s="94"/>
-      <c r="Y1" s="108"/>
-      <c r="Z1" s="108" t="s">
+      <c r="Y1" s="97"/>
+      <c r="Z1" s="97" t="s">
         <v>0</v>
       </c>
-      <c r="AA1" s="108"/>
+      <c r="AA1" s="97"/>
     </row>
     <row r="2" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A2" s="107"/>
+      <c r="A2" s="96"/>
       <c r="B2" s="48"/>
       <c r="C2" s="82"/>
       <c r="D2" s="49"/>
@@ -30446,16 +30446,16 @@
       <c r="T2" s="27"/>
       <c r="U2" s="27"/>
       <c r="V2" s="27"/>
-      <c r="W2" s="112"/>
+      <c r="W2" s="101"/>
       <c r="X2" s="92"/>
-      <c r="Y2" s="109"/>
-      <c r="Z2" s="109" t="s">
+      <c r="Y2" s="98"/>
+      <c r="Z2" s="98" t="s">
         <v>28</v>
       </c>
-      <c r="AA2" s="109"/>
+      <c r="AA2" s="98"/>
     </row>
     <row r="3" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="107"/>
+      <c r="A3" s="96"/>
       <c r="B3" s="48"/>
       <c r="C3" s="82"/>
       <c r="D3" s="49"/>
@@ -30484,7 +30484,7 @@
       <c r="AA3" s="28"/>
     </row>
     <row r="4" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="107"/>
+      <c r="A4" s="96"/>
       <c r="B4" s="52" t="s">
         <v>29</v>
       </c>
@@ -30515,7 +30515,7 @@
       <c r="AA4" s="28"/>
     </row>
     <row r="5" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="107"/>
+      <c r="A5" s="96"/>
       <c r="B5" s="48"/>
       <c r="C5" s="82"/>
       <c r="D5" s="49"/>
@@ -30539,14 +30539,14 @@
       <c r="V5" s="28"/>
       <c r="W5" s="93"/>
       <c r="X5" s="94"/>
-      <c r="Y5" s="108"/>
-      <c r="Z5" s="108" t="s">
+      <c r="Y5" s="97"/>
+      <c r="Z5" s="97" t="s">
         <v>30</v>
       </c>
-      <c r="AA5" s="108"/>
+      <c r="AA5" s="97"/>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="107"/>
+      <c r="A6" s="96"/>
       <c r="B6" s="48"/>
       <c r="C6" s="82"/>
       <c r="D6" s="49"/>
@@ -30575,7 +30575,7 @@
       <c r="AA6" s="28"/>
     </row>
     <row r="7" spans="1:27" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="107"/>
+      <c r="A7" s="96"/>
       <c r="B7" s="88" t="s">
         <v>31</v>
       </c>
@@ -30656,7 +30656,7 @@
       </c>
     </row>
     <row r="8" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="107"/>
+      <c r="A8" s="96"/>
       <c r="B8" s="89"/>
       <c r="C8" s="85"/>
       <c r="D8" s="60"/>
@@ -30680,12 +30680,12 @@
       <c r="V8" s="61"/>
       <c r="W8" s="31"/>
       <c r="X8" s="32"/>
-      <c r="Y8" s="110"/>
-      <c r="Z8" s="110"/>
-      <c r="AA8" s="110"/>
+      <c r="Y8" s="99"/>
+      <c r="Z8" s="99"/>
+      <c r="AA8" s="99"/>
     </row>
     <row r="9" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="107"/>
+      <c r="A9" s="96"/>
       <c r="B9" s="89"/>
       <c r="C9" s="85"/>
       <c r="D9" s="60"/>
@@ -30709,12 +30709,12 @@
       <c r="V9" s="61"/>
       <c r="W9" s="31"/>
       <c r="X9" s="32"/>
-      <c r="Y9" s="110"/>
-      <c r="Z9" s="110"/>
-      <c r="AA9" s="110"/>
+      <c r="Y9" s="99"/>
+      <c r="Z9" s="99"/>
+      <c r="AA9" s="99"/>
     </row>
     <row r="10" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="107"/>
+      <c r="A10" s="96"/>
       <c r="B10" s="89"/>
       <c r="C10" s="85"/>
       <c r="D10" s="60"/>
@@ -30738,12 +30738,12 @@
       <c r="V10" s="61"/>
       <c r="W10" s="31"/>
       <c r="X10" s="32"/>
-      <c r="Y10" s="110"/>
-      <c r="Z10" s="110"/>
-      <c r="AA10" s="110"/>
+      <c r="Y10" s="99"/>
+      <c r="Z10" s="99"/>
+      <c r="AA10" s="99"/>
     </row>
     <row r="11" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="107"/>
+      <c r="A11" s="96"/>
       <c r="B11" s="89"/>
       <c r="C11" s="85"/>
       <c r="D11" s="60"/>
@@ -30767,12 +30767,12 @@
       <c r="V11" s="61"/>
       <c r="W11" s="31"/>
       <c r="X11" s="32"/>
-      <c r="Y11" s="110"/>
-      <c r="Z11" s="110"/>
-      <c r="AA11" s="110"/>
+      <c r="Y11" s="99"/>
+      <c r="Z11" s="99"/>
+      <c r="AA11" s="99"/>
     </row>
     <row r="12" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="107"/>
+      <c r="A12" s="96"/>
       <c r="B12" s="89"/>
       <c r="C12" s="85"/>
       <c r="D12" s="60"/>
@@ -30796,12 +30796,12 @@
       <c r="V12" s="61"/>
       <c r="W12" s="31"/>
       <c r="X12" s="32"/>
-      <c r="Y12" s="110"/>
-      <c r="Z12" s="110"/>
-      <c r="AA12" s="110"/>
+      <c r="Y12" s="99"/>
+      <c r="Z12" s="99"/>
+      <c r="AA12" s="99"/>
     </row>
     <row r="13" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="107"/>
+      <c r="A13" s="96"/>
       <c r="B13" s="89"/>
       <c r="C13" s="85"/>
       <c r="D13" s="60"/>
@@ -30825,12 +30825,12 @@
       <c r="V13" s="61"/>
       <c r="W13" s="31"/>
       <c r="X13" s="32"/>
-      <c r="Y13" s="110"/>
-      <c r="Z13" s="110"/>
-      <c r="AA13" s="110"/>
+      <c r="Y13" s="99"/>
+      <c r="Z13" s="99"/>
+      <c r="AA13" s="99"/>
     </row>
     <row r="14" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="107"/>
+      <c r="A14" s="96"/>
       <c r="B14" s="89"/>
       <c r="C14" s="85"/>
       <c r="D14" s="60"/>
@@ -30854,12 +30854,12 @@
       <c r="V14" s="61"/>
       <c r="W14" s="31"/>
       <c r="X14" s="32"/>
-      <c r="Y14" s="110"/>
-      <c r="Z14" s="110"/>
-      <c r="AA14" s="110"/>
+      <c r="Y14" s="99"/>
+      <c r="Z14" s="99"/>
+      <c r="AA14" s="99"/>
     </row>
     <row r="15" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="107"/>
+      <c r="A15" s="96"/>
       <c r="B15" s="89"/>
       <c r="C15" s="85"/>
       <c r="D15" s="60"/>
@@ -30883,12 +30883,12 @@
       <c r="V15" s="61"/>
       <c r="W15" s="31"/>
       <c r="X15" s="32"/>
-      <c r="Y15" s="110"/>
-      <c r="Z15" s="110"/>
-      <c r="AA15" s="110"/>
+      <c r="Y15" s="99"/>
+      <c r="Z15" s="99"/>
+      <c r="AA15" s="99"/>
     </row>
     <row r="16" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="107"/>
+      <c r="A16" s="96"/>
       <c r="B16" s="89"/>
       <c r="C16" s="85"/>
       <c r="D16" s="60"/>
@@ -30912,12 +30912,12 @@
       <c r="V16" s="61"/>
       <c r="W16" s="31"/>
       <c r="X16" s="32"/>
-      <c r="Y16" s="110"/>
-      <c r="Z16" s="110"/>
-      <c r="AA16" s="110"/>
+      <c r="Y16" s="99"/>
+      <c r="Z16" s="99"/>
+      <c r="AA16" s="99"/>
     </row>
     <row r="17" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="107"/>
+      <c r="A17" s="96"/>
       <c r="B17" s="89"/>
       <c r="C17" s="85"/>
       <c r="D17" s="60"/>
@@ -30941,12 +30941,12 @@
       <c r="V17" s="61"/>
       <c r="W17" s="31"/>
       <c r="X17" s="32"/>
-      <c r="Y17" s="110"/>
-      <c r="Z17" s="110"/>
-      <c r="AA17" s="110"/>
+      <c r="Y17" s="99"/>
+      <c r="Z17" s="99"/>
+      <c r="AA17" s="99"/>
     </row>
     <row r="18" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="107"/>
+      <c r="A18" s="96"/>
       <c r="B18" s="89"/>
       <c r="C18" s="85"/>
       <c r="D18" s="60"/>
@@ -30970,12 +30970,12 @@
       <c r="V18" s="61"/>
       <c r="W18" s="31"/>
       <c r="X18" s="32"/>
-      <c r="Y18" s="110"/>
-      <c r="Z18" s="110"/>
-      <c r="AA18" s="110"/>
+      <c r="Y18" s="99"/>
+      <c r="Z18" s="99"/>
+      <c r="AA18" s="99"/>
     </row>
     <row r="19" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="107"/>
+      <c r="A19" s="96"/>
       <c r="B19" s="89"/>
       <c r="C19" s="85"/>
       <c r="D19" s="60"/>
@@ -30999,12 +30999,12 @@
       <c r="V19" s="61"/>
       <c r="W19" s="31"/>
       <c r="X19" s="32"/>
-      <c r="Y19" s="110"/>
-      <c r="Z19" s="110"/>
-      <c r="AA19" s="110"/>
+      <c r="Y19" s="99"/>
+      <c r="Z19" s="99"/>
+      <c r="AA19" s="99"/>
     </row>
     <row r="20" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="107"/>
+      <c r="A20" s="96"/>
       <c r="B20" s="89"/>
       <c r="C20" s="85"/>
       <c r="D20" s="60"/>
@@ -31028,12 +31028,12 @@
       <c r="V20" s="61"/>
       <c r="W20" s="31"/>
       <c r="X20" s="32"/>
-      <c r="Y20" s="110"/>
-      <c r="Z20" s="110"/>
-      <c r="AA20" s="110"/>
+      <c r="Y20" s="99"/>
+      <c r="Z20" s="99"/>
+      <c r="AA20" s="99"/>
     </row>
     <row r="21" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="107"/>
+      <c r="A21" s="96"/>
       <c r="B21" s="89"/>
       <c r="C21" s="85"/>
       <c r="D21" s="60"/>
@@ -31057,12 +31057,12 @@
       <c r="V21" s="61"/>
       <c r="W21" s="31"/>
       <c r="X21" s="32"/>
-      <c r="Y21" s="110"/>
-      <c r="Z21" s="110"/>
-      <c r="AA21" s="110"/>
+      <c r="Y21" s="99"/>
+      <c r="Z21" s="99"/>
+      <c r="AA21" s="99"/>
     </row>
     <row r="22" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="107"/>
+      <c r="A22" s="96"/>
       <c r="B22" s="89"/>
       <c r="C22" s="85"/>
       <c r="D22" s="60"/>
@@ -31086,12 +31086,12 @@
       <c r="V22" s="61"/>
       <c r="W22" s="31"/>
       <c r="X22" s="32"/>
-      <c r="Y22" s="110"/>
-      <c r="Z22" s="110"/>
-      <c r="AA22" s="110"/>
+      <c r="Y22" s="99"/>
+      <c r="Z22" s="99"/>
+      <c r="AA22" s="99"/>
     </row>
     <row r="23" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="107"/>
+      <c r="A23" s="96"/>
       <c r="B23" s="89"/>
       <c r="C23" s="85"/>
       <c r="D23" s="60"/>
@@ -31115,12 +31115,12 @@
       <c r="V23" s="61"/>
       <c r="W23" s="31"/>
       <c r="X23" s="32"/>
-      <c r="Y23" s="110"/>
-      <c r="Z23" s="110"/>
-      <c r="AA23" s="110"/>
+      <c r="Y23" s="99"/>
+      <c r="Z23" s="99"/>
+      <c r="AA23" s="99"/>
     </row>
     <row r="24" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="107"/>
+      <c r="A24" s="96"/>
       <c r="B24" s="89"/>
       <c r="C24" s="85"/>
       <c r="D24" s="60"/>
@@ -31144,12 +31144,12 @@
       <c r="V24" s="61"/>
       <c r="W24" s="31"/>
       <c r="X24" s="32"/>
-      <c r="Y24" s="110"/>
-      <c r="Z24" s="110"/>
-      <c r="AA24" s="110"/>
+      <c r="Y24" s="99"/>
+      <c r="Z24" s="99"/>
+      <c r="AA24" s="99"/>
     </row>
     <row r="25" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="107"/>
+      <c r="A25" s="96"/>
       <c r="B25" s="89"/>
       <c r="C25" s="85"/>
       <c r="D25" s="60"/>
@@ -31173,12 +31173,12 @@
       <c r="V25" s="61"/>
       <c r="W25" s="31"/>
       <c r="X25" s="32"/>
-      <c r="Y25" s="110"/>
-      <c r="Z25" s="110"/>
-      <c r="AA25" s="110"/>
+      <c r="Y25" s="99"/>
+      <c r="Z25" s="99"/>
+      <c r="AA25" s="99"/>
     </row>
     <row r="26" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="107"/>
+      <c r="A26" s="96"/>
       <c r="B26" s="89"/>
       <c r="C26" s="85"/>
       <c r="D26" s="60"/>
@@ -31202,12 +31202,12 @@
       <c r="V26" s="61"/>
       <c r="W26" s="31"/>
       <c r="X26" s="32"/>
-      <c r="Y26" s="110"/>
-      <c r="Z26" s="110"/>
-      <c r="AA26" s="110"/>
+      <c r="Y26" s="99"/>
+      <c r="Z26" s="99"/>
+      <c r="AA26" s="99"/>
     </row>
     <row r="27" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="107"/>
+      <c r="A27" s="96"/>
       <c r="B27" s="89"/>
       <c r="C27" s="85"/>
       <c r="D27" s="60"/>
@@ -31231,12 +31231,12 @@
       <c r="V27" s="61"/>
       <c r="W27" s="31"/>
       <c r="X27" s="32"/>
-      <c r="Y27" s="110"/>
-      <c r="Z27" s="110"/>
-      <c r="AA27" s="110"/>
+      <c r="Y27" s="99"/>
+      <c r="Z27" s="99"/>
+      <c r="AA27" s="99"/>
     </row>
     <row r="28" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="107"/>
+      <c r="A28" s="96"/>
       <c r="B28" s="89"/>
       <c r="C28" s="85"/>
       <c r="D28" s="60"/>
@@ -31260,12 +31260,12 @@
       <c r="V28" s="61"/>
       <c r="W28" s="31"/>
       <c r="X28" s="32"/>
-      <c r="Y28" s="110"/>
-      <c r="Z28" s="110"/>
-      <c r="AA28" s="110"/>
+      <c r="Y28" s="99"/>
+      <c r="Z28" s="99"/>
+      <c r="AA28" s="99"/>
     </row>
     <row r="29" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="107"/>
+      <c r="A29" s="96"/>
       <c r="B29" s="89"/>
       <c r="C29" s="85"/>
       <c r="D29" s="60"/>
@@ -31289,12 +31289,12 @@
       <c r="V29" s="61"/>
       <c r="W29" s="31"/>
       <c r="X29" s="32"/>
-      <c r="Y29" s="110"/>
-      <c r="Z29" s="110"/>
-      <c r="AA29" s="110"/>
+      <c r="Y29" s="99"/>
+      <c r="Z29" s="99"/>
+      <c r="AA29" s="99"/>
     </row>
     <row r="30" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="107"/>
+      <c r="A30" s="96"/>
       <c r="B30" s="89"/>
       <c r="C30" s="85"/>
       <c r="D30" s="60"/>
@@ -31318,12 +31318,12 @@
       <c r="V30" s="61"/>
       <c r="W30" s="31"/>
       <c r="X30" s="32"/>
-      <c r="Y30" s="110"/>
-      <c r="Z30" s="110"/>
-      <c r="AA30" s="110"/>
+      <c r="Y30" s="99"/>
+      <c r="Z30" s="99"/>
+      <c r="AA30" s="99"/>
     </row>
     <row r="31" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="107"/>
+      <c r="A31" s="96"/>
       <c r="B31" s="89"/>
       <c r="C31" s="85"/>
       <c r="D31" s="60"/>
@@ -31347,12 +31347,12 @@
       <c r="V31" s="61"/>
       <c r="W31" s="31"/>
       <c r="X31" s="32"/>
-      <c r="Y31" s="110"/>
-      <c r="Z31" s="110"/>
-      <c r="AA31" s="110"/>
+      <c r="Y31" s="99"/>
+      <c r="Z31" s="99"/>
+      <c r="AA31" s="99"/>
     </row>
     <row r="32" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="107"/>
+      <c r="A32" s="96"/>
       <c r="B32" s="89"/>
       <c r="C32" s="85"/>
       <c r="D32" s="60"/>
@@ -31376,12 +31376,12 @@
       <c r="V32" s="61"/>
       <c r="W32" s="31"/>
       <c r="X32" s="32"/>
-      <c r="Y32" s="110"/>
-      <c r="Z32" s="110"/>
-      <c r="AA32" s="110"/>
+      <c r="Y32" s="99"/>
+      <c r="Z32" s="99"/>
+      <c r="AA32" s="99"/>
     </row>
     <row r="33" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="107"/>
+      <c r="A33" s="96"/>
       <c r="B33" s="89"/>
       <c r="C33" s="85"/>
       <c r="D33" s="60"/>
@@ -31405,12 +31405,12 @@
       <c r="V33" s="61"/>
       <c r="W33" s="31"/>
       <c r="X33" s="32"/>
-      <c r="Y33" s="110"/>
-      <c r="Z33" s="110"/>
-      <c r="AA33" s="110"/>
+      <c r="Y33" s="99"/>
+      <c r="Z33" s="99"/>
+      <c r="AA33" s="99"/>
     </row>
     <row r="34" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="107"/>
+      <c r="A34" s="96"/>
       <c r="B34" s="89"/>
       <c r="C34" s="85"/>
       <c r="D34" s="60"/>
@@ -31434,12 +31434,12 @@
       <c r="V34" s="61"/>
       <c r="W34" s="31"/>
       <c r="X34" s="32"/>
-      <c r="Y34" s="110"/>
-      <c r="Z34" s="110"/>
-      <c r="AA34" s="110"/>
+      <c r="Y34" s="99"/>
+      <c r="Z34" s="99"/>
+      <c r="AA34" s="99"/>
     </row>
     <row r="35" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="107"/>
+      <c r="A35" s="96"/>
       <c r="B35" s="89"/>
       <c r="C35" s="85"/>
       <c r="D35" s="60"/>
@@ -31463,12 +31463,12 @@
       <c r="V35" s="61"/>
       <c r="W35" s="31"/>
       <c r="X35" s="32"/>
-      <c r="Y35" s="110"/>
-      <c r="Z35" s="110"/>
-      <c r="AA35" s="110"/>
+      <c r="Y35" s="99"/>
+      <c r="Z35" s="99"/>
+      <c r="AA35" s="99"/>
     </row>
     <row r="36" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="107"/>
+      <c r="A36" s="96"/>
       <c r="B36" s="89"/>
       <c r="C36" s="85"/>
       <c r="D36" s="60"/>
@@ -31492,12 +31492,12 @@
       <c r="V36" s="61"/>
       <c r="W36" s="31"/>
       <c r="X36" s="32"/>
-      <c r="Y36" s="110"/>
-      <c r="Z36" s="110"/>
-      <c r="AA36" s="110"/>
+      <c r="Y36" s="99"/>
+      <c r="Z36" s="99"/>
+      <c r="AA36" s="99"/>
     </row>
     <row r="37" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="107"/>
+      <c r="A37" s="96"/>
       <c r="B37" s="89"/>
       <c r="C37" s="85"/>
       <c r="D37" s="60"/>
@@ -31521,12 +31521,12 @@
       <c r="V37" s="61"/>
       <c r="W37" s="31"/>
       <c r="X37" s="32"/>
-      <c r="Y37" s="110"/>
-      <c r="Z37" s="110"/>
-      <c r="AA37" s="110"/>
+      <c r="Y37" s="99"/>
+      <c r="Z37" s="99"/>
+      <c r="AA37" s="99"/>
     </row>
     <row r="38" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="107"/>
+      <c r="A38" s="96"/>
       <c r="B38" s="89"/>
       <c r="C38" s="85"/>
       <c r="D38" s="60"/>
@@ -31550,12 +31550,12 @@
       <c r="V38" s="61"/>
       <c r="W38" s="31"/>
       <c r="X38" s="32"/>
-      <c r="Y38" s="110"/>
-      <c r="Z38" s="110"/>
-      <c r="AA38" s="110"/>
+      <c r="Y38" s="99"/>
+      <c r="Z38" s="99"/>
+      <c r="AA38" s="99"/>
     </row>
     <row r="39" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="107"/>
+      <c r="A39" s="96"/>
       <c r="B39" s="89"/>
       <c r="C39" s="85"/>
       <c r="D39" s="60"/>
@@ -31579,12 +31579,12 @@
       <c r="V39" s="61"/>
       <c r="W39" s="31"/>
       <c r="X39" s="32"/>
-      <c r="Y39" s="110"/>
-      <c r="Z39" s="110"/>
-      <c r="AA39" s="110"/>
+      <c r="Y39" s="99"/>
+      <c r="Z39" s="99"/>
+      <c r="AA39" s="99"/>
     </row>
     <row r="40" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="107"/>
+      <c r="A40" s="96"/>
       <c r="B40" s="89"/>
       <c r="C40" s="85"/>
       <c r="D40" s="60"/>
@@ -31608,12 +31608,12 @@
       <c r="V40" s="61"/>
       <c r="W40" s="31"/>
       <c r="X40" s="32"/>
-      <c r="Y40" s="110"/>
-      <c r="Z40" s="110"/>
-      <c r="AA40" s="110"/>
+      <c r="Y40" s="99"/>
+      <c r="Z40" s="99"/>
+      <c r="AA40" s="99"/>
     </row>
     <row r="41" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="107"/>
+      <c r="A41" s="96"/>
       <c r="B41" s="89"/>
       <c r="C41" s="85"/>
       <c r="D41" s="60"/>
@@ -31637,12 +31637,12 @@
       <c r="V41" s="61"/>
       <c r="W41" s="31"/>
       <c r="X41" s="32"/>
-      <c r="Y41" s="110"/>
-      <c r="Z41" s="110"/>
-      <c r="AA41" s="110"/>
+      <c r="Y41" s="99"/>
+      <c r="Z41" s="99"/>
+      <c r="AA41" s="99"/>
     </row>
     <row r="42" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="107"/>
+      <c r="A42" s="96"/>
       <c r="B42" s="89"/>
       <c r="C42" s="85"/>
       <c r="D42" s="60"/>
@@ -31666,12 +31666,12 @@
       <c r="V42" s="61"/>
       <c r="W42" s="31"/>
       <c r="X42" s="32"/>
-      <c r="Y42" s="110"/>
-      <c r="Z42" s="110"/>
-      <c r="AA42" s="110"/>
+      <c r="Y42" s="99"/>
+      <c r="Z42" s="99"/>
+      <c r="AA42" s="99"/>
     </row>
     <row r="43" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="107"/>
+      <c r="A43" s="96"/>
       <c r="B43" s="89"/>
       <c r="C43" s="85"/>
       <c r="D43" s="60"/>
@@ -31695,12 +31695,12 @@
       <c r="V43" s="61"/>
       <c r="W43" s="31"/>
       <c r="X43" s="32"/>
-      <c r="Y43" s="110"/>
-      <c r="Z43" s="110"/>
-      <c r="AA43" s="110"/>
+      <c r="Y43" s="99"/>
+      <c r="Z43" s="99"/>
+      <c r="AA43" s="99"/>
     </row>
     <row r="44" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="107"/>
+      <c r="A44" s="96"/>
       <c r="B44" s="89"/>
       <c r="C44" s="85"/>
       <c r="D44" s="60"/>
@@ -31724,12 +31724,12 @@
       <c r="V44" s="61"/>
       <c r="W44" s="31"/>
       <c r="X44" s="32"/>
-      <c r="Y44" s="110"/>
-      <c r="Z44" s="110"/>
-      <c r="AA44" s="110"/>
+      <c r="Y44" s="99"/>
+      <c r="Z44" s="99"/>
+      <c r="AA44" s="99"/>
     </row>
     <row r="45" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="107"/>
+      <c r="A45" s="96"/>
       <c r="B45" s="89"/>
       <c r="C45" s="85"/>
       <c r="D45" s="60"/>
@@ -31753,12 +31753,12 @@
       <c r="V45" s="61"/>
       <c r="W45" s="31"/>
       <c r="X45" s="32"/>
-      <c r="Y45" s="110"/>
-      <c r="Z45" s="110"/>
-      <c r="AA45" s="110"/>
+      <c r="Y45" s="99"/>
+      <c r="Z45" s="99"/>
+      <c r="AA45" s="99"/>
     </row>
     <row r="46" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="107"/>
+      <c r="A46" s="96"/>
       <c r="B46" s="89"/>
       <c r="C46" s="85"/>
       <c r="D46" s="60"/>
@@ -31782,12 +31782,12 @@
       <c r="V46" s="61"/>
       <c r="W46" s="31"/>
       <c r="X46" s="32"/>
-      <c r="Y46" s="110"/>
-      <c r="Z46" s="110"/>
-      <c r="AA46" s="110"/>
+      <c r="Y46" s="99"/>
+      <c r="Z46" s="99"/>
+      <c r="AA46" s="99"/>
     </row>
     <row r="47" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="107"/>
+      <c r="A47" s="96"/>
       <c r="B47" s="89"/>
       <c r="C47" s="85"/>
       <c r="D47" s="60"/>
@@ -31811,12 +31811,12 @@
       <c r="V47" s="61"/>
       <c r="W47" s="31"/>
       <c r="X47" s="32"/>
-      <c r="Y47" s="110"/>
-      <c r="Z47" s="110"/>
-      <c r="AA47" s="110"/>
+      <c r="Y47" s="99"/>
+      <c r="Z47" s="99"/>
+      <c r="AA47" s="99"/>
     </row>
     <row r="48" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="107"/>
+      <c r="A48" s="96"/>
       <c r="B48" s="89"/>
       <c r="C48" s="85"/>
       <c r="D48" s="60"/>
@@ -31840,12 +31840,12 @@
       <c r="V48" s="61"/>
       <c r="W48" s="31"/>
       <c r="X48" s="32"/>
-      <c r="Y48" s="110"/>
-      <c r="Z48" s="110"/>
-      <c r="AA48" s="110"/>
+      <c r="Y48" s="99"/>
+      <c r="Z48" s="99"/>
+      <c r="AA48" s="99"/>
     </row>
     <row r="49" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="107"/>
+      <c r="A49" s="96"/>
       <c r="B49" s="89"/>
       <c r="C49" s="85"/>
       <c r="D49" s="60"/>
@@ -31869,12 +31869,12 @@
       <c r="V49" s="61"/>
       <c r="W49" s="31"/>
       <c r="X49" s="32"/>
-      <c r="Y49" s="110"/>
-      <c r="Z49" s="110"/>
-      <c r="AA49" s="110"/>
+      <c r="Y49" s="99"/>
+      <c r="Z49" s="99"/>
+      <c r="AA49" s="99"/>
     </row>
     <row r="50" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="107"/>
+      <c r="A50" s="96"/>
       <c r="B50" s="89"/>
       <c r="C50" s="85"/>
       <c r="D50" s="60"/>
@@ -31898,12 +31898,12 @@
       <c r="V50" s="61"/>
       <c r="W50" s="31"/>
       <c r="X50" s="32"/>
-      <c r="Y50" s="110"/>
-      <c r="Z50" s="110"/>
-      <c r="AA50" s="110"/>
+      <c r="Y50" s="99"/>
+      <c r="Z50" s="99"/>
+      <c r="AA50" s="99"/>
     </row>
     <row r="51" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="107"/>
+      <c r="A51" s="96"/>
       <c r="B51" s="89"/>
       <c r="C51" s="85"/>
       <c r="D51" s="60"/>
@@ -31927,12 +31927,12 @@
       <c r="V51" s="61"/>
       <c r="W51" s="31"/>
       <c r="X51" s="32"/>
-      <c r="Y51" s="110"/>
-      <c r="Z51" s="110"/>
-      <c r="AA51" s="110"/>
+      <c r="Y51" s="99"/>
+      <c r="Z51" s="99"/>
+      <c r="AA51" s="99"/>
     </row>
     <row r="52" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="107"/>
+      <c r="A52" s="96"/>
       <c r="B52" s="89"/>
       <c r="C52" s="85"/>
       <c r="D52" s="60"/>
@@ -31956,12 +31956,12 @@
       <c r="V52" s="61"/>
       <c r="W52" s="31"/>
       <c r="X52" s="32"/>
-      <c r="Y52" s="110"/>
-      <c r="Z52" s="110"/>
-      <c r="AA52" s="110"/>
+      <c r="Y52" s="99"/>
+      <c r="Z52" s="99"/>
+      <c r="AA52" s="99"/>
     </row>
     <row r="53" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="107"/>
+      <c r="A53" s="96"/>
       <c r="B53" s="89"/>
       <c r="C53" s="85"/>
       <c r="D53" s="60"/>
@@ -31985,12 +31985,12 @@
       <c r="V53" s="61"/>
       <c r="W53" s="31"/>
       <c r="X53" s="32"/>
-      <c r="Y53" s="110"/>
-      <c r="Z53" s="110"/>
-      <c r="AA53" s="110"/>
+      <c r="Y53" s="99"/>
+      <c r="Z53" s="99"/>
+      <c r="AA53" s="99"/>
     </row>
     <row r="54" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="107"/>
+      <c r="A54" s="96"/>
       <c r="B54" s="89"/>
       <c r="C54" s="85"/>
       <c r="D54" s="60"/>
@@ -32014,12 +32014,12 @@
       <c r="V54" s="61"/>
       <c r="W54" s="31"/>
       <c r="X54" s="32"/>
-      <c r="Y54" s="110"/>
-      <c r="Z54" s="110"/>
-      <c r="AA54" s="110"/>
+      <c r="Y54" s="99"/>
+      <c r="Z54" s="99"/>
+      <c r="AA54" s="99"/>
     </row>
     <row r="55" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="107"/>
+      <c r="A55" s="96"/>
       <c r="B55" s="89"/>
       <c r="C55" s="85"/>
       <c r="D55" s="60"/>
@@ -32043,12 +32043,12 @@
       <c r="V55" s="61"/>
       <c r="W55" s="31"/>
       <c r="X55" s="32"/>
-      <c r="Y55" s="110"/>
-      <c r="Z55" s="110"/>
-      <c r="AA55" s="110"/>
+      <c r="Y55" s="99"/>
+      <c r="Z55" s="99"/>
+      <c r="AA55" s="99"/>
     </row>
     <row r="56" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="107"/>
+      <c r="A56" s="96"/>
       <c r="B56" s="89"/>
       <c r="C56" s="85"/>
       <c r="D56" s="60"/>
@@ -32072,12 +32072,12 @@
       <c r="V56" s="61"/>
       <c r="W56" s="31"/>
       <c r="X56" s="32"/>
-      <c r="Y56" s="110"/>
-      <c r="Z56" s="110"/>
-      <c r="AA56" s="110"/>
+      <c r="Y56" s="99"/>
+      <c r="Z56" s="99"/>
+      <c r="AA56" s="99"/>
     </row>
     <row r="57" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="107"/>
+      <c r="A57" s="96"/>
       <c r="B57" s="89"/>
       <c r="C57" s="85"/>
       <c r="D57" s="60"/>
@@ -32101,12 +32101,12 @@
       <c r="V57" s="61"/>
       <c r="W57" s="31"/>
       <c r="X57" s="32"/>
-      <c r="Y57" s="110"/>
-      <c r="Z57" s="110"/>
-      <c r="AA57" s="110"/>
+      <c r="Y57" s="99"/>
+      <c r="Z57" s="99"/>
+      <c r="AA57" s="99"/>
     </row>
     <row r="58" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="107"/>
+      <c r="A58" s="96"/>
       <c r="B58" s="89"/>
       <c r="C58" s="85"/>
       <c r="D58" s="60"/>
@@ -32130,12 +32130,12 @@
       <c r="V58" s="61"/>
       <c r="W58" s="31"/>
       <c r="X58" s="32"/>
-      <c r="Y58" s="110"/>
-      <c r="Z58" s="110"/>
-      <c r="AA58" s="110"/>
+      <c r="Y58" s="99"/>
+      <c r="Z58" s="99"/>
+      <c r="AA58" s="99"/>
     </row>
     <row r="59" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="107"/>
+      <c r="A59" s="96"/>
       <c r="B59" s="89"/>
       <c r="C59" s="85"/>
       <c r="D59" s="60"/>
@@ -32159,12 +32159,12 @@
       <c r="V59" s="61"/>
       <c r="W59" s="31"/>
       <c r="X59" s="32"/>
-      <c r="Y59" s="110"/>
-      <c r="Z59" s="110"/>
-      <c r="AA59" s="110"/>
+      <c r="Y59" s="99"/>
+      <c r="Z59" s="99"/>
+      <c r="AA59" s="99"/>
     </row>
     <row r="60" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="107"/>
+      <c r="A60" s="96"/>
       <c r="B60" s="89"/>
       <c r="C60" s="85"/>
       <c r="D60" s="60"/>
@@ -32188,12 +32188,12 @@
       <c r="V60" s="61"/>
       <c r="W60" s="31"/>
       <c r="X60" s="32"/>
-      <c r="Y60" s="110"/>
-      <c r="Z60" s="110"/>
-      <c r="AA60" s="110"/>
+      <c r="Y60" s="99"/>
+      <c r="Z60" s="99"/>
+      <c r="AA60" s="99"/>
     </row>
     <row r="61" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="107"/>
+      <c r="A61" s="96"/>
       <c r="B61" s="89"/>
       <c r="C61" s="85"/>
       <c r="D61" s="60"/>
@@ -32217,12 +32217,12 @@
       <c r="V61" s="61"/>
       <c r="W61" s="31"/>
       <c r="X61" s="32"/>
-      <c r="Y61" s="110"/>
-      <c r="Z61" s="110"/>
-      <c r="AA61" s="110"/>
+      <c r="Y61" s="99"/>
+      <c r="Z61" s="99"/>
+      <c r="AA61" s="99"/>
     </row>
     <row r="62" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="107"/>
+      <c r="A62" s="96"/>
       <c r="B62" s="89"/>
       <c r="C62" s="85"/>
       <c r="D62" s="60"/>
@@ -32246,12 +32246,12 @@
       <c r="V62" s="61"/>
       <c r="W62" s="31"/>
       <c r="X62" s="32"/>
-      <c r="Y62" s="110"/>
-      <c r="Z62" s="110"/>
-      <c r="AA62" s="110"/>
+      <c r="Y62" s="99"/>
+      <c r="Z62" s="99"/>
+      <c r="AA62" s="99"/>
     </row>
     <row r="63" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="107"/>
+      <c r="A63" s="96"/>
       <c r="B63" s="89"/>
       <c r="C63" s="85"/>
       <c r="D63" s="60"/>
@@ -32275,12 +32275,12 @@
       <c r="V63" s="61"/>
       <c r="W63" s="31"/>
       <c r="X63" s="32"/>
-      <c r="Y63" s="110"/>
-      <c r="Z63" s="110"/>
-      <c r="AA63" s="110"/>
+      <c r="Y63" s="99"/>
+      <c r="Z63" s="99"/>
+      <c r="AA63" s="99"/>
     </row>
     <row r="64" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="107"/>
+      <c r="A64" s="96"/>
       <c r="B64" s="89"/>
       <c r="C64" s="85"/>
       <c r="D64" s="60"/>
@@ -32304,12 +32304,12 @@
       <c r="V64" s="61"/>
       <c r="W64" s="31"/>
       <c r="X64" s="32"/>
-      <c r="Y64" s="110"/>
-      <c r="Z64" s="110"/>
-      <c r="AA64" s="110"/>
+      <c r="Y64" s="99"/>
+      <c r="Z64" s="99"/>
+      <c r="AA64" s="99"/>
     </row>
     <row r="65" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="107"/>
+      <c r="A65" s="96"/>
       <c r="B65" s="89"/>
       <c r="C65" s="85"/>
       <c r="D65" s="60"/>
@@ -32333,12 +32333,12 @@
       <c r="V65" s="61"/>
       <c r="W65" s="31"/>
       <c r="X65" s="32"/>
-      <c r="Y65" s="110"/>
-      <c r="Z65" s="110"/>
-      <c r="AA65" s="110"/>
+      <c r="Y65" s="99"/>
+      <c r="Z65" s="99"/>
+      <c r="AA65" s="99"/>
     </row>
     <row r="66" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="107"/>
+      <c r="A66" s="96"/>
       <c r="B66" s="89"/>
       <c r="C66" s="85"/>
       <c r="D66" s="60"/>
@@ -32362,12 +32362,12 @@
       <c r="V66" s="61"/>
       <c r="W66" s="31"/>
       <c r="X66" s="32"/>
-      <c r="Y66" s="110"/>
-      <c r="Z66" s="110"/>
-      <c r="AA66" s="110"/>
+      <c r="Y66" s="99"/>
+      <c r="Z66" s="99"/>
+      <c r="AA66" s="99"/>
     </row>
     <row r="67" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="107"/>
+      <c r="A67" s="96"/>
       <c r="B67" s="89"/>
       <c r="C67" s="85"/>
       <c r="D67" s="60"/>
@@ -32391,12 +32391,12 @@
       <c r="V67" s="61"/>
       <c r="W67" s="31"/>
       <c r="X67" s="32"/>
-      <c r="Y67" s="110"/>
-      <c r="Z67" s="110"/>
-      <c r="AA67" s="110"/>
+      <c r="Y67" s="99"/>
+      <c r="Z67" s="99"/>
+      <c r="AA67" s="99"/>
     </row>
     <row r="68" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="107"/>
+      <c r="A68" s="96"/>
       <c r="B68" s="89"/>
       <c r="C68" s="85"/>
       <c r="D68" s="60"/>
@@ -32420,12 +32420,12 @@
       <c r="V68" s="61"/>
       <c r="W68" s="31"/>
       <c r="X68" s="32"/>
-      <c r="Y68" s="110"/>
-      <c r="Z68" s="110"/>
-      <c r="AA68" s="110"/>
+      <c r="Y68" s="99"/>
+      <c r="Z68" s="99"/>
+      <c r="AA68" s="99"/>
     </row>
     <row r="69" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="107"/>
+      <c r="A69" s="96"/>
       <c r="B69" s="89"/>
       <c r="C69" s="85"/>
       <c r="D69" s="60"/>
@@ -32449,12 +32449,12 @@
       <c r="V69" s="61"/>
       <c r="W69" s="31"/>
       <c r="X69" s="32"/>
-      <c r="Y69" s="110"/>
-      <c r="Z69" s="110"/>
-      <c r="AA69" s="110"/>
+      <c r="Y69" s="99"/>
+      <c r="Z69" s="99"/>
+      <c r="AA69" s="99"/>
     </row>
     <row r="70" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="107"/>
+      <c r="A70" s="96"/>
       <c r="B70" s="89"/>
       <c r="C70" s="85"/>
       <c r="D70" s="60"/>
@@ -32478,12 +32478,12 @@
       <c r="V70" s="61"/>
       <c r="W70" s="31"/>
       <c r="X70" s="32"/>
-      <c r="Y70" s="110"/>
-      <c r="Z70" s="110"/>
-      <c r="AA70" s="110"/>
+      <c r="Y70" s="99"/>
+      <c r="Z70" s="99"/>
+      <c r="AA70" s="99"/>
     </row>
     <row r="71" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="107"/>
+      <c r="A71" s="96"/>
       <c r="B71" s="89"/>
       <c r="C71" s="85"/>
       <c r="D71" s="60"/>
@@ -32507,12 +32507,12 @@
       <c r="V71" s="61"/>
       <c r="W71" s="31"/>
       <c r="X71" s="32"/>
-      <c r="Y71" s="110"/>
-      <c r="Z71" s="110"/>
-      <c r="AA71" s="110"/>
+      <c r="Y71" s="99"/>
+      <c r="Z71" s="99"/>
+      <c r="AA71" s="99"/>
     </row>
     <row r="72" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="107"/>
+      <c r="A72" s="96"/>
       <c r="B72" s="89"/>
       <c r="C72" s="85"/>
       <c r="D72" s="60"/>
@@ -32536,12 +32536,12 @@
       <c r="V72" s="61"/>
       <c r="W72" s="31"/>
       <c r="X72" s="32"/>
-      <c r="Y72" s="110"/>
-      <c r="Z72" s="110"/>
-      <c r="AA72" s="110"/>
+      <c r="Y72" s="99"/>
+      <c r="Z72" s="99"/>
+      <c r="AA72" s="99"/>
     </row>
     <row r="73" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="107"/>
+      <c r="A73" s="96"/>
       <c r="B73" s="89"/>
       <c r="C73" s="85"/>
       <c r="D73" s="60"/>
@@ -32565,12 +32565,12 @@
       <c r="V73" s="61"/>
       <c r="W73" s="31"/>
       <c r="X73" s="32"/>
-      <c r="Y73" s="110"/>
-      <c r="Z73" s="110"/>
-      <c r="AA73" s="110"/>
+      <c r="Y73" s="99"/>
+      <c r="Z73" s="99"/>
+      <c r="AA73" s="99"/>
     </row>
     <row r="74" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="107"/>
+      <c r="A74" s="96"/>
       <c r="B74" s="89"/>
       <c r="C74" s="85"/>
       <c r="D74" s="60"/>
@@ -32594,12 +32594,12 @@
       <c r="V74" s="61"/>
       <c r="W74" s="31"/>
       <c r="X74" s="32"/>
-      <c r="Y74" s="110"/>
-      <c r="Z74" s="110"/>
-      <c r="AA74" s="110"/>
+      <c r="Y74" s="99"/>
+      <c r="Z74" s="99"/>
+      <c r="AA74" s="99"/>
     </row>
     <row r="75" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="107"/>
+      <c r="A75" s="96"/>
       <c r="B75" s="89"/>
       <c r="C75" s="85"/>
       <c r="D75" s="60"/>
@@ -32623,12 +32623,12 @@
       <c r="V75" s="61"/>
       <c r="W75" s="31"/>
       <c r="X75" s="32"/>
-      <c r="Y75" s="110"/>
-      <c r="Z75" s="110"/>
-      <c r="AA75" s="110"/>
+      <c r="Y75" s="99"/>
+      <c r="Z75" s="99"/>
+      <c r="AA75" s="99"/>
     </row>
     <row r="76" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="107"/>
+      <c r="A76" s="96"/>
       <c r="B76" s="89"/>
       <c r="C76" s="85"/>
       <c r="D76" s="60"/>
@@ -32652,12 +32652,12 @@
       <c r="V76" s="61"/>
       <c r="W76" s="31"/>
       <c r="X76" s="32"/>
-      <c r="Y76" s="110"/>
-      <c r="Z76" s="110"/>
-      <c r="AA76" s="110"/>
+      <c r="Y76" s="99"/>
+      <c r="Z76" s="99"/>
+      <c r="AA76" s="99"/>
     </row>
     <row r="77" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="107"/>
+      <c r="A77" s="96"/>
       <c r="B77" s="89"/>
       <c r="C77" s="85"/>
       <c r="D77" s="60"/>
@@ -32681,12 +32681,12 @@
       <c r="V77" s="61"/>
       <c r="W77" s="31"/>
       <c r="X77" s="32"/>
-      <c r="Y77" s="110"/>
-      <c r="Z77" s="110"/>
-      <c r="AA77" s="110"/>
+      <c r="Y77" s="99"/>
+      <c r="Z77" s="99"/>
+      <c r="AA77" s="99"/>
     </row>
     <row r="78" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="107"/>
+      <c r="A78" s="96"/>
       <c r="B78" s="89"/>
       <c r="C78" s="85"/>
       <c r="D78" s="60"/>
@@ -32710,12 +32710,12 @@
       <c r="V78" s="61"/>
       <c r="W78" s="31"/>
       <c r="X78" s="32"/>
-      <c r="Y78" s="110"/>
-      <c r="Z78" s="110"/>
-      <c r="AA78" s="110"/>
+      <c r="Y78" s="99"/>
+      <c r="Z78" s="99"/>
+      <c r="AA78" s="99"/>
     </row>
     <row r="79" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="107"/>
+      <c r="A79" s="96"/>
       <c r="B79" s="89"/>
       <c r="C79" s="85"/>
       <c r="D79" s="60"/>
@@ -32739,12 +32739,12 @@
       <c r="V79" s="61"/>
       <c r="W79" s="31"/>
       <c r="X79" s="32"/>
-      <c r="Y79" s="110"/>
-      <c r="Z79" s="110"/>
-      <c r="AA79" s="110"/>
+      <c r="Y79" s="99"/>
+      <c r="Z79" s="99"/>
+      <c r="AA79" s="99"/>
     </row>
     <row r="80" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="107"/>
+      <c r="A80" s="96"/>
       <c r="B80" s="89"/>
       <c r="C80" s="85"/>
       <c r="D80" s="60"/>
@@ -32768,12 +32768,12 @@
       <c r="V80" s="61"/>
       <c r="W80" s="31"/>
       <c r="X80" s="32"/>
-      <c r="Y80" s="110"/>
-      <c r="Z80" s="110"/>
-      <c r="AA80" s="110"/>
+      <c r="Y80" s="99"/>
+      <c r="Z80" s="99"/>
+      <c r="AA80" s="99"/>
     </row>
     <row r="81" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="107"/>
+      <c r="A81" s="96"/>
       <c r="B81" s="89"/>
       <c r="C81" s="85"/>
       <c r="D81" s="60"/>
@@ -32797,12 +32797,12 @@
       <c r="V81" s="61"/>
       <c r="W81" s="31"/>
       <c r="X81" s="32"/>
-      <c r="Y81" s="110"/>
-      <c r="Z81" s="110"/>
-      <c r="AA81" s="110"/>
+      <c r="Y81" s="99"/>
+      <c r="Z81" s="99"/>
+      <c r="AA81" s="99"/>
     </row>
     <row r="82" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="107"/>
+      <c r="A82" s="96"/>
       <c r="B82" s="89"/>
       <c r="C82" s="85"/>
       <c r="D82" s="60"/>
@@ -32826,12 +32826,12 @@
       <c r="V82" s="61"/>
       <c r="W82" s="31"/>
       <c r="X82" s="32"/>
-      <c r="Y82" s="110"/>
-      <c r="Z82" s="110"/>
-      <c r="AA82" s="110"/>
+      <c r="Y82" s="99"/>
+      <c r="Z82" s="99"/>
+      <c r="AA82" s="99"/>
     </row>
     <row r="83" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="107"/>
+      <c r="A83" s="96"/>
       <c r="B83" s="89"/>
       <c r="C83" s="85"/>
       <c r="D83" s="60"/>
@@ -32855,12 +32855,12 @@
       <c r="V83" s="61"/>
       <c r="W83" s="31"/>
       <c r="X83" s="32"/>
-      <c r="Y83" s="110"/>
-      <c r="Z83" s="110"/>
-      <c r="AA83" s="110"/>
+      <c r="Y83" s="99"/>
+      <c r="Z83" s="99"/>
+      <c r="AA83" s="99"/>
     </row>
     <row r="84" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="107"/>
+      <c r="A84" s="96"/>
       <c r="B84" s="89"/>
       <c r="C84" s="85"/>
       <c r="D84" s="60"/>
@@ -32884,12 +32884,12 @@
       <c r="V84" s="61"/>
       <c r="W84" s="31"/>
       <c r="X84" s="32"/>
-      <c r="Y84" s="110"/>
-      <c r="Z84" s="110"/>
-      <c r="AA84" s="110"/>
+      <c r="Y84" s="99"/>
+      <c r="Z84" s="99"/>
+      <c r="AA84" s="99"/>
     </row>
     <row r="85" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="107"/>
+      <c r="A85" s="96"/>
       <c r="B85" s="89"/>
       <c r="C85" s="85"/>
       <c r="D85" s="60"/>
@@ -32913,12 +32913,12 @@
       <c r="V85" s="61"/>
       <c r="W85" s="31"/>
       <c r="X85" s="32"/>
-      <c r="Y85" s="110"/>
-      <c r="Z85" s="110"/>
-      <c r="AA85" s="110"/>
+      <c r="Y85" s="99"/>
+      <c r="Z85" s="99"/>
+      <c r="AA85" s="99"/>
     </row>
     <row r="86" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="107"/>
+      <c r="A86" s="96"/>
       <c r="B86" s="89"/>
       <c r="C86" s="85"/>
       <c r="D86" s="60"/>
@@ -32942,12 +32942,12 @@
       <c r="V86" s="61"/>
       <c r="W86" s="31"/>
       <c r="X86" s="32"/>
-      <c r="Y86" s="110"/>
-      <c r="Z86" s="110"/>
-      <c r="AA86" s="110"/>
+      <c r="Y86" s="99"/>
+      <c r="Z86" s="99"/>
+      <c r="AA86" s="99"/>
     </row>
     <row r="87" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="107"/>
+      <c r="A87" s="96"/>
       <c r="B87" s="89"/>
       <c r="C87" s="85"/>
       <c r="D87" s="60"/>
@@ -32971,12 +32971,12 @@
       <c r="V87" s="61"/>
       <c r="W87" s="31"/>
       <c r="X87" s="32"/>
-      <c r="Y87" s="110"/>
-      <c r="Z87" s="110"/>
-      <c r="AA87" s="110"/>
+      <c r="Y87" s="99"/>
+      <c r="Z87" s="99"/>
+      <c r="AA87" s="99"/>
     </row>
     <row r="88" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="107"/>
+      <c r="A88" s="96"/>
       <c r="B88" s="89"/>
       <c r="C88" s="85"/>
       <c r="D88" s="60"/>
@@ -33000,12 +33000,12 @@
       <c r="V88" s="61"/>
       <c r="W88" s="31"/>
       <c r="X88" s="32"/>
-      <c r="Y88" s="110"/>
-      <c r="Z88" s="110"/>
-      <c r="AA88" s="110"/>
+      <c r="Y88" s="99"/>
+      <c r="Z88" s="99"/>
+      <c r="AA88" s="99"/>
     </row>
     <row r="89" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="107"/>
+      <c r="A89" s="96"/>
       <c r="B89" s="89"/>
       <c r="C89" s="85"/>
       <c r="D89" s="60"/>
@@ -33029,12 +33029,12 @@
       <c r="V89" s="61"/>
       <c r="W89" s="31"/>
       <c r="X89" s="32"/>
-      <c r="Y89" s="110"/>
-      <c r="Z89" s="110"/>
-      <c r="AA89" s="110"/>
+      <c r="Y89" s="99"/>
+      <c r="Z89" s="99"/>
+      <c r="AA89" s="99"/>
     </row>
     <row r="90" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="107"/>
+      <c r="A90" s="96"/>
       <c r="B90" s="89"/>
       <c r="C90" s="85"/>
       <c r="D90" s="60"/>
@@ -33058,12 +33058,12 @@
       <c r="V90" s="61"/>
       <c r="W90" s="31"/>
       <c r="X90" s="32"/>
-      <c r="Y90" s="110"/>
-      <c r="Z90" s="110"/>
-      <c r="AA90" s="110"/>
+      <c r="Y90" s="99"/>
+      <c r="Z90" s="99"/>
+      <c r="AA90" s="99"/>
     </row>
     <row r="91" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="107"/>
+      <c r="A91" s="96"/>
       <c r="B91" s="89"/>
       <c r="C91" s="85"/>
       <c r="D91" s="60"/>
@@ -33087,12 +33087,12 @@
       <c r="V91" s="61"/>
       <c r="W91" s="31"/>
       <c r="X91" s="32"/>
-      <c r="Y91" s="110"/>
-      <c r="Z91" s="110"/>
-      <c r="AA91" s="110"/>
+      <c r="Y91" s="99"/>
+      <c r="Z91" s="99"/>
+      <c r="AA91" s="99"/>
     </row>
     <row r="92" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="107"/>
+      <c r="A92" s="96"/>
       <c r="B92" s="89"/>
       <c r="C92" s="85"/>
       <c r="D92" s="60"/>
@@ -33116,12 +33116,12 @@
       <c r="V92" s="61"/>
       <c r="W92" s="31"/>
       <c r="X92" s="32"/>
-      <c r="Y92" s="110"/>
-      <c r="Z92" s="110"/>
-      <c r="AA92" s="110"/>
+      <c r="Y92" s="99"/>
+      <c r="Z92" s="99"/>
+      <c r="AA92" s="99"/>
     </row>
     <row r="93" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="107"/>
+      <c r="A93" s="96"/>
       <c r="B93" s="89"/>
       <c r="C93" s="85"/>
       <c r="D93" s="60"/>
@@ -33145,12 +33145,12 @@
       <c r="V93" s="61"/>
       <c r="W93" s="31"/>
       <c r="X93" s="32"/>
-      <c r="Y93" s="110"/>
-      <c r="Z93" s="110"/>
-      <c r="AA93" s="110"/>
+      <c r="Y93" s="99"/>
+      <c r="Z93" s="99"/>
+      <c r="AA93" s="99"/>
     </row>
     <row r="94" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="107"/>
+      <c r="A94" s="96"/>
       <c r="B94" s="89"/>
       <c r="C94" s="85"/>
       <c r="D94" s="60"/>
@@ -33174,12 +33174,12 @@
       <c r="V94" s="61"/>
       <c r="W94" s="31"/>
       <c r="X94" s="32"/>
-      <c r="Y94" s="110"/>
-      <c r="Z94" s="110"/>
-      <c r="AA94" s="110"/>
+      <c r="Y94" s="99"/>
+      <c r="Z94" s="99"/>
+      <c r="AA94" s="99"/>
     </row>
     <row r="95" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="107"/>
+      <c r="A95" s="96"/>
       <c r="B95" s="89"/>
       <c r="C95" s="85"/>
       <c r="D95" s="60"/>
@@ -33203,12 +33203,12 @@
       <c r="V95" s="61"/>
       <c r="W95" s="31"/>
       <c r="X95" s="32"/>
-      <c r="Y95" s="110"/>
-      <c r="Z95" s="110"/>
-      <c r="AA95" s="110"/>
+      <c r="Y95" s="99"/>
+      <c r="Z95" s="99"/>
+      <c r="AA95" s="99"/>
     </row>
     <row r="96" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="107"/>
+      <c r="A96" s="96"/>
       <c r="B96" s="89"/>
       <c r="C96" s="85"/>
       <c r="D96" s="60"/>
@@ -33232,12 +33232,12 @@
       <c r="V96" s="61"/>
       <c r="W96" s="31"/>
       <c r="X96" s="32"/>
-      <c r="Y96" s="110"/>
-      <c r="Z96" s="110"/>
-      <c r="AA96" s="110"/>
+      <c r="Y96" s="99"/>
+      <c r="Z96" s="99"/>
+      <c r="AA96" s="99"/>
     </row>
     <row r="97" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="107"/>
+      <c r="A97" s="96"/>
       <c r="B97" s="89"/>
       <c r="C97" s="85"/>
       <c r="D97" s="60"/>
@@ -33261,12 +33261,12 @@
       <c r="V97" s="61"/>
       <c r="W97" s="31"/>
       <c r="X97" s="32"/>
-      <c r="Y97" s="110"/>
-      <c r="Z97" s="110"/>
-      <c r="AA97" s="110"/>
+      <c r="Y97" s="99"/>
+      <c r="Z97" s="99"/>
+      <c r="AA97" s="99"/>
     </row>
     <row r="98" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="107"/>
+      <c r="A98" s="96"/>
       <c r="B98" s="89"/>
       <c r="C98" s="85"/>
       <c r="D98" s="60"/>
@@ -33290,12 +33290,12 @@
       <c r="V98" s="61"/>
       <c r="W98" s="31"/>
       <c r="X98" s="32"/>
-      <c r="Y98" s="110"/>
-      <c r="Z98" s="110"/>
-      <c r="AA98" s="110"/>
+      <c r="Y98" s="99"/>
+      <c r="Z98" s="99"/>
+      <c r="AA98" s="99"/>
     </row>
     <row r="99" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="107"/>
+      <c r="A99" s="96"/>
       <c r="B99" s="89"/>
       <c r="C99" s="85"/>
       <c r="D99" s="60"/>
@@ -33319,12 +33319,12 @@
       <c r="V99" s="61"/>
       <c r="W99" s="31"/>
       <c r="X99" s="32"/>
-      <c r="Y99" s="110"/>
-      <c r="Z99" s="110"/>
-      <c r="AA99" s="110"/>
+      <c r="Y99" s="99"/>
+      <c r="Z99" s="99"/>
+      <c r="AA99" s="99"/>
     </row>
     <row r="100" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="107"/>
+      <c r="A100" s="96"/>
       <c r="B100" s="89"/>
       <c r="C100" s="85"/>
       <c r="D100" s="60"/>
@@ -33348,12 +33348,12 @@
       <c r="V100" s="61"/>
       <c r="W100" s="31"/>
       <c r="X100" s="32"/>
-      <c r="Y100" s="110"/>
-      <c r="Z100" s="110"/>
-      <c r="AA100" s="110"/>
+      <c r="Y100" s="99"/>
+      <c r="Z100" s="99"/>
+      <c r="AA100" s="99"/>
     </row>
     <row r="101" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="107"/>
+      <c r="A101" s="96"/>
       <c r="B101" s="89"/>
       <c r="C101" s="85"/>
       <c r="D101" s="60"/>
@@ -33377,12 +33377,12 @@
       <c r="V101" s="61"/>
       <c r="W101" s="31"/>
       <c r="X101" s="32"/>
-      <c r="Y101" s="110"/>
-      <c r="Z101" s="110"/>
-      <c r="AA101" s="110"/>
+      <c r="Y101" s="99"/>
+      <c r="Z101" s="99"/>
+      <c r="AA101" s="99"/>
     </row>
     <row r="102" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="107"/>
+      <c r="A102" s="96"/>
       <c r="B102" s="89"/>
       <c r="C102" s="85"/>
       <c r="D102" s="60"/>
@@ -33406,12 +33406,12 @@
       <c r="V102" s="61"/>
       <c r="W102" s="31"/>
       <c r="X102" s="32"/>
-      <c r="Y102" s="110"/>
-      <c r="Z102" s="110"/>
-      <c r="AA102" s="110"/>
+      <c r="Y102" s="99"/>
+      <c r="Z102" s="99"/>
+      <c r="AA102" s="99"/>
     </row>
     <row r="103" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="107"/>
+      <c r="A103" s="96"/>
       <c r="B103" s="89"/>
       <c r="C103" s="85"/>
       <c r="D103" s="60"/>
@@ -33435,12 +33435,12 @@
       <c r="V103" s="61"/>
       <c r="W103" s="31"/>
       <c r="X103" s="32"/>
-      <c r="Y103" s="110"/>
-      <c r="Z103" s="110"/>
-      <c r="AA103" s="110"/>
+      <c r="Y103" s="99"/>
+      <c r="Z103" s="99"/>
+      <c r="AA103" s="99"/>
     </row>
     <row r="104" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="107"/>
+      <c r="A104" s="96"/>
       <c r="B104" s="89"/>
       <c r="C104" s="85"/>
       <c r="D104" s="60"/>
@@ -33464,12 +33464,12 @@
       <c r="V104" s="61"/>
       <c r="W104" s="31"/>
       <c r="X104" s="32"/>
-      <c r="Y104" s="110"/>
-      <c r="Z104" s="110"/>
-      <c r="AA104" s="110"/>
+      <c r="Y104" s="99"/>
+      <c r="Z104" s="99"/>
+      <c r="AA104" s="99"/>
     </row>
     <row r="105" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="107"/>
+      <c r="A105" s="96"/>
       <c r="B105" s="89"/>
       <c r="C105" s="85"/>
       <c r="D105" s="60"/>
@@ -33493,12 +33493,12 @@
       <c r="V105" s="61"/>
       <c r="W105" s="31"/>
       <c r="X105" s="32"/>
-      <c r="Y105" s="110"/>
-      <c r="Z105" s="110"/>
-      <c r="AA105" s="110"/>
+      <c r="Y105" s="99"/>
+      <c r="Z105" s="99"/>
+      <c r="AA105" s="99"/>
     </row>
     <row r="106" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="107"/>
+      <c r="A106" s="96"/>
       <c r="B106" s="89"/>
       <c r="C106" s="85"/>
       <c r="D106" s="60"/>
@@ -33522,12 +33522,12 @@
       <c r="V106" s="61"/>
       <c r="W106" s="31"/>
       <c r="X106" s="32"/>
-      <c r="Y106" s="110"/>
-      <c r="Z106" s="110"/>
-      <c r="AA106" s="110"/>
+      <c r="Y106" s="99"/>
+      <c r="Z106" s="99"/>
+      <c r="AA106" s="99"/>
     </row>
     <row r="107" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="107"/>
+      <c r="A107" s="96"/>
       <c r="B107" s="89"/>
       <c r="C107" s="85"/>
       <c r="D107" s="60"/>
@@ -33551,12 +33551,12 @@
       <c r="V107" s="61"/>
       <c r="W107" s="31"/>
       <c r="X107" s="32"/>
-      <c r="Y107" s="110"/>
-      <c r="Z107" s="110"/>
-      <c r="AA107" s="110"/>
+      <c r="Y107" s="99"/>
+      <c r="Z107" s="99"/>
+      <c r="AA107" s="99"/>
     </row>
     <row r="108" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="107"/>
+      <c r="A108" s="96"/>
       <c r="B108" s="89"/>
       <c r="C108" s="85"/>
       <c r="D108" s="60"/>
@@ -33580,12 +33580,12 @@
       <c r="V108" s="61"/>
       <c r="W108" s="31"/>
       <c r="X108" s="32"/>
-      <c r="Y108" s="110"/>
-      <c r="Z108" s="110"/>
-      <c r="AA108" s="110"/>
+      <c r="Y108" s="99"/>
+      <c r="Z108" s="99"/>
+      <c r="AA108" s="99"/>
     </row>
     <row r="109" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="107"/>
+      <c r="A109" s="96"/>
       <c r="B109" s="89"/>
       <c r="C109" s="85"/>
       <c r="D109" s="60"/>
@@ -33609,12 +33609,12 @@
       <c r="V109" s="61"/>
       <c r="W109" s="31"/>
       <c r="X109" s="32"/>
-      <c r="Y109" s="110"/>
-      <c r="Z109" s="110"/>
-      <c r="AA109" s="110"/>
+      <c r="Y109" s="99"/>
+      <c r="Z109" s="99"/>
+      <c r="AA109" s="99"/>
     </row>
     <row r="110" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="107"/>
+      <c r="A110" s="96"/>
       <c r="B110" s="89"/>
       <c r="C110" s="85"/>
       <c r="D110" s="60"/>
@@ -33638,12 +33638,12 @@
       <c r="V110" s="61"/>
       <c r="W110" s="31"/>
       <c r="X110" s="32"/>
-      <c r="Y110" s="110"/>
-      <c r="Z110" s="110"/>
-      <c r="AA110" s="110"/>
+      <c r="Y110" s="99"/>
+      <c r="Z110" s="99"/>
+      <c r="AA110" s="99"/>
     </row>
     <row r="111" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="107"/>
+      <c r="A111" s="96"/>
       <c r="B111" s="89"/>
       <c r="C111" s="85"/>
       <c r="D111" s="60"/>
@@ -33667,12 +33667,12 @@
       <c r="V111" s="61"/>
       <c r="W111" s="31"/>
       <c r="X111" s="32"/>
-      <c r="Y111" s="110"/>
-      <c r="Z111" s="110"/>
-      <c r="AA111" s="110"/>
+      <c r="Y111" s="99"/>
+      <c r="Z111" s="99"/>
+      <c r="AA111" s="99"/>
     </row>
     <row r="112" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="107"/>
+      <c r="A112" s="96"/>
       <c r="B112" s="89"/>
       <c r="C112" s="85"/>
       <c r="D112" s="60"/>
@@ -33696,12 +33696,12 @@
       <c r="V112" s="61"/>
       <c r="W112" s="31"/>
       <c r="X112" s="32"/>
-      <c r="Y112" s="110"/>
-      <c r="Z112" s="110"/>
-      <c r="AA112" s="110"/>
+      <c r="Y112" s="99"/>
+      <c r="Z112" s="99"/>
+      <c r="AA112" s="99"/>
     </row>
     <row r="113" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="107"/>
+      <c r="A113" s="96"/>
       <c r="B113" s="89"/>
       <c r="C113" s="85"/>
       <c r="D113" s="60"/>
@@ -33725,12 +33725,12 @@
       <c r="V113" s="61"/>
       <c r="W113" s="31"/>
       <c r="X113" s="32"/>
-      <c r="Y113" s="110"/>
-      <c r="Z113" s="110"/>
-      <c r="AA113" s="110"/>
+      <c r="Y113" s="99"/>
+      <c r="Z113" s="99"/>
+      <c r="AA113" s="99"/>
     </row>
     <row r="114" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="107"/>
+      <c r="A114" s="96"/>
       <c r="B114" s="89"/>
       <c r="C114" s="85"/>
       <c r="D114" s="60"/>
@@ -33754,12 +33754,12 @@
       <c r="V114" s="61"/>
       <c r="W114" s="31"/>
       <c r="X114" s="32"/>
-      <c r="Y114" s="110"/>
-      <c r="Z114" s="110"/>
-      <c r="AA114" s="110"/>
+      <c r="Y114" s="99"/>
+      <c r="Z114" s="99"/>
+      <c r="AA114" s="99"/>
     </row>
     <row r="115" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="107"/>
+      <c r="A115" s="96"/>
       <c r="B115" s="89"/>
       <c r="C115" s="85"/>
       <c r="D115" s="60"/>
@@ -33783,12 +33783,12 @@
       <c r="V115" s="61"/>
       <c r="W115" s="31"/>
       <c r="X115" s="32"/>
-      <c r="Y115" s="110"/>
-      <c r="Z115" s="110"/>
-      <c r="AA115" s="110"/>
+      <c r="Y115" s="99"/>
+      <c r="Z115" s="99"/>
+      <c r="AA115" s="99"/>
     </row>
     <row r="116" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="107"/>
+      <c r="A116" s="96"/>
       <c r="B116" s="89"/>
       <c r="C116" s="85"/>
       <c r="D116" s="60"/>
@@ -33812,12 +33812,12 @@
       <c r="V116" s="61"/>
       <c r="W116" s="31"/>
       <c r="X116" s="32"/>
-      <c r="Y116" s="110"/>
-      <c r="Z116" s="110"/>
-      <c r="AA116" s="110"/>
+      <c r="Y116" s="99"/>
+      <c r="Z116" s="99"/>
+      <c r="AA116" s="99"/>
     </row>
     <row r="117" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="107"/>
+      <c r="A117" s="96"/>
       <c r="B117" s="89"/>
       <c r="C117" s="85"/>
       <c r="D117" s="60"/>
@@ -33841,12 +33841,12 @@
       <c r="V117" s="61"/>
       <c r="W117" s="31"/>
       <c r="X117" s="32"/>
-      <c r="Y117" s="110"/>
-      <c r="Z117" s="110"/>
-      <c r="AA117" s="110"/>
+      <c r="Y117" s="99"/>
+      <c r="Z117" s="99"/>
+      <c r="AA117" s="99"/>
     </row>
     <row r="118" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="107"/>
+      <c r="A118" s="96"/>
       <c r="B118" s="89"/>
       <c r="C118" s="85"/>
       <c r="D118" s="60"/>
@@ -33870,12 +33870,12 @@
       <c r="V118" s="61"/>
       <c r="W118" s="31"/>
       <c r="X118" s="32"/>
-      <c r="Y118" s="110"/>
-      <c r="Z118" s="110"/>
-      <c r="AA118" s="110"/>
+      <c r="Y118" s="99"/>
+      <c r="Z118" s="99"/>
+      <c r="AA118" s="99"/>
     </row>
     <row r="119" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="107"/>
+      <c r="A119" s="96"/>
       <c r="B119" s="89"/>
       <c r="C119" s="85"/>
       <c r="D119" s="60"/>
@@ -33899,12 +33899,12 @@
       <c r="V119" s="61"/>
       <c r="W119" s="31"/>
       <c r="X119" s="32"/>
-      <c r="Y119" s="110"/>
-      <c r="Z119" s="110"/>
-      <c r="AA119" s="110"/>
+      <c r="Y119" s="99"/>
+      <c r="Z119" s="99"/>
+      <c r="AA119" s="99"/>
     </row>
     <row r="120" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="107"/>
+      <c r="A120" s="96"/>
       <c r="B120" s="89"/>
       <c r="C120" s="85"/>
       <c r="D120" s="60"/>
@@ -33928,12 +33928,12 @@
       <c r="V120" s="61"/>
       <c r="W120" s="31"/>
       <c r="X120" s="32"/>
-      <c r="Y120" s="110"/>
-      <c r="Z120" s="110"/>
-      <c r="AA120" s="110"/>
+      <c r="Y120" s="99"/>
+      <c r="Z120" s="99"/>
+      <c r="AA120" s="99"/>
     </row>
     <row r="121" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="107"/>
+      <c r="A121" s="96"/>
       <c r="B121" s="89"/>
       <c r="C121" s="85"/>
       <c r="D121" s="60"/>
@@ -33957,12 +33957,12 @@
       <c r="V121" s="61"/>
       <c r="W121" s="31"/>
       <c r="X121" s="32"/>
-      <c r="Y121" s="110"/>
-      <c r="Z121" s="110"/>
-      <c r="AA121" s="110"/>
+      <c r="Y121" s="99"/>
+      <c r="Z121" s="99"/>
+      <c r="AA121" s="99"/>
     </row>
     <row r="122" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="107"/>
+      <c r="A122" s="96"/>
       <c r="B122" s="89"/>
       <c r="C122" s="85"/>
       <c r="D122" s="60"/>
@@ -33986,12 +33986,12 @@
       <c r="V122" s="61"/>
       <c r="W122" s="31"/>
       <c r="X122" s="32"/>
-      <c r="Y122" s="110"/>
-      <c r="Z122" s="110"/>
-      <c r="AA122" s="110"/>
+      <c r="Y122" s="99"/>
+      <c r="Z122" s="99"/>
+      <c r="AA122" s="99"/>
     </row>
     <row r="123" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="107"/>
+      <c r="A123" s="96"/>
       <c r="B123" s="89"/>
       <c r="C123" s="85"/>
       <c r="D123" s="60"/>
@@ -34015,12 +34015,12 @@
       <c r="V123" s="61"/>
       <c r="W123" s="31"/>
       <c r="X123" s="32"/>
-      <c r="Y123" s="110"/>
-      <c r="Z123" s="110"/>
-      <c r="AA123" s="110"/>
+      <c r="Y123" s="99"/>
+      <c r="Z123" s="99"/>
+      <c r="AA123" s="99"/>
     </row>
     <row r="124" spans="1:27" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A124" s="107"/>
+      <c r="A124" s="96"/>
       <c r="B124" s="89"/>
       <c r="C124" s="85"/>
       <c r="D124" s="60"/>
@@ -34044,12 +34044,12 @@
       <c r="V124" s="61"/>
       <c r="W124" s="31"/>
       <c r="X124" s="32"/>
-      <c r="Y124" s="110"/>
-      <c r="Z124" s="110"/>
-      <c r="AA124" s="110"/>
+      <c r="Y124" s="99"/>
+      <c r="Z124" s="99"/>
+      <c r="AA124" s="99"/>
     </row>
     <row r="125" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A125" s="107"/>
+      <c r="A125" s="96"/>
       <c r="B125" s="89"/>
       <c r="C125" s="85"/>
       <c r="D125" s="60"/>
@@ -34073,12 +34073,12 @@
       <c r="V125" s="61"/>
       <c r="W125" s="31"/>
       <c r="X125" s="32"/>
-      <c r="Y125" s="110"/>
-      <c r="Z125" s="110"/>
-      <c r="AA125" s="110"/>
+      <c r="Y125" s="99"/>
+      <c r="Z125" s="99"/>
+      <c r="AA125" s="99"/>
     </row>
     <row r="126" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A126" s="107"/>
+      <c r="A126" s="96"/>
       <c r="B126" s="89"/>
       <c r="C126" s="85"/>
       <c r="D126" s="60"/>
@@ -34102,12 +34102,12 @@
       <c r="V126" s="61"/>
       <c r="W126" s="31"/>
       <c r="X126" s="32"/>
-      <c r="Y126" s="110"/>
-      <c r="Z126" s="110"/>
-      <c r="AA126" s="110"/>
+      <c r="Y126" s="99"/>
+      <c r="Z126" s="99"/>
+      <c r="AA126" s="99"/>
     </row>
     <row r="127" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="107"/>
+      <c r="A127" s="96"/>
       <c r="B127" s="89"/>
       <c r="C127" s="85"/>
       <c r="D127" s="60"/>
@@ -34131,12 +34131,12 @@
       <c r="V127" s="61"/>
       <c r="W127" s="31"/>
       <c r="X127" s="32"/>
-      <c r="Y127" s="110"/>
-      <c r="Z127" s="110"/>
-      <c r="AA127" s="110"/>
+      <c r="Y127" s="99"/>
+      <c r="Z127" s="99"/>
+      <c r="AA127" s="99"/>
     </row>
     <row r="128" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A128" s="107"/>
+      <c r="A128" s="96"/>
       <c r="B128" s="89"/>
       <c r="C128" s="85"/>
       <c r="D128" s="60"/>
@@ -34160,12 +34160,12 @@
       <c r="V128" s="61"/>
       <c r="W128" s="31"/>
       <c r="X128" s="32"/>
-      <c r="Y128" s="110"/>
-      <c r="Z128" s="110"/>
-      <c r="AA128" s="110"/>
+      <c r="Y128" s="99"/>
+      <c r="Z128" s="99"/>
+      <c r="AA128" s="99"/>
     </row>
     <row r="129" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A129" s="107"/>
+      <c r="A129" s="96"/>
       <c r="B129" s="89"/>
       <c r="C129" s="85"/>
       <c r="D129" s="60"/>
@@ -34189,12 +34189,12 @@
       <c r="V129" s="61"/>
       <c r="W129" s="31"/>
       <c r="X129" s="32"/>
-      <c r="Y129" s="110"/>
-      <c r="Z129" s="110"/>
-      <c r="AA129" s="110"/>
+      <c r="Y129" s="99"/>
+      <c r="Z129" s="99"/>
+      <c r="AA129" s="99"/>
     </row>
     <row r="130" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A130" s="107"/>
+      <c r="A130" s="96"/>
       <c r="B130" s="89"/>
       <c r="C130" s="85"/>
       <c r="D130" s="60"/>
@@ -34218,12 +34218,12 @@
       <c r="V130" s="61"/>
       <c r="W130" s="31"/>
       <c r="X130" s="32"/>
-      <c r="Y130" s="110"/>
-      <c r="Z130" s="110"/>
-      <c r="AA130" s="110"/>
+      <c r="Y130" s="99"/>
+      <c r="Z130" s="99"/>
+      <c r="AA130" s="99"/>
     </row>
     <row r="131" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A131" s="107"/>
+      <c r="A131" s="96"/>
       <c r="B131" s="89"/>
       <c r="C131" s="85"/>
       <c r="D131" s="60"/>
@@ -34247,12 +34247,12 @@
       <c r="V131" s="61"/>
       <c r="W131" s="31"/>
       <c r="X131" s="32"/>
-      <c r="Y131" s="110"/>
-      <c r="Z131" s="110"/>
-      <c r="AA131" s="110"/>
+      <c r="Y131" s="99"/>
+      <c r="Z131" s="99"/>
+      <c r="AA131" s="99"/>
     </row>
     <row r="132" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A132" s="107"/>
+      <c r="A132" s="96"/>
       <c r="B132" s="89"/>
       <c r="C132" s="85"/>
       <c r="D132" s="60"/>
@@ -34276,12 +34276,12 @@
       <c r="V132" s="61"/>
       <c r="W132" s="31"/>
       <c r="X132" s="32"/>
-      <c r="Y132" s="110"/>
-      <c r="Z132" s="110"/>
-      <c r="AA132" s="110"/>
+      <c r="Y132" s="99"/>
+      <c r="Z132" s="99"/>
+      <c r="AA132" s="99"/>
     </row>
     <row r="133" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A133" s="107"/>
+      <c r="A133" s="96"/>
       <c r="B133" s="89"/>
       <c r="C133" s="85"/>
       <c r="D133" s="60"/>
@@ -34305,12 +34305,12 @@
       <c r="V133" s="61"/>
       <c r="W133" s="31"/>
       <c r="X133" s="32"/>
-      <c r="Y133" s="110"/>
-      <c r="Z133" s="110"/>
-      <c r="AA133" s="110"/>
+      <c r="Y133" s="99"/>
+      <c r="Z133" s="99"/>
+      <c r="AA133" s="99"/>
     </row>
     <row r="134" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="107"/>
+      <c r="A134" s="96"/>
       <c r="B134" s="89"/>
       <c r="C134" s="85"/>
       <c r="D134" s="60"/>
@@ -34334,12 +34334,12 @@
       <c r="V134" s="61"/>
       <c r="W134" s="31"/>
       <c r="X134" s="32"/>
-      <c r="Y134" s="110"/>
-      <c r="Z134" s="110"/>
-      <c r="AA134" s="110"/>
+      <c r="Y134" s="99"/>
+      <c r="Z134" s="99"/>
+      <c r="AA134" s="99"/>
     </row>
     <row r="135" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A135" s="107"/>
+      <c r="A135" s="96"/>
       <c r="B135" s="89"/>
       <c r="C135" s="85"/>
       <c r="D135" s="60"/>
@@ -34363,12 +34363,12 @@
       <c r="V135" s="61"/>
       <c r="W135" s="31"/>
       <c r="X135" s="32"/>
-      <c r="Y135" s="110"/>
-      <c r="Z135" s="110"/>
-      <c r="AA135" s="110"/>
+      <c r="Y135" s="99"/>
+      <c r="Z135" s="99"/>
+      <c r="AA135" s="99"/>
     </row>
     <row r="136" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A136" s="107"/>
+      <c r="A136" s="96"/>
       <c r="B136" s="89"/>
       <c r="C136" s="85"/>
       <c r="D136" s="60"/>
@@ -34392,12 +34392,12 @@
       <c r="V136" s="61"/>
       <c r="W136" s="31"/>
       <c r="X136" s="32"/>
-      <c r="Y136" s="110"/>
-      <c r="Z136" s="110"/>
-      <c r="AA136" s="110"/>
+      <c r="Y136" s="99"/>
+      <c r="Z136" s="99"/>
+      <c r="AA136" s="99"/>
     </row>
     <row r="137" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="107"/>
+      <c r="A137" s="96"/>
       <c r="B137" s="89"/>
       <c r="C137" s="85"/>
       <c r="D137" s="60"/>
@@ -34421,12 +34421,12 @@
       <c r="V137" s="61"/>
       <c r="W137" s="31"/>
       <c r="X137" s="32"/>
-      <c r="Y137" s="110"/>
-      <c r="Z137" s="110"/>
-      <c r="AA137" s="110"/>
+      <c r="Y137" s="99"/>
+      <c r="Z137" s="99"/>
+      <c r="AA137" s="99"/>
     </row>
     <row r="138" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A138" s="107"/>
+      <c r="A138" s="96"/>
       <c r="B138" s="89"/>
       <c r="C138" s="85"/>
       <c r="D138" s="60"/>
@@ -34450,12 +34450,12 @@
       <c r="V138" s="61"/>
       <c r="W138" s="31"/>
       <c r="X138" s="32"/>
-      <c r="Y138" s="110"/>
-      <c r="Z138" s="110"/>
-      <c r="AA138" s="110"/>
+      <c r="Y138" s="99"/>
+      <c r="Z138" s="99"/>
+      <c r="AA138" s="99"/>
     </row>
     <row r="139" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A139" s="107"/>
+      <c r="A139" s="96"/>
       <c r="B139" s="89"/>
       <c r="C139" s="85"/>
       <c r="D139" s="60"/>
@@ -34479,12 +34479,12 @@
       <c r="V139" s="61"/>
       <c r="W139" s="31"/>
       <c r="X139" s="32"/>
-      <c r="Y139" s="110"/>
-      <c r="Z139" s="110"/>
-      <c r="AA139" s="110"/>
+      <c r="Y139" s="99"/>
+      <c r="Z139" s="99"/>
+      <c r="AA139" s="99"/>
     </row>
     <row r="140" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A140" s="107"/>
+      <c r="A140" s="96"/>
       <c r="B140" s="89"/>
       <c r="C140" s="85"/>
       <c r="D140" s="60"/>
@@ -34508,12 +34508,12 @@
       <c r="V140" s="61"/>
       <c r="W140" s="31"/>
       <c r="X140" s="32"/>
-      <c r="Y140" s="110"/>
-      <c r="Z140" s="110"/>
-      <c r="AA140" s="110"/>
+      <c r="Y140" s="99"/>
+      <c r="Z140" s="99"/>
+      <c r="AA140" s="99"/>
     </row>
     <row r="141" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A141" s="107"/>
+      <c r="A141" s="96"/>
       <c r="B141" s="89"/>
       <c r="C141" s="85"/>
       <c r="D141" s="60"/>
@@ -34537,12 +34537,12 @@
       <c r="V141" s="61"/>
       <c r="W141" s="31"/>
       <c r="X141" s="32"/>
-      <c r="Y141" s="110"/>
-      <c r="Z141" s="110"/>
-      <c r="AA141" s="110"/>
+      <c r="Y141" s="99"/>
+      <c r="Z141" s="99"/>
+      <c r="AA141" s="99"/>
     </row>
     <row r="142" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A142" s="107"/>
+      <c r="A142" s="96"/>
       <c r="B142" s="89"/>
       <c r="C142" s="85"/>
       <c r="D142" s="60"/>
@@ -34566,12 +34566,12 @@
       <c r="V142" s="61"/>
       <c r="W142" s="31"/>
       <c r="X142" s="32"/>
-      <c r="Y142" s="110"/>
-      <c r="Z142" s="110"/>
-      <c r="AA142" s="110"/>
+      <c r="Y142" s="99"/>
+      <c r="Z142" s="99"/>
+      <c r="AA142" s="99"/>
     </row>
     <row r="143" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A143" s="107"/>
+      <c r="A143" s="96"/>
       <c r="B143" s="89"/>
       <c r="C143" s="85"/>
       <c r="D143" s="60"/>
@@ -34595,12 +34595,12 @@
       <c r="V143" s="61"/>
       <c r="W143" s="31"/>
       <c r="X143" s="32"/>
-      <c r="Y143" s="110"/>
-      <c r="Z143" s="110"/>
-      <c r="AA143" s="110"/>
+      <c r="Y143" s="99"/>
+      <c r="Z143" s="99"/>
+      <c r="AA143" s="99"/>
     </row>
     <row r="144" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A144" s="107"/>
+      <c r="A144" s="96"/>
       <c r="B144" s="89"/>
       <c r="C144" s="85"/>
       <c r="D144" s="60"/>
@@ -34624,12 +34624,12 @@
       <c r="V144" s="61"/>
       <c r="W144" s="31"/>
       <c r="X144" s="32"/>
-      <c r="Y144" s="110"/>
-      <c r="Z144" s="110"/>
-      <c r="AA144" s="110"/>
+      <c r="Y144" s="99"/>
+      <c r="Z144" s="99"/>
+      <c r="AA144" s="99"/>
     </row>
     <row r="145" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A145" s="107"/>
+      <c r="A145" s="96"/>
       <c r="B145" s="89"/>
       <c r="C145" s="85"/>
       <c r="D145" s="60"/>
@@ -34653,12 +34653,12 @@
       <c r="V145" s="61"/>
       <c r="W145" s="31"/>
       <c r="X145" s="32"/>
-      <c r="Y145" s="110"/>
-      <c r="Z145" s="110"/>
-      <c r="AA145" s="110"/>
+      <c r="Y145" s="99"/>
+      <c r="Z145" s="99"/>
+      <c r="AA145" s="99"/>
     </row>
     <row r="146" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="107"/>
+      <c r="A146" s="96"/>
       <c r="B146" s="89"/>
       <c r="C146" s="85"/>
       <c r="D146" s="60"/>
@@ -34682,12 +34682,12 @@
       <c r="V146" s="61"/>
       <c r="W146" s="31"/>
       <c r="X146" s="32"/>
-      <c r="Y146" s="110"/>
-      <c r="Z146" s="110"/>
-      <c r="AA146" s="110"/>
+      <c r="Y146" s="99"/>
+      <c r="Z146" s="99"/>
+      <c r="AA146" s="99"/>
     </row>
     <row r="147" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" s="107"/>
+      <c r="A147" s="96"/>
       <c r="B147" s="89"/>
       <c r="C147" s="85"/>
       <c r="D147" s="60"/>
@@ -34711,12 +34711,12 @@
       <c r="V147" s="61"/>
       <c r="W147" s="31"/>
       <c r="X147" s="32"/>
-      <c r="Y147" s="110"/>
-      <c r="Z147" s="110"/>
-      <c r="AA147" s="110"/>
+      <c r="Y147" s="99"/>
+      <c r="Z147" s="99"/>
+      <c r="AA147" s="99"/>
     </row>
     <row r="148" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="107"/>
+      <c r="A148" s="96"/>
       <c r="B148" s="89"/>
       <c r="C148" s="85"/>
       <c r="D148" s="60"/>
@@ -34740,12 +34740,12 @@
       <c r="V148" s="61"/>
       <c r="W148" s="31"/>
       <c r="X148" s="32"/>
-      <c r="Y148" s="110"/>
-      <c r="Z148" s="110"/>
-      <c r="AA148" s="110"/>
+      <c r="Y148" s="99"/>
+      <c r="Z148" s="99"/>
+      <c r="AA148" s="99"/>
     </row>
     <row r="149" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A149" s="107"/>
+      <c r="A149" s="96"/>
       <c r="B149" s="89"/>
       <c r="C149" s="85"/>
       <c r="D149" s="60"/>
@@ -34769,12 +34769,12 @@
       <c r="V149" s="61"/>
       <c r="W149" s="31"/>
       <c r="X149" s="32"/>
-      <c r="Y149" s="110"/>
-      <c r="Z149" s="110"/>
-      <c r="AA149" s="110"/>
+      <c r="Y149" s="99"/>
+      <c r="Z149" s="99"/>
+      <c r="AA149" s="99"/>
     </row>
     <row r="150" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="107"/>
+      <c r="A150" s="96"/>
       <c r="B150" s="89"/>
       <c r="C150" s="85"/>
       <c r="D150" s="60"/>
@@ -34798,12 +34798,12 @@
       <c r="V150" s="61"/>
       <c r="W150" s="31"/>
       <c r="X150" s="32"/>
-      <c r="Y150" s="110"/>
-      <c r="Z150" s="110"/>
-      <c r="AA150" s="110"/>
+      <c r="Y150" s="99"/>
+      <c r="Z150" s="99"/>
+      <c r="AA150" s="99"/>
     </row>
     <row r="151" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="107"/>
+      <c r="A151" s="96"/>
       <c r="B151" s="89"/>
       <c r="C151" s="85"/>
       <c r="D151" s="60"/>
@@ -34827,12 +34827,12 @@
       <c r="V151" s="61"/>
       <c r="W151" s="31"/>
       <c r="X151" s="32"/>
-      <c r="Y151" s="110"/>
-      <c r="Z151" s="110"/>
-      <c r="AA151" s="110"/>
+      <c r="Y151" s="99"/>
+      <c r="Z151" s="99"/>
+      <c r="AA151" s="99"/>
     </row>
     <row r="152" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A152" s="107"/>
+      <c r="A152" s="96"/>
       <c r="B152" s="89"/>
       <c r="C152" s="85"/>
       <c r="D152" s="60"/>
@@ -34856,12 +34856,12 @@
       <c r="V152" s="61"/>
       <c r="W152" s="31"/>
       <c r="X152" s="32"/>
-      <c r="Y152" s="110"/>
-      <c r="Z152" s="110"/>
-      <c r="AA152" s="110"/>
+      <c r="Y152" s="99"/>
+      <c r="Z152" s="99"/>
+      <c r="AA152" s="99"/>
     </row>
     <row r="153" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A153" s="107"/>
+      <c r="A153" s="96"/>
       <c r="B153" s="89"/>
       <c r="C153" s="85"/>
       <c r="D153" s="60"/>
@@ -34885,12 +34885,12 @@
       <c r="V153" s="61"/>
       <c r="W153" s="31"/>
       <c r="X153" s="32"/>
-      <c r="Y153" s="110"/>
-      <c r="Z153" s="110"/>
-      <c r="AA153" s="110"/>
+      <c r="Y153" s="99"/>
+      <c r="Z153" s="99"/>
+      <c r="AA153" s="99"/>
     </row>
     <row r="154" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="107"/>
+      <c r="A154" s="96"/>
       <c r="B154" s="89"/>
       <c r="C154" s="85"/>
       <c r="D154" s="60"/>
@@ -34914,12 +34914,12 @@
       <c r="V154" s="61"/>
       <c r="W154" s="31"/>
       <c r="X154" s="32"/>
-      <c r="Y154" s="110"/>
-      <c r="Z154" s="110"/>
-      <c r="AA154" s="110"/>
+      <c r="Y154" s="99"/>
+      <c r="Z154" s="99"/>
+      <c r="AA154" s="99"/>
     </row>
     <row r="155" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A155" s="107"/>
+      <c r="A155" s="96"/>
       <c r="B155" s="89"/>
       <c r="C155" s="85"/>
       <c r="D155" s="60"/>
@@ -34943,12 +34943,12 @@
       <c r="V155" s="61"/>
       <c r="W155" s="31"/>
       <c r="X155" s="32"/>
-      <c r="Y155" s="110"/>
-      <c r="Z155" s="110"/>
-      <c r="AA155" s="110"/>
+      <c r="Y155" s="99"/>
+      <c r="Z155" s="99"/>
+      <c r="AA155" s="99"/>
     </row>
     <row r="156" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A156" s="107"/>
+      <c r="A156" s="96"/>
       <c r="B156" s="89"/>
       <c r="C156" s="85"/>
       <c r="D156" s="60"/>
@@ -34972,12 +34972,12 @@
       <c r="V156" s="61"/>
       <c r="W156" s="31"/>
       <c r="X156" s="32"/>
-      <c r="Y156" s="110"/>
-      <c r="Z156" s="110"/>
-      <c r="AA156" s="110"/>
+      <c r="Y156" s="99"/>
+      <c r="Z156" s="99"/>
+      <c r="AA156" s="99"/>
     </row>
     <row r="157" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="107"/>
+      <c r="A157" s="96"/>
       <c r="B157" s="89"/>
       <c r="C157" s="85"/>
       <c r="D157" s="60"/>
@@ -35001,12 +35001,12 @@
       <c r="V157" s="61"/>
       <c r="W157" s="31"/>
       <c r="X157" s="32"/>
-      <c r="Y157" s="110"/>
-      <c r="Z157" s="110"/>
-      <c r="AA157" s="110"/>
+      <c r="Y157" s="99"/>
+      <c r="Z157" s="99"/>
+      <c r="AA157" s="99"/>
     </row>
     <row r="158" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="107"/>
+      <c r="A158" s="96"/>
       <c r="B158" s="89"/>
       <c r="C158" s="85"/>
       <c r="D158" s="60"/>
@@ -35030,12 +35030,12 @@
       <c r="V158" s="61"/>
       <c r="W158" s="31"/>
       <c r="X158" s="32"/>
-      <c r="Y158" s="110"/>
-      <c r="Z158" s="110"/>
-      <c r="AA158" s="110"/>
+      <c r="Y158" s="99"/>
+      <c r="Z158" s="99"/>
+      <c r="AA158" s="99"/>
     </row>
     <row r="159" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A159" s="107"/>
+      <c r="A159" s="96"/>
       <c r="B159" s="89"/>
       <c r="C159" s="85"/>
       <c r="D159" s="60"/>
@@ -35059,12 +35059,12 @@
       <c r="V159" s="61"/>
       <c r="W159" s="31"/>
       <c r="X159" s="32"/>
-      <c r="Y159" s="110"/>
-      <c r="Z159" s="110"/>
-      <c r="AA159" s="110"/>
+      <c r="Y159" s="99"/>
+      <c r="Z159" s="99"/>
+      <c r="AA159" s="99"/>
     </row>
     <row r="160" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="107"/>
+      <c r="A160" s="96"/>
       <c r="B160" s="89"/>
       <c r="C160" s="85"/>
       <c r="D160" s="60"/>
@@ -35088,12 +35088,12 @@
       <c r="V160" s="61"/>
       <c r="W160" s="31"/>
       <c r="X160" s="32"/>
-      <c r="Y160" s="110"/>
-      <c r="Z160" s="110"/>
-      <c r="AA160" s="110"/>
+      <c r="Y160" s="99"/>
+      <c r="Z160" s="99"/>
+      <c r="AA160" s="99"/>
     </row>
     <row r="161" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A161" s="107"/>
+      <c r="A161" s="96"/>
       <c r="B161" s="89"/>
       <c r="C161" s="85"/>
       <c r="D161" s="60"/>
@@ -35117,12 +35117,12 @@
       <c r="V161" s="61"/>
       <c r="W161" s="31"/>
       <c r="X161" s="32"/>
-      <c r="Y161" s="110"/>
-      <c r="Z161" s="110"/>
-      <c r="AA161" s="110"/>
+      <c r="Y161" s="99"/>
+      <c r="Z161" s="99"/>
+      <c r="AA161" s="99"/>
     </row>
     <row r="162" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A162" s="107"/>
+      <c r="A162" s="96"/>
       <c r="B162" s="89"/>
       <c r="C162" s="85"/>
       <c r="D162" s="60"/>
@@ -35146,12 +35146,12 @@
       <c r="V162" s="61"/>
       <c r="W162" s="31"/>
       <c r="X162" s="32"/>
-      <c r="Y162" s="110"/>
-      <c r="Z162" s="110"/>
-      <c r="AA162" s="110"/>
+      <c r="Y162" s="99"/>
+      <c r="Z162" s="99"/>
+      <c r="AA162" s="99"/>
     </row>
     <row r="163" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="107"/>
+      <c r="A163" s="96"/>
       <c r="B163" s="89"/>
       <c r="C163" s="85"/>
       <c r="D163" s="60"/>
@@ -35175,12 +35175,12 @@
       <c r="V163" s="61"/>
       <c r="W163" s="31"/>
       <c r="X163" s="32"/>
-      <c r="Y163" s="110"/>
-      <c r="Z163" s="110"/>
-      <c r="AA163" s="110"/>
+      <c r="Y163" s="99"/>
+      <c r="Z163" s="99"/>
+      <c r="AA163" s="99"/>
     </row>
     <row r="164" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A164" s="107"/>
+      <c r="A164" s="96"/>
       <c r="B164" s="89"/>
       <c r="C164" s="85"/>
       <c r="D164" s="60"/>
@@ -35204,12 +35204,12 @@
       <c r="V164" s="61"/>
       <c r="W164" s="31"/>
       <c r="X164" s="32"/>
-      <c r="Y164" s="110"/>
-      <c r="Z164" s="110"/>
-      <c r="AA164" s="110"/>
+      <c r="Y164" s="99"/>
+      <c r="Z164" s="99"/>
+      <c r="AA164" s="99"/>
     </row>
     <row r="165" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A165" s="107"/>
+      <c r="A165" s="96"/>
       <c r="B165" s="89"/>
       <c r="C165" s="85"/>
       <c r="D165" s="60"/>
@@ -35233,12 +35233,12 @@
       <c r="V165" s="61"/>
       <c r="W165" s="31"/>
       <c r="X165" s="32"/>
-      <c r="Y165" s="110"/>
-      <c r="Z165" s="110"/>
-      <c r="AA165" s="110"/>
+      <c r="Y165" s="99"/>
+      <c r="Z165" s="99"/>
+      <c r="AA165" s="99"/>
     </row>
     <row r="166" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="107"/>
+      <c r="A166" s="96"/>
       <c r="B166" s="89"/>
       <c r="C166" s="85"/>
       <c r="D166" s="60"/>
@@ -35262,12 +35262,12 @@
       <c r="V166" s="61"/>
       <c r="W166" s="31"/>
       <c r="X166" s="32"/>
-      <c r="Y166" s="110"/>
-      <c r="Z166" s="110"/>
-      <c r="AA166" s="110"/>
+      <c r="Y166" s="99"/>
+      <c r="Z166" s="99"/>
+      <c r="AA166" s="99"/>
     </row>
     <row r="167" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A167" s="107"/>
+      <c r="A167" s="96"/>
       <c r="B167" s="89"/>
       <c r="C167" s="85"/>
       <c r="D167" s="60"/>
@@ -35291,12 +35291,12 @@
       <c r="V167" s="61"/>
       <c r="W167" s="31"/>
       <c r="X167" s="32"/>
-      <c r="Y167" s="110"/>
-      <c r="Z167" s="110"/>
-      <c r="AA167" s="110"/>
+      <c r="Y167" s="99"/>
+      <c r="Z167" s="99"/>
+      <c r="AA167" s="99"/>
     </row>
     <row r="168" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A168" s="107"/>
+      <c r="A168" s="96"/>
       <c r="B168" s="89"/>
       <c r="C168" s="85"/>
       <c r="D168" s="60"/>
@@ -35320,12 +35320,12 @@
       <c r="V168" s="61"/>
       <c r="W168" s="31"/>
       <c r="X168" s="32"/>
-      <c r="Y168" s="110"/>
-      <c r="Z168" s="110"/>
-      <c r="AA168" s="110"/>
+      <c r="Y168" s="99"/>
+      <c r="Z168" s="99"/>
+      <c r="AA168" s="99"/>
     </row>
     <row r="169" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="107"/>
+      <c r="A169" s="96"/>
       <c r="B169" s="89"/>
       <c r="C169" s="85"/>
       <c r="D169" s="60"/>
@@ -35349,12 +35349,12 @@
       <c r="V169" s="61"/>
       <c r="W169" s="31"/>
       <c r="X169" s="32"/>
-      <c r="Y169" s="110"/>
-      <c r="Z169" s="110"/>
-      <c r="AA169" s="110"/>
+      <c r="Y169" s="99"/>
+      <c r="Z169" s="99"/>
+      <c r="AA169" s="99"/>
     </row>
     <row r="170" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A170" s="107"/>
+      <c r="A170" s="96"/>
       <c r="B170" s="89"/>
       <c r="C170" s="85"/>
       <c r="D170" s="60"/>
@@ -35378,12 +35378,12 @@
       <c r="V170" s="61"/>
       <c r="W170" s="31"/>
       <c r="X170" s="32"/>
-      <c r="Y170" s="110"/>
-      <c r="Z170" s="110"/>
-      <c r="AA170" s="110"/>
+      <c r="Y170" s="99"/>
+      <c r="Z170" s="99"/>
+      <c r="AA170" s="99"/>
     </row>
     <row r="171" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A171" s="107"/>
+      <c r="A171" s="96"/>
       <c r="B171" s="89"/>
       <c r="C171" s="85"/>
       <c r="D171" s="60"/>
@@ -35407,12 +35407,12 @@
       <c r="V171" s="61"/>
       <c r="W171" s="31"/>
       <c r="X171" s="32"/>
-      <c r="Y171" s="110"/>
-      <c r="Z171" s="110"/>
-      <c r="AA171" s="110"/>
+      <c r="Y171" s="99"/>
+      <c r="Z171" s="99"/>
+      <c r="AA171" s="99"/>
     </row>
     <row r="172" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="107"/>
+      <c r="A172" s="96"/>
       <c r="B172" s="89"/>
       <c r="C172" s="85"/>
       <c r="D172" s="60"/>
@@ -35436,12 +35436,12 @@
       <c r="V172" s="61"/>
       <c r="W172" s="31"/>
       <c r="X172" s="32"/>
-      <c r="Y172" s="110"/>
-      <c r="Z172" s="110"/>
-      <c r="AA172" s="110"/>
+      <c r="Y172" s="99"/>
+      <c r="Z172" s="99"/>
+      <c r="AA172" s="99"/>
     </row>
     <row r="173" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A173" s="107"/>
+      <c r="A173" s="96"/>
       <c r="B173" s="89"/>
       <c r="C173" s="85"/>
       <c r="D173" s="60"/>
@@ -35465,12 +35465,12 @@
       <c r="V173" s="61"/>
       <c r="W173" s="31"/>
       <c r="X173" s="32"/>
-      <c r="Y173" s="110"/>
-      <c r="Z173" s="110"/>
-      <c r="AA173" s="110"/>
+      <c r="Y173" s="99"/>
+      <c r="Z173" s="99"/>
+      <c r="AA173" s="99"/>
     </row>
     <row r="174" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A174" s="107"/>
+      <c r="A174" s="96"/>
       <c r="B174" s="89"/>
       <c r="C174" s="85"/>
       <c r="D174" s="60"/>
@@ -35494,12 +35494,12 @@
       <c r="V174" s="61"/>
       <c r="W174" s="31"/>
       <c r="X174" s="32"/>
-      <c r="Y174" s="110"/>
-      <c r="Z174" s="110"/>
-      <c r="AA174" s="110"/>
+      <c r="Y174" s="99"/>
+      <c r="Z174" s="99"/>
+      <c r="AA174" s="99"/>
     </row>
     <row r="175" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="107"/>
+      <c r="A175" s="96"/>
       <c r="B175" s="89"/>
       <c r="C175" s="85"/>
       <c r="D175" s="60"/>
@@ -35523,12 +35523,12 @@
       <c r="V175" s="61"/>
       <c r="W175" s="31"/>
       <c r="X175" s="32"/>
-      <c r="Y175" s="110"/>
-      <c r="Z175" s="110"/>
-      <c r="AA175" s="110"/>
+      <c r="Y175" s="99"/>
+      <c r="Z175" s="99"/>
+      <c r="AA175" s="99"/>
     </row>
     <row r="176" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A176" s="107"/>
+      <c r="A176" s="96"/>
       <c r="B176" s="89"/>
       <c r="C176" s="85"/>
       <c r="D176" s="60"/>
@@ -35552,12 +35552,12 @@
       <c r="V176" s="61"/>
       <c r="W176" s="31"/>
       <c r="X176" s="32"/>
-      <c r="Y176" s="110"/>
-      <c r="Z176" s="110"/>
-      <c r="AA176" s="110"/>
+      <c r="Y176" s="99"/>
+      <c r="Z176" s="99"/>
+      <c r="AA176" s="99"/>
     </row>
     <row r="177" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A177" s="107"/>
+      <c r="A177" s="96"/>
       <c r="B177" s="89"/>
       <c r="C177" s="85"/>
       <c r="D177" s="60"/>
@@ -35581,12 +35581,12 @@
       <c r="V177" s="61"/>
       <c r="W177" s="31"/>
       <c r="X177" s="32"/>
-      <c r="Y177" s="110"/>
-      <c r="Z177" s="110"/>
-      <c r="AA177" s="110"/>
+      <c r="Y177" s="99"/>
+      <c r="Z177" s="99"/>
+      <c r="AA177" s="99"/>
     </row>
     <row r="178" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="107"/>
+      <c r="A178" s="96"/>
       <c r="B178" s="90"/>
       <c r="C178" s="86"/>
       <c r="D178" s="66"/>
@@ -35610,12 +35610,12 @@
       <c r="V178" s="61"/>
       <c r="W178" s="31"/>
       <c r="X178" s="33"/>
-      <c r="Y178" s="111"/>
-      <c r="Z178" s="111"/>
-      <c r="AA178" s="111"/>
+      <c r="Y178" s="100"/>
+      <c r="Z178" s="100"/>
+      <c r="AA178" s="100"/>
     </row>
     <row r="179" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A179" s="107"/>
+      <c r="A179" s="96"/>
       <c r="B179" s="90"/>
       <c r="C179" s="91"/>
       <c r="D179" s="71"/>
@@ -35639,12 +35639,12 @@
       <c r="V179" s="61"/>
       <c r="W179" s="34"/>
       <c r="X179" s="33"/>
-      <c r="Y179" s="111"/>
-      <c r="Z179" s="111"/>
-      <c r="AA179" s="111"/>
+      <c r="Y179" s="100"/>
+      <c r="Z179" s="100"/>
+      <c r="AA179" s="100"/>
     </row>
     <row r="180" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A180" s="107"/>
+      <c r="A180" s="96"/>
       <c r="B180" s="90"/>
       <c r="C180" s="86"/>
       <c r="D180" s="66"/>
@@ -35668,12 +35668,12 @@
       <c r="V180" s="61"/>
       <c r="W180" s="33"/>
       <c r="X180" s="33"/>
-      <c r="Y180" s="111"/>
-      <c r="Z180" s="111"/>
-      <c r="AA180" s="111"/>
+      <c r="Y180" s="100"/>
+      <c r="Z180" s="100"/>
+      <c r="AA180" s="100"/>
     </row>
     <row r="181" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="107"/>
+      <c r="A181" s="96"/>
       <c r="B181" s="90"/>
       <c r="C181" s="86"/>
       <c r="D181" s="66"/>
@@ -35697,12 +35697,12 @@
       <c r="V181" s="61"/>
       <c r="W181" s="31"/>
       <c r="X181" s="33"/>
-      <c r="Y181" s="111"/>
-      <c r="Z181" s="111"/>
-      <c r="AA181" s="111"/>
+      <c r="Y181" s="100"/>
+      <c r="Z181" s="100"/>
+      <c r="AA181" s="100"/>
     </row>
     <row r="182" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="107"/>
+      <c r="A182" s="96"/>
       <c r="B182" s="90"/>
       <c r="C182" s="86"/>
       <c r="D182" s="66"/>
@@ -35726,12 +35726,12 @@
       <c r="V182" s="61"/>
       <c r="W182" s="31"/>
       <c r="X182" s="33"/>
-      <c r="Y182" s="111"/>
-      <c r="Z182" s="111"/>
-      <c r="AA182" s="111"/>
+      <c r="Y182" s="100"/>
+      <c r="Z182" s="100"/>
+      <c r="AA182" s="100"/>
     </row>
     <row r="183" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A183" s="107"/>
+      <c r="A183" s="96"/>
       <c r="B183" s="90"/>
       <c r="C183" s="86"/>
       <c r="D183" s="66"/>
@@ -35755,12 +35755,12 @@
       <c r="V183" s="61"/>
       <c r="W183" s="31"/>
       <c r="X183" s="33"/>
-      <c r="Y183" s="111"/>
-      <c r="Z183" s="111"/>
-      <c r="AA183" s="111"/>
+      <c r="Y183" s="100"/>
+      <c r="Z183" s="100"/>
+      <c r="AA183" s="100"/>
     </row>
     <row r="184" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="107"/>
+      <c r="A184" s="96"/>
       <c r="B184" s="90"/>
       <c r="C184" s="86"/>
       <c r="D184" s="66"/>
@@ -35784,12 +35784,12 @@
       <c r="V184" s="61"/>
       <c r="W184" s="31"/>
       <c r="X184" s="33"/>
-      <c r="Y184" s="111"/>
-      <c r="Z184" s="111"/>
-      <c r="AA184" s="111"/>
+      <c r="Y184" s="100"/>
+      <c r="Z184" s="100"/>
+      <c r="AA184" s="100"/>
     </row>
     <row r="185" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="107"/>
+      <c r="A185" s="96"/>
       <c r="B185" s="90"/>
       <c r="C185" s="91"/>
       <c r="D185" s="71"/>
@@ -35813,12 +35813,12 @@
       <c r="V185" s="61"/>
       <c r="W185" s="34"/>
       <c r="X185" s="33"/>
-      <c r="Y185" s="111"/>
-      <c r="Z185" s="111"/>
-      <c r="AA185" s="111"/>
+      <c r="Y185" s="100"/>
+      <c r="Z185" s="100"/>
+      <c r="AA185" s="100"/>
     </row>
     <row r="186" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A186" s="107"/>
+      <c r="A186" s="96"/>
       <c r="B186" s="90"/>
       <c r="C186" s="86"/>
       <c r="D186" s="66"/>
@@ -35842,12 +35842,12 @@
       <c r="V186" s="61"/>
       <c r="W186" s="33"/>
       <c r="X186" s="33"/>
-      <c r="Y186" s="111"/>
-      <c r="Z186" s="111"/>
-      <c r="AA186" s="111"/>
+      <c r="Y186" s="100"/>
+      <c r="Z186" s="100"/>
+      <c r="AA186" s="100"/>
     </row>
     <row r="187" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="107"/>
+      <c r="A187" s="96"/>
       <c r="B187" s="90"/>
       <c r="C187" s="86"/>
       <c r="D187" s="66"/>
@@ -35871,12 +35871,12 @@
       <c r="V187" s="61"/>
       <c r="W187" s="31"/>
       <c r="X187" s="33"/>
-      <c r="Y187" s="111"/>
-      <c r="Z187" s="111"/>
-      <c r="AA187" s="111"/>
+      <c r="Y187" s="100"/>
+      <c r="Z187" s="100"/>
+      <c r="AA187" s="100"/>
     </row>
     <row r="188" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A188" s="107"/>
+      <c r="A188" s="96"/>
       <c r="B188" s="90"/>
       <c r="C188" s="86"/>
       <c r="D188" s="66"/>
@@ -35900,12 +35900,12 @@
       <c r="V188" s="61"/>
       <c r="W188" s="31"/>
       <c r="X188" s="33"/>
-      <c r="Y188" s="111"/>
-      <c r="Z188" s="111"/>
-      <c r="AA188" s="111"/>
+      <c r="Y188" s="100"/>
+      <c r="Z188" s="100"/>
+      <c r="AA188" s="100"/>
     </row>
     <row r="189" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A189" s="107"/>
+      <c r="A189" s="96"/>
       <c r="B189" s="90"/>
       <c r="C189" s="86"/>
       <c r="D189" s="66"/>
@@ -35929,12 +35929,12 @@
       <c r="V189" s="61"/>
       <c r="W189" s="31"/>
       <c r="X189" s="33"/>
-      <c r="Y189" s="111"/>
-      <c r="Z189" s="111"/>
-      <c r="AA189" s="111"/>
+      <c r="Y189" s="100"/>
+      <c r="Z189" s="100"/>
+      <c r="AA189" s="100"/>
     </row>
     <row r="190" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="107"/>
+      <c r="A190" s="96"/>
       <c r="B190" s="90"/>
       <c r="C190" s="86"/>
       <c r="D190" s="66"/>
@@ -35958,12 +35958,12 @@
       <c r="V190" s="61"/>
       <c r="W190" s="31"/>
       <c r="X190" s="33"/>
-      <c r="Y190" s="111"/>
-      <c r="Z190" s="111"/>
-      <c r="AA190" s="111"/>
+      <c r="Y190" s="100"/>
+      <c r="Z190" s="100"/>
+      <c r="AA190" s="100"/>
     </row>
     <row r="191" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A191" s="107"/>
+      <c r="A191" s="96"/>
       <c r="B191" s="90"/>
       <c r="C191" s="86"/>
       <c r="D191" s="66"/>
@@ -35987,12 +35987,12 @@
       <c r="V191" s="61"/>
       <c r="W191" s="31"/>
       <c r="X191" s="33"/>
-      <c r="Y191" s="111"/>
-      <c r="Z191" s="111"/>
-      <c r="AA191" s="111"/>
+      <c r="Y191" s="100"/>
+      <c r="Z191" s="100"/>
+      <c r="AA191" s="100"/>
     </row>
     <row r="192" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A192" s="107"/>
+      <c r="A192" s="96"/>
       <c r="B192" s="90"/>
       <c r="C192" s="86"/>
       <c r="D192" s="66"/>
@@ -36016,12 +36016,12 @@
       <c r="V192" s="61"/>
       <c r="W192" s="31"/>
       <c r="X192" s="33"/>
-      <c r="Y192" s="111"/>
-      <c r="Z192" s="111"/>
-      <c r="AA192" s="111"/>
+      <c r="Y192" s="100"/>
+      <c r="Z192" s="100"/>
+      <c r="AA192" s="100"/>
     </row>
     <row r="193" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="107"/>
+      <c r="A193" s="96"/>
       <c r="B193" s="90"/>
       <c r="C193" s="91"/>
       <c r="D193" s="71"/>
@@ -36045,12 +36045,12 @@
       <c r="V193" s="61"/>
       <c r="W193" s="34"/>
       <c r="X193" s="33"/>
-      <c r="Y193" s="111"/>
-      <c r="Z193" s="111"/>
-      <c r="AA193" s="111"/>
+      <c r="Y193" s="100"/>
+      <c r="Z193" s="100"/>
+      <c r="AA193" s="100"/>
     </row>
     <row r="194" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A194" s="107"/>
+      <c r="A194" s="96"/>
       <c r="B194" s="90"/>
       <c r="C194" s="86"/>
       <c r="D194" s="66"/>
@@ -36074,12 +36074,12 @@
       <c r="V194" s="61"/>
       <c r="W194" s="33"/>
       <c r="X194" s="33"/>
-      <c r="Y194" s="111"/>
-      <c r="Z194" s="111"/>
-      <c r="AA194" s="111"/>
+      <c r="Y194" s="100"/>
+      <c r="Z194" s="100"/>
+      <c r="AA194" s="100"/>
     </row>
     <row r="195" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A195" s="107"/>
+      <c r="A195" s="96"/>
       <c r="B195" s="90"/>
       <c r="C195" s="86"/>
       <c r="D195" s="66"/>
@@ -36103,12 +36103,12 @@
       <c r="V195" s="61"/>
       <c r="W195" s="31"/>
       <c r="X195" s="33"/>
-      <c r="Y195" s="111"/>
-      <c r="Z195" s="111"/>
-      <c r="AA195" s="111"/>
+      <c r="Y195" s="100"/>
+      <c r="Z195" s="100"/>
+      <c r="AA195" s="100"/>
     </row>
     <row r="196" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="107"/>
+      <c r="A196" s="96"/>
       <c r="B196" s="90"/>
       <c r="C196" s="86"/>
       <c r="D196" s="66"/>
@@ -36132,12 +36132,12 @@
       <c r="V196" s="61"/>
       <c r="W196" s="31"/>
       <c r="X196" s="33"/>
-      <c r="Y196" s="111"/>
-      <c r="Z196" s="111"/>
-      <c r="AA196" s="111"/>
+      <c r="Y196" s="100"/>
+      <c r="Z196" s="100"/>
+      <c r="AA196" s="100"/>
     </row>
     <row r="197" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A197" s="107"/>
+      <c r="A197" s="96"/>
       <c r="B197" s="90"/>
       <c r="C197" s="86"/>
       <c r="D197" s="66"/>
@@ -36161,12 +36161,12 @@
       <c r="V197" s="61"/>
       <c r="W197" s="31"/>
       <c r="X197" s="33"/>
-      <c r="Y197" s="111"/>
-      <c r="Z197" s="111"/>
-      <c r="AA197" s="111"/>
+      <c r="Y197" s="100"/>
+      <c r="Z197" s="100"/>
+      <c r="AA197" s="100"/>
     </row>
     <row r="198" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A198" s="107"/>
+      <c r="A198" s="96"/>
       <c r="B198" s="90"/>
       <c r="C198" s="86"/>
       <c r="D198" s="66"/>
@@ -36190,12 +36190,12 @@
       <c r="V198" s="61"/>
       <c r="W198" s="31"/>
       <c r="X198" s="33"/>
-      <c r="Y198" s="111"/>
-      <c r="Z198" s="111"/>
-      <c r="AA198" s="111"/>
+      <c r="Y198" s="100"/>
+      <c r="Z198" s="100"/>
+      <c r="AA198" s="100"/>
     </row>
     <row r="199" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A199" s="107"/>
+      <c r="A199" s="96"/>
       <c r="B199" s="90"/>
       <c r="C199" s="91"/>
       <c r="D199" s="71"/>
@@ -36219,12 +36219,12 @@
       <c r="V199" s="61"/>
       <c r="W199" s="34"/>
       <c r="X199" s="33"/>
-      <c r="Y199" s="111"/>
-      <c r="Z199" s="111"/>
-      <c r="AA199" s="111"/>
+      <c r="Y199" s="100"/>
+      <c r="Z199" s="100"/>
+      <c r="AA199" s="100"/>
     </row>
     <row r="200" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A200" s="107"/>
+      <c r="A200" s="96"/>
       <c r="B200" s="90"/>
       <c r="C200" s="86"/>
       <c r="D200" s="66"/>
@@ -36248,12 +36248,12 @@
       <c r="V200" s="61"/>
       <c r="W200" s="33"/>
       <c r="X200" s="33"/>
-      <c r="Y200" s="111"/>
-      <c r="Z200" s="111"/>
-      <c r="AA200" s="111"/>
+      <c r="Y200" s="100"/>
+      <c r="Z200" s="100"/>
+      <c r="AA200" s="100"/>
     </row>
     <row r="201" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A201" s="107"/>
+      <c r="A201" s="96"/>
       <c r="B201" s="90"/>
       <c r="C201" s="86"/>
       <c r="D201" s="66"/>
@@ -36277,12 +36277,12 @@
       <c r="V201" s="61"/>
       <c r="W201" s="31"/>
       <c r="X201" s="33"/>
-      <c r="Y201" s="111"/>
-      <c r="Z201" s="111"/>
-      <c r="AA201" s="111"/>
+      <c r="Y201" s="100"/>
+      <c r="Z201" s="100"/>
+      <c r="AA201" s="100"/>
     </row>
     <row r="202" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A202" s="107"/>
+      <c r="A202" s="96"/>
       <c r="B202" s="90"/>
       <c r="C202" s="86"/>
       <c r="D202" s="66"/>
@@ -36306,12 +36306,12 @@
       <c r="V202" s="61"/>
       <c r="W202" s="31"/>
       <c r="X202" s="33"/>
-      <c r="Y202" s="111"/>
-      <c r="Z202" s="111"/>
-      <c r="AA202" s="111"/>
+      <c r="Y202" s="100"/>
+      <c r="Z202" s="100"/>
+      <c r="AA202" s="100"/>
     </row>
     <row r="203" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A203" s="107"/>
+      <c r="A203" s="96"/>
       <c r="B203" s="90"/>
       <c r="C203" s="86"/>
       <c r="D203" s="66"/>
@@ -36335,12 +36335,12 @@
       <c r="V203" s="61"/>
       <c r="W203" s="31"/>
       <c r="X203" s="33"/>
-      <c r="Y203" s="111"/>
-      <c r="Z203" s="111"/>
-      <c r="AA203" s="111"/>
+      <c r="Y203" s="100"/>
+      <c r="Z203" s="100"/>
+      <c r="AA203" s="100"/>
     </row>
     <row r="204" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A204" s="107"/>
+      <c r="A204" s="96"/>
       <c r="B204" s="90"/>
       <c r="C204" s="86"/>
       <c r="D204" s="66"/>
@@ -36364,12 +36364,12 @@
       <c r="V204" s="61"/>
       <c r="W204" s="31"/>
       <c r="X204" s="33"/>
-      <c r="Y204" s="111"/>
-      <c r="Z204" s="111"/>
-      <c r="AA204" s="111"/>
+      <c r="Y204" s="100"/>
+      <c r="Z204" s="100"/>
+      <c r="AA204" s="100"/>
     </row>
     <row r="205" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A205" s="107"/>
+      <c r="A205" s="96"/>
       <c r="B205" s="90"/>
       <c r="C205" s="86"/>
       <c r="D205" s="66"/>
@@ -36393,12 +36393,12 @@
       <c r="V205" s="61"/>
       <c r="W205" s="31"/>
       <c r="X205" s="33"/>
-      <c r="Y205" s="111"/>
-      <c r="Z205" s="111"/>
-      <c r="AA205" s="111"/>
+      <c r="Y205" s="100"/>
+      <c r="Z205" s="100"/>
+      <c r="AA205" s="100"/>
     </row>
     <row r="206" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A206" s="107"/>
+      <c r="A206" s="96"/>
       <c r="B206" s="90"/>
       <c r="C206" s="86"/>
       <c r="D206" s="66"/>
@@ -36422,12 +36422,12 @@
       <c r="V206" s="61"/>
       <c r="W206" s="31"/>
       <c r="X206" s="33"/>
-      <c r="Y206" s="111"/>
-      <c r="Z206" s="111"/>
-      <c r="AA206" s="111"/>
+      <c r="Y206" s="100"/>
+      <c r="Z206" s="100"/>
+      <c r="AA206" s="100"/>
     </row>
     <row r="207" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A207" s="107"/>
+      <c r="A207" s="96"/>
       <c r="B207" s="90"/>
       <c r="C207" s="91"/>
       <c r="D207" s="71"/>
@@ -36451,12 +36451,12 @@
       <c r="V207" s="61"/>
       <c r="W207" s="34"/>
       <c r="X207" s="33"/>
-      <c r="Y207" s="111"/>
-      <c r="Z207" s="111"/>
-      <c r="AA207" s="111"/>
+      <c r="Y207" s="100"/>
+      <c r="Z207" s="100"/>
+      <c r="AA207" s="100"/>
     </row>
     <row r="208" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A208" s="107"/>
+      <c r="A208" s="96"/>
       <c r="B208" s="90"/>
       <c r="C208" s="86"/>
       <c r="D208" s="66"/>
@@ -36480,12 +36480,12 @@
       <c r="V208" s="61"/>
       <c r="W208" s="33"/>
       <c r="X208" s="33"/>
-      <c r="Y208" s="111"/>
-      <c r="Z208" s="111"/>
-      <c r="AA208" s="111"/>
+      <c r="Y208" s="100"/>
+      <c r="Z208" s="100"/>
+      <c r="AA208" s="100"/>
     </row>
     <row r="209" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A209" s="107"/>
+      <c r="A209" s="96"/>
       <c r="B209" s="90"/>
       <c r="C209" s="86"/>
       <c r="D209" s="66"/>
@@ -36509,12 +36509,12 @@
       <c r="V209" s="61"/>
       <c r="W209" s="31"/>
       <c r="X209" s="33"/>
-      <c r="Y209" s="111"/>
-      <c r="Z209" s="111"/>
-      <c r="AA209" s="111"/>
+      <c r="Y209" s="100"/>
+      <c r="Z209" s="100"/>
+      <c r="AA209" s="100"/>
     </row>
     <row r="210" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A210" s="107"/>
+      <c r="A210" s="96"/>
       <c r="B210" s="90"/>
       <c r="C210" s="86"/>
       <c r="D210" s="66"/>
@@ -36538,12 +36538,12 @@
       <c r="V210" s="61"/>
       <c r="W210" s="31"/>
       <c r="X210" s="33"/>
-      <c r="Y210" s="111"/>
-      <c r="Z210" s="111"/>
-      <c r="AA210" s="111"/>
+      <c r="Y210" s="100"/>
+      <c r="Z210" s="100"/>
+      <c r="AA210" s="100"/>
     </row>
     <row r="211" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A211" s="107"/>
+      <c r="A211" s="96"/>
       <c r="B211" s="90"/>
       <c r="C211" s="86"/>
       <c r="D211" s="66"/>
@@ -36567,12 +36567,12 @@
       <c r="V211" s="61"/>
       <c r="W211" s="31"/>
       <c r="X211" s="33"/>
-      <c r="Y211" s="111"/>
-      <c r="Z211" s="111"/>
-      <c r="AA211" s="111"/>
+      <c r="Y211" s="100"/>
+      <c r="Z211" s="100"/>
+      <c r="AA211" s="100"/>
     </row>
     <row r="212" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A212" s="107"/>
+      <c r="A212" s="96"/>
       <c r="B212" s="90"/>
       <c r="C212" s="86"/>
       <c r="D212" s="66"/>
@@ -36596,12 +36596,12 @@
       <c r="V212" s="61"/>
       <c r="W212" s="31"/>
       <c r="X212" s="33"/>
-      <c r="Y212" s="111"/>
-      <c r="Z212" s="111"/>
-      <c r="AA212" s="111"/>
+      <c r="Y212" s="100"/>
+      <c r="Z212" s="100"/>
+      <c r="AA212" s="100"/>
     </row>
     <row r="213" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A213" s="107"/>
+      <c r="A213" s="96"/>
       <c r="B213" s="90"/>
       <c r="C213" s="91"/>
       <c r="D213" s="71"/>
@@ -36625,12 +36625,12 @@
       <c r="V213" s="61"/>
       <c r="W213" s="34"/>
       <c r="X213" s="33"/>
-      <c r="Y213" s="111"/>
-      <c r="Z213" s="111"/>
-      <c r="AA213" s="111"/>
+      <c r="Y213" s="100"/>
+      <c r="Z213" s="100"/>
+      <c r="AA213" s="100"/>
     </row>
     <row r="214" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A214" s="107"/>
+      <c r="A214" s="96"/>
       <c r="B214" s="90"/>
       <c r="C214" s="86"/>
       <c r="D214" s="66"/>
@@ -36654,12 +36654,12 @@
       <c r="V214" s="61"/>
       <c r="W214" s="33"/>
       <c r="X214" s="33"/>
-      <c r="Y214" s="111"/>
-      <c r="Z214" s="111"/>
-      <c r="AA214" s="111"/>
+      <c r="Y214" s="100"/>
+      <c r="Z214" s="100"/>
+      <c r="AA214" s="100"/>
     </row>
     <row r="215" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A215" s="107"/>
+      <c r="A215" s="96"/>
       <c r="B215" s="90"/>
       <c r="C215" s="86"/>
       <c r="D215" s="66"/>
@@ -36683,12 +36683,12 @@
       <c r="V215" s="61"/>
       <c r="W215" s="31"/>
       <c r="X215" s="33"/>
-      <c r="Y215" s="111"/>
-      <c r="Z215" s="111"/>
-      <c r="AA215" s="111"/>
+      <c r="Y215" s="100"/>
+      <c r="Z215" s="100"/>
+      <c r="AA215" s="100"/>
     </row>
     <row r="216" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A216" s="107"/>
+      <c r="A216" s="96"/>
       <c r="B216" s="90"/>
       <c r="C216" s="86"/>
       <c r="D216" s="66"/>
@@ -36712,12 +36712,12 @@
       <c r="V216" s="61"/>
       <c r="W216" s="31"/>
       <c r="X216" s="33"/>
-      <c r="Y216" s="111"/>
-      <c r="Z216" s="111"/>
-      <c r="AA216" s="111"/>
+      <c r="Y216" s="100"/>
+      <c r="Z216" s="100"/>
+      <c r="AA216" s="100"/>
     </row>
     <row r="217" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A217" s="107"/>
+      <c r="A217" s="96"/>
       <c r="B217" s="90"/>
       <c r="C217" s="86"/>
       <c r="D217" s="66"/>
@@ -36741,12 +36741,12 @@
       <c r="V217" s="61"/>
       <c r="W217" s="31"/>
       <c r="X217" s="33"/>
-      <c r="Y217" s="111"/>
-      <c r="Z217" s="111"/>
-      <c r="AA217" s="111"/>
+      <c r="Y217" s="100"/>
+      <c r="Z217" s="100"/>
+      <c r="AA217" s="100"/>
     </row>
     <row r="218" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A218" s="107"/>
+      <c r="A218" s="96"/>
       <c r="B218" s="90"/>
       <c r="C218" s="86"/>
       <c r="D218" s="66"/>
@@ -36770,12 +36770,12 @@
       <c r="V218" s="61"/>
       <c r="W218" s="31"/>
       <c r="X218" s="33"/>
-      <c r="Y218" s="111"/>
-      <c r="Z218" s="111"/>
-      <c r="AA218" s="111"/>
+      <c r="Y218" s="100"/>
+      <c r="Z218" s="100"/>
+      <c r="AA218" s="100"/>
     </row>
     <row r="219" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A219" s="107"/>
+      <c r="A219" s="96"/>
       <c r="B219" s="90"/>
       <c r="C219" s="86"/>
       <c r="D219" s="66"/>
@@ -36799,12 +36799,12 @@
       <c r="V219" s="61"/>
       <c r="W219" s="31"/>
       <c r="X219" s="33"/>
-      <c r="Y219" s="111"/>
-      <c r="Z219" s="111"/>
-      <c r="AA219" s="111"/>
+      <c r="Y219" s="100"/>
+      <c r="Z219" s="100"/>
+      <c r="AA219" s="100"/>
     </row>
     <row r="220" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A220" s="107"/>
+      <c r="A220" s="96"/>
       <c r="B220" s="90"/>
       <c r="C220" s="86"/>
       <c r="D220" s="66"/>
@@ -36828,12 +36828,12 @@
       <c r="V220" s="61"/>
       <c r="W220" s="31"/>
       <c r="X220" s="33"/>
-      <c r="Y220" s="111"/>
-      <c r="Z220" s="111"/>
-      <c r="AA220" s="111"/>
+      <c r="Y220" s="100"/>
+      <c r="Z220" s="100"/>
+      <c r="AA220" s="100"/>
     </row>
     <row r="221" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A221" s="107"/>
+      <c r="A221" s="96"/>
       <c r="B221" s="90"/>
       <c r="C221" s="91"/>
       <c r="D221" s="71"/>
@@ -36857,12 +36857,12 @@
       <c r="V221" s="61"/>
       <c r="W221" s="34"/>
       <c r="X221" s="33"/>
-      <c r="Y221" s="111"/>
-      <c r="Z221" s="111"/>
-      <c r="AA221" s="111"/>
+      <c r="Y221" s="100"/>
+      <c r="Z221" s="100"/>
+      <c r="AA221" s="100"/>
     </row>
     <row r="222" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A222" s="107"/>
+      <c r="A222" s="96"/>
       <c r="B222" s="90"/>
       <c r="C222" s="86"/>
       <c r="D222" s="66"/>
@@ -36886,12 +36886,12 @@
       <c r="V222" s="61"/>
       <c r="W222" s="33"/>
       <c r="X222" s="33"/>
-      <c r="Y222" s="111"/>
-      <c r="Z222" s="111"/>
-      <c r="AA222" s="111"/>
+      <c r="Y222" s="100"/>
+      <c r="Z222" s="100"/>
+      <c r="AA222" s="100"/>
     </row>
     <row r="223" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A223" s="107"/>
+      <c r="A223" s="96"/>
       <c r="B223" s="90"/>
       <c r="C223" s="86"/>
       <c r="D223" s="66"/>
@@ -36915,12 +36915,12 @@
       <c r="V223" s="61"/>
       <c r="W223" s="31"/>
       <c r="X223" s="33"/>
-      <c r="Y223" s="111"/>
-      <c r="Z223" s="111"/>
-      <c r="AA223" s="111"/>
+      <c r="Y223" s="100"/>
+      <c r="Z223" s="100"/>
+      <c r="AA223" s="100"/>
     </row>
     <row r="224" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A224" s="107"/>
+      <c r="A224" s="96"/>
       <c r="B224" s="90"/>
       <c r="C224" s="86"/>
       <c r="D224" s="66"/>
@@ -36944,12 +36944,12 @@
       <c r="V224" s="61"/>
       <c r="W224" s="31"/>
       <c r="X224" s="33"/>
-      <c r="Y224" s="111"/>
-      <c r="Z224" s="111"/>
-      <c r="AA224" s="111"/>
+      <c r="Y224" s="100"/>
+      <c r="Z224" s="100"/>
+      <c r="AA224" s="100"/>
     </row>
     <row r="225" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A225" s="107"/>
+      <c r="A225" s="96"/>
       <c r="B225" s="90"/>
       <c r="C225" s="86"/>
       <c r="D225" s="66"/>
@@ -36973,12 +36973,12 @@
       <c r="V225" s="61"/>
       <c r="W225" s="31"/>
       <c r="X225" s="33"/>
-      <c r="Y225" s="111"/>
-      <c r="Z225" s="111"/>
-      <c r="AA225" s="111"/>
+      <c r="Y225" s="100"/>
+      <c r="Z225" s="100"/>
+      <c r="AA225" s="100"/>
     </row>
     <row r="226" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A226" s="107"/>
+      <c r="A226" s="96"/>
       <c r="B226" s="90"/>
       <c r="C226" s="86"/>
       <c r="D226" s="66"/>
@@ -37002,12 +37002,12 @@
       <c r="V226" s="61"/>
       <c r="W226" s="31"/>
       <c r="X226" s="33"/>
-      <c r="Y226" s="111"/>
-      <c r="Z226" s="111"/>
-      <c r="AA226" s="111"/>
+      <c r="Y226" s="100"/>
+      <c r="Z226" s="100"/>
+      <c r="AA226" s="100"/>
     </row>
     <row r="227" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A227" s="107"/>
+      <c r="A227" s="96"/>
       <c r="B227" s="90"/>
       <c r="C227" s="91"/>
       <c r="D227" s="71"/>
@@ -37031,12 +37031,12 @@
       <c r="V227" s="61"/>
       <c r="W227" s="34"/>
       <c r="X227" s="33"/>
-      <c r="Y227" s="111"/>
-      <c r="Z227" s="111"/>
-      <c r="AA227" s="111"/>
+      <c r="Y227" s="100"/>
+      <c r="Z227" s="100"/>
+      <c r="AA227" s="100"/>
     </row>
     <row r="228" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A228" s="107"/>
+      <c r="A228" s="96"/>
       <c r="B228" s="90"/>
       <c r="C228" s="86"/>
       <c r="D228" s="66"/>
@@ -37060,12 +37060,12 @@
       <c r="V228" s="61"/>
       <c r="W228" s="33"/>
       <c r="X228" s="33"/>
-      <c r="Y228" s="111"/>
-      <c r="Z228" s="111"/>
-      <c r="AA228" s="111"/>
+      <c r="Y228" s="100"/>
+      <c r="Z228" s="100"/>
+      <c r="AA228" s="100"/>
     </row>
     <row r="229" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A229" s="107"/>
+      <c r="A229" s="96"/>
       <c r="B229" s="90"/>
       <c r="C229" s="86"/>
       <c r="D229" s="66"/>
@@ -37089,12 +37089,12 @@
       <c r="V229" s="61"/>
       <c r="W229" s="31"/>
       <c r="X229" s="33"/>
-      <c r="Y229" s="111"/>
-      <c r="Z229" s="111"/>
-      <c r="AA229" s="111"/>
+      <c r="Y229" s="100"/>
+      <c r="Z229" s="100"/>
+      <c r="AA229" s="100"/>
     </row>
     <row r="230" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A230" s="107"/>
+      <c r="A230" s="96"/>
       <c r="B230" s="90"/>
       <c r="C230" s="86"/>
       <c r="D230" s="66"/>
@@ -37118,12 +37118,12 @@
       <c r="V230" s="61"/>
       <c r="W230" s="31"/>
       <c r="X230" s="33"/>
-      <c r="Y230" s="111"/>
-      <c r="Z230" s="111"/>
-      <c r="AA230" s="111"/>
+      <c r="Y230" s="100"/>
+      <c r="Z230" s="100"/>
+      <c r="AA230" s="100"/>
     </row>
     <row r="231" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A231" s="107"/>
+      <c r="A231" s="96"/>
       <c r="B231" s="90"/>
       <c r="C231" s="86"/>
       <c r="D231" s="66"/>
@@ -37147,12 +37147,12 @@
       <c r="V231" s="61"/>
       <c r="W231" s="31"/>
       <c r="X231" s="33"/>
-      <c r="Y231" s="111"/>
-      <c r="Z231" s="111"/>
-      <c r="AA231" s="111"/>
+      <c r="Y231" s="100"/>
+      <c r="Z231" s="100"/>
+      <c r="AA231" s="100"/>
     </row>
     <row r="232" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A232" s="107"/>
+      <c r="A232" s="96"/>
       <c r="B232" s="90"/>
       <c r="C232" s="86"/>
       <c r="D232" s="66"/>
@@ -37176,12 +37176,12 @@
       <c r="V232" s="61"/>
       <c r="W232" s="31"/>
       <c r="X232" s="33"/>
-      <c r="Y232" s="111"/>
-      <c r="Z232" s="111"/>
-      <c r="AA232" s="111"/>
+      <c r="Y232" s="100"/>
+      <c r="Z232" s="100"/>
+      <c r="AA232" s="100"/>
     </row>
     <row r="233" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A233" s="107"/>
+      <c r="A233" s="96"/>
       <c r="B233" s="90"/>
       <c r="C233" s="86"/>
       <c r="D233" s="66"/>
@@ -37205,12 +37205,12 @@
       <c r="V233" s="61"/>
       <c r="W233" s="31"/>
       <c r="X233" s="33"/>
-      <c r="Y233" s="111"/>
-      <c r="Z233" s="111"/>
-      <c r="AA233" s="111"/>
+      <c r="Y233" s="100"/>
+      <c r="Z233" s="100"/>
+      <c r="AA233" s="100"/>
     </row>
     <row r="234" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A234" s="107"/>
+      <c r="A234" s="96"/>
       <c r="B234" s="90"/>
       <c r="C234" s="86"/>
       <c r="D234" s="66"/>
@@ -37234,12 +37234,12 @@
       <c r="V234" s="61"/>
       <c r="W234" s="31"/>
       <c r="X234" s="33"/>
-      <c r="Y234" s="111"/>
-      <c r="Z234" s="111"/>
-      <c r="AA234" s="111"/>
+      <c r="Y234" s="100"/>
+      <c r="Z234" s="100"/>
+      <c r="AA234" s="100"/>
     </row>
     <row r="235" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A235" s="107"/>
+      <c r="A235" s="96"/>
       <c r="B235" s="90"/>
       <c r="C235" s="91"/>
       <c r="D235" s="71"/>
@@ -37263,12 +37263,12 @@
       <c r="V235" s="61"/>
       <c r="W235" s="34"/>
       <c r="X235" s="33"/>
-      <c r="Y235" s="111"/>
-      <c r="Z235" s="111"/>
-      <c r="AA235" s="111"/>
+      <c r="Y235" s="100"/>
+      <c r="Z235" s="100"/>
+      <c r="AA235" s="100"/>
     </row>
     <row r="236" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A236" s="107"/>
+      <c r="A236" s="96"/>
       <c r="B236" s="90"/>
       <c r="C236" s="86"/>
       <c r="D236" s="66"/>
@@ -37292,12 +37292,12 @@
       <c r="V236" s="61"/>
       <c r="W236" s="33"/>
       <c r="X236" s="33"/>
-      <c r="Y236" s="111"/>
-      <c r="Z236" s="111"/>
-      <c r="AA236" s="111"/>
+      <c r="Y236" s="100"/>
+      <c r="Z236" s="100"/>
+      <c r="AA236" s="100"/>
     </row>
     <row r="237" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A237" s="107"/>
+      <c r="A237" s="96"/>
       <c r="B237" s="90"/>
       <c r="C237" s="86"/>
       <c r="D237" s="66"/>
@@ -37321,12 +37321,12 @@
       <c r="V237" s="61"/>
       <c r="W237" s="31"/>
       <c r="X237" s="33"/>
-      <c r="Y237" s="111"/>
-      <c r="Z237" s="111"/>
-      <c r="AA237" s="111"/>
+      <c r="Y237" s="100"/>
+      <c r="Z237" s="100"/>
+      <c r="AA237" s="100"/>
     </row>
     <row r="238" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A238" s="107"/>
+      <c r="A238" s="96"/>
       <c r="B238" s="90"/>
       <c r="C238" s="86"/>
       <c r="D238" s="66"/>
@@ -37350,12 +37350,12 @@
       <c r="V238" s="61"/>
       <c r="W238" s="31"/>
       <c r="X238" s="33"/>
-      <c r="Y238" s="111"/>
-      <c r="Z238" s="111"/>
-      <c r="AA238" s="111"/>
+      <c r="Y238" s="100"/>
+      <c r="Z238" s="100"/>
+      <c r="AA238" s="100"/>
     </row>
     <row r="239" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A239" s="107"/>
+      <c r="A239" s="96"/>
       <c r="B239" s="90"/>
       <c r="C239" s="86"/>
       <c r="D239" s="66"/>
@@ -37379,12 +37379,12 @@
       <c r="V239" s="61"/>
       <c r="W239" s="31"/>
       <c r="X239" s="33"/>
-      <c r="Y239" s="111"/>
-      <c r="Z239" s="111"/>
-      <c r="AA239" s="111"/>
+      <c r="Y239" s="100"/>
+      <c r="Z239" s="100"/>
+      <c r="AA239" s="100"/>
     </row>
     <row r="240" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A240" s="107"/>
+      <c r="A240" s="96"/>
       <c r="B240" s="90"/>
       <c r="C240" s="86"/>
       <c r="D240" s="66"/>
@@ -37408,12 +37408,12 @@
       <c r="V240" s="61"/>
       <c r="W240" s="31"/>
       <c r="X240" s="33"/>
-      <c r="Y240" s="111"/>
-      <c r="Z240" s="111"/>
-      <c r="AA240" s="111"/>
+      <c r="Y240" s="100"/>
+      <c r="Z240" s="100"/>
+      <c r="AA240" s="100"/>
     </row>
     <row r="241" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A241" s="107"/>
+      <c r="A241" s="96"/>
       <c r="B241" s="90"/>
       <c r="C241" s="91"/>
       <c r="D241" s="71"/>
@@ -37437,12 +37437,12 @@
       <c r="V241" s="61"/>
       <c r="W241" s="34"/>
       <c r="X241" s="33"/>
-      <c r="Y241" s="111"/>
-      <c r="Z241" s="111"/>
-      <c r="AA241" s="111"/>
+      <c r="Y241" s="100"/>
+      <c r="Z241" s="100"/>
+      <c r="AA241" s="100"/>
     </row>
     <row r="242" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A242" s="107"/>
+      <c r="A242" s="96"/>
       <c r="B242" s="90"/>
       <c r="C242" s="86"/>
       <c r="D242" s="66"/>
@@ -37466,12 +37466,12 @@
       <c r="V242" s="61"/>
       <c r="W242" s="33"/>
       <c r="X242" s="33"/>
-      <c r="Y242" s="111"/>
-      <c r="Z242" s="111"/>
-      <c r="AA242" s="111"/>
+      <c r="Y242" s="100"/>
+      <c r="Z242" s="100"/>
+      <c r="AA242" s="100"/>
     </row>
     <row r="243" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A243" s="107"/>
+      <c r="A243" s="96"/>
       <c r="B243" s="90"/>
       <c r="C243" s="86"/>
       <c r="D243" s="66"/>
@@ -37495,12 +37495,12 @@
       <c r="V243" s="61"/>
       <c r="W243" s="31"/>
       <c r="X243" s="33"/>
-      <c r="Y243" s="111"/>
-      <c r="Z243" s="111"/>
-      <c r="AA243" s="111"/>
+      <c r="Y243" s="100"/>
+      <c r="Z243" s="100"/>
+      <c r="AA243" s="100"/>
     </row>
     <row r="244" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A244" s="107"/>
+      <c r="A244" s="96"/>
       <c r="B244" s="90"/>
       <c r="C244" s="86"/>
       <c r="D244" s="66"/>
@@ -37524,12 +37524,12 @@
       <c r="V244" s="61"/>
       <c r="W244" s="31"/>
       <c r="X244" s="33"/>
-      <c r="Y244" s="111"/>
-      <c r="Z244" s="111"/>
-      <c r="AA244" s="111"/>
+      <c r="Y244" s="100"/>
+      <c r="Z244" s="100"/>
+      <c r="AA244" s="100"/>
     </row>
     <row r="245" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A245" s="107"/>
+      <c r="A245" s="96"/>
       <c r="B245" s="90"/>
       <c r="C245" s="86"/>
       <c r="D245" s="66"/>
@@ -37553,12 +37553,12 @@
       <c r="V245" s="61"/>
       <c r="W245" s="31"/>
       <c r="X245" s="33"/>
-      <c r="Y245" s="111"/>
-      <c r="Z245" s="111"/>
-      <c r="AA245" s="111"/>
+      <c r="Y245" s="100"/>
+      <c r="Z245" s="100"/>
+      <c r="AA245" s="100"/>
     </row>
     <row r="246" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A246" s="107"/>
+      <c r="A246" s="96"/>
       <c r="B246" s="90"/>
       <c r="C246" s="86"/>
       <c r="D246" s="66"/>
@@ -37582,12 +37582,12 @@
       <c r="V246" s="61"/>
       <c r="W246" s="31"/>
       <c r="X246" s="33"/>
-      <c r="Y246" s="111"/>
-      <c r="Z246" s="111"/>
-      <c r="AA246" s="111"/>
+      <c r="Y246" s="100"/>
+      <c r="Z246" s="100"/>
+      <c r="AA246" s="100"/>
     </row>
     <row r="247" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A247" s="107"/>
+      <c r="A247" s="96"/>
       <c r="B247" s="90"/>
       <c r="C247" s="86"/>
       <c r="D247" s="66"/>
@@ -37611,12 +37611,12 @@
       <c r="V247" s="61"/>
       <c r="W247" s="31"/>
       <c r="X247" s="33"/>
-      <c r="Y247" s="111"/>
-      <c r="Z247" s="111"/>
-      <c r="AA247" s="111"/>
+      <c r="Y247" s="100"/>
+      <c r="Z247" s="100"/>
+      <c r="AA247" s="100"/>
     </row>
     <row r="248" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A248" s="107"/>
+      <c r="A248" s="96"/>
       <c r="B248" s="90"/>
       <c r="C248" s="86"/>
       <c r="D248" s="66"/>
@@ -37640,12 +37640,12 @@
       <c r="V248" s="61"/>
       <c r="W248" s="31"/>
       <c r="X248" s="33"/>
-      <c r="Y248" s="111"/>
-      <c r="Z248" s="111"/>
-      <c r="AA248" s="111"/>
+      <c r="Y248" s="100"/>
+      <c r="Z248" s="100"/>
+      <c r="AA248" s="100"/>
     </row>
     <row r="249" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A249" s="107"/>
+      <c r="A249" s="96"/>
       <c r="B249" s="90"/>
       <c r="C249" s="91"/>
       <c r="D249" s="71"/>
@@ -37669,12 +37669,12 @@
       <c r="V249" s="61"/>
       <c r="W249" s="34"/>
       <c r="X249" s="33"/>
-      <c r="Y249" s="111"/>
-      <c r="Z249" s="111"/>
-      <c r="AA249" s="111"/>
+      <c r="Y249" s="100"/>
+      <c r="Z249" s="100"/>
+      <c r="AA249" s="100"/>
     </row>
     <row r="250" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A250" s="107"/>
+      <c r="A250" s="96"/>
       <c r="B250" s="90"/>
       <c r="C250" s="86"/>
       <c r="D250" s="66"/>
@@ -37698,12 +37698,12 @@
       <c r="V250" s="61"/>
       <c r="W250" s="33"/>
       <c r="X250" s="33"/>
-      <c r="Y250" s="111"/>
-      <c r="Z250" s="111"/>
-      <c r="AA250" s="111"/>
+      <c r="Y250" s="100"/>
+      <c r="Z250" s="100"/>
+      <c r="AA250" s="100"/>
     </row>
     <row r="251" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A251" s="107"/>
+      <c r="A251" s="96"/>
       <c r="B251" s="90"/>
       <c r="C251" s="86"/>
       <c r="D251" s="66"/>
@@ -37727,12 +37727,12 @@
       <c r="V251" s="61"/>
       <c r="W251" s="31"/>
       <c r="X251" s="33"/>
-      <c r="Y251" s="111"/>
-      <c r="Z251" s="111"/>
-      <c r="AA251" s="111"/>
+      <c r="Y251" s="100"/>
+      <c r="Z251" s="100"/>
+      <c r="AA251" s="100"/>
     </row>
     <row r="252" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A252" s="107"/>
+      <c r="A252" s="96"/>
       <c r="B252" s="90"/>
       <c r="C252" s="86"/>
       <c r="D252" s="66"/>
@@ -37756,12 +37756,12 @@
       <c r="V252" s="61"/>
       <c r="W252" s="31"/>
       <c r="X252" s="33"/>
-      <c r="Y252" s="111"/>
-      <c r="Z252" s="111"/>
-      <c r="AA252" s="111"/>
+      <c r="Y252" s="100"/>
+      <c r="Z252" s="100"/>
+      <c r="AA252" s="100"/>
     </row>
     <row r="253" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A253" s="107"/>
+      <c r="A253" s="96"/>
       <c r="B253" s="90"/>
       <c r="C253" s="86"/>
       <c r="D253" s="66"/>
@@ -37785,12 +37785,12 @@
       <c r="V253" s="61"/>
       <c r="W253" s="31"/>
       <c r="X253" s="33"/>
-      <c r="Y253" s="111"/>
-      <c r="Z253" s="111"/>
-      <c r="AA253" s="111"/>
+      <c r="Y253" s="100"/>
+      <c r="Z253" s="100"/>
+      <c r="AA253" s="100"/>
     </row>
     <row r="254" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="107"/>
+      <c r="A254" s="96"/>
       <c r="B254" s="90"/>
       <c r="C254" s="86"/>
       <c r="D254" s="66"/>
@@ -37814,12 +37814,12 @@
       <c r="V254" s="61"/>
       <c r="W254" s="31"/>
       <c r="X254" s="33"/>
-      <c r="Y254" s="111"/>
-      <c r="Z254" s="111"/>
-      <c r="AA254" s="111"/>
+      <c r="Y254" s="100"/>
+      <c r="Z254" s="100"/>
+      <c r="AA254" s="100"/>
     </row>
     <row r="255" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A255" s="107"/>
+      <c r="A255" s="96"/>
       <c r="B255" s="90"/>
       <c r="C255" s="91"/>
       <c r="D255" s="71"/>
@@ -37843,12 +37843,12 @@
       <c r="V255" s="61"/>
       <c r="W255" s="34"/>
       <c r="X255" s="33"/>
-      <c r="Y255" s="111"/>
-      <c r="Z255" s="111"/>
-      <c r="AA255" s="111"/>
+      <c r="Y255" s="100"/>
+      <c r="Z255" s="100"/>
+      <c r="AA255" s="100"/>
     </row>
     <row r="256" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A256" s="107"/>
+      <c r="A256" s="96"/>
       <c r="B256" s="90"/>
       <c r="C256" s="86"/>
       <c r="D256" s="66"/>
@@ -37872,12 +37872,12 @@
       <c r="V256" s="61"/>
       <c r="W256" s="33"/>
       <c r="X256" s="33"/>
-      <c r="Y256" s="111"/>
-      <c r="Z256" s="111"/>
-      <c r="AA256" s="111"/>
+      <c r="Y256" s="100"/>
+      <c r="Z256" s="100"/>
+      <c r="AA256" s="100"/>
     </row>
     <row r="257" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A257" s="107"/>
+      <c r="A257" s="96"/>
       <c r="B257" s="90"/>
       <c r="C257" s="86"/>
       <c r="D257" s="66"/>
@@ -37901,12 +37901,12 @@
       <c r="V257" s="61"/>
       <c r="W257" s="31"/>
       <c r="X257" s="33"/>
-      <c r="Y257" s="111"/>
-      <c r="Z257" s="111"/>
-      <c r="AA257" s="111"/>
+      <c r="Y257" s="100"/>
+      <c r="Z257" s="100"/>
+      <c r="AA257" s="100"/>
     </row>
     <row r="258" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A258" s="107"/>
+      <c r="A258" s="96"/>
       <c r="B258" s="90"/>
       <c r="C258" s="86"/>
       <c r="D258" s="66"/>
@@ -37930,12 +37930,12 @@
       <c r="V258" s="61"/>
       <c r="W258" s="31"/>
       <c r="X258" s="33"/>
-      <c r="Y258" s="111"/>
-      <c r="Z258" s="111"/>
-      <c r="AA258" s="111"/>
+      <c r="Y258" s="100"/>
+      <c r="Z258" s="100"/>
+      <c r="AA258" s="100"/>
     </row>
     <row r="259" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A259" s="107"/>
+      <c r="A259" s="96"/>
       <c r="B259" s="90"/>
       <c r="C259" s="86"/>
       <c r="D259" s="66"/>
@@ -37959,12 +37959,12 @@
       <c r="V259" s="61"/>
       <c r="W259" s="31"/>
       <c r="X259" s="33"/>
-      <c r="Y259" s="111"/>
-      <c r="Z259" s="111"/>
-      <c r="AA259" s="111"/>
+      <c r="Y259" s="100"/>
+      <c r="Z259" s="100"/>
+      <c r="AA259" s="100"/>
     </row>
     <row r="260" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A260" s="107"/>
+      <c r="A260" s="96"/>
       <c r="B260" s="90"/>
       <c r="C260" s="86"/>
       <c r="D260" s="66"/>
@@ -37988,12 +37988,12 @@
       <c r="V260" s="61"/>
       <c r="W260" s="31"/>
       <c r="X260" s="33"/>
-      <c r="Y260" s="111"/>
-      <c r="Z260" s="111"/>
-      <c r="AA260" s="111"/>
+      <c r="Y260" s="100"/>
+      <c r="Z260" s="100"/>
+      <c r="AA260" s="100"/>
     </row>
     <row r="261" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A261" s="107"/>
+      <c r="A261" s="96"/>
       <c r="B261" s="90"/>
       <c r="C261" s="86"/>
       <c r="D261" s="66"/>
@@ -38017,12 +38017,12 @@
       <c r="V261" s="61"/>
       <c r="W261" s="31"/>
       <c r="X261" s="33"/>
-      <c r="Y261" s="111"/>
-      <c r="Z261" s="111"/>
-      <c r="AA261" s="111"/>
+      <c r="Y261" s="100"/>
+      <c r="Z261" s="100"/>
+      <c r="AA261" s="100"/>
     </row>
     <row r="262" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A262" s="107"/>
+      <c r="A262" s="96"/>
       <c r="B262" s="90"/>
       <c r="C262" s="86"/>
       <c r="D262" s="66"/>
@@ -38046,12 +38046,12 @@
       <c r="V262" s="61"/>
       <c r="W262" s="31"/>
       <c r="X262" s="33"/>
-      <c r="Y262" s="111"/>
-      <c r="Z262" s="111"/>
-      <c r="AA262" s="111"/>
+      <c r="Y262" s="100"/>
+      <c r="Z262" s="100"/>
+      <c r="AA262" s="100"/>
     </row>
     <row r="263" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A263" s="107"/>
+      <c r="A263" s="96"/>
       <c r="B263" s="90"/>
       <c r="C263" s="91"/>
       <c r="D263" s="71"/>
@@ -38075,12 +38075,12 @@
       <c r="V263" s="61"/>
       <c r="W263" s="34"/>
       <c r="X263" s="33"/>
-      <c r="Y263" s="111"/>
-      <c r="Z263" s="111"/>
-      <c r="AA263" s="111"/>
+      <c r="Y263" s="100"/>
+      <c r="Z263" s="100"/>
+      <c r="AA263" s="100"/>
     </row>
     <row r="264" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A264" s="107"/>
+      <c r="A264" s="96"/>
       <c r="B264" s="90"/>
       <c r="C264" s="86"/>
       <c r="D264" s="66"/>
@@ -38104,12 +38104,12 @@
       <c r="V264" s="61"/>
       <c r="W264" s="33"/>
       <c r="X264" s="33"/>
-      <c r="Y264" s="111"/>
-      <c r="Z264" s="111"/>
-      <c r="AA264" s="111"/>
+      <c r="Y264" s="100"/>
+      <c r="Z264" s="100"/>
+      <c r="AA264" s="100"/>
     </row>
     <row r="265" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A265" s="107"/>
+      <c r="A265" s="96"/>
       <c r="B265" s="90"/>
       <c r="C265" s="86"/>
       <c r="D265" s="66"/>
@@ -38133,12 +38133,12 @@
       <c r="V265" s="61"/>
       <c r="W265" s="31"/>
       <c r="X265" s="33"/>
-      <c r="Y265" s="111"/>
-      <c r="Z265" s="111"/>
-      <c r="AA265" s="111"/>
+      <c r="Y265" s="100"/>
+      <c r="Z265" s="100"/>
+      <c r="AA265" s="100"/>
     </row>
     <row r="266" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A266" s="107"/>
+      <c r="A266" s="96"/>
       <c r="B266" s="90"/>
       <c r="C266" s="86"/>
       <c r="D266" s="66"/>
@@ -38162,12 +38162,12 @@
       <c r="V266" s="61"/>
       <c r="W266" s="31"/>
       <c r="X266" s="33"/>
-      <c r="Y266" s="111"/>
-      <c r="Z266" s="111"/>
-      <c r="AA266" s="111"/>
+      <c r="Y266" s="100"/>
+      <c r="Z266" s="100"/>
+      <c r="AA266" s="100"/>
     </row>
     <row r="267" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A267" s="107"/>
+      <c r="A267" s="96"/>
       <c r="B267" s="90"/>
       <c r="C267" s="86"/>
       <c r="D267" s="66"/>
@@ -38191,12 +38191,12 @@
       <c r="V267" s="61"/>
       <c r="W267" s="31"/>
       <c r="X267" s="33"/>
-      <c r="Y267" s="111"/>
-      <c r="Z267" s="111"/>
-      <c r="AA267" s="111"/>
+      <c r="Y267" s="100"/>
+      <c r="Z267" s="100"/>
+      <c r="AA267" s="100"/>
     </row>
     <row r="268" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A268" s="107"/>
+      <c r="A268" s="96"/>
       <c r="B268" s="90"/>
       <c r="C268" s="86"/>
       <c r="D268" s="66"/>
@@ -38220,12 +38220,12 @@
       <c r="V268" s="61"/>
       <c r="W268" s="31"/>
       <c r="X268" s="33"/>
-      <c r="Y268" s="111"/>
-      <c r="Z268" s="111"/>
-      <c r="AA268" s="111"/>
+      <c r="Y268" s="100"/>
+      <c r="Z268" s="100"/>
+      <c r="AA268" s="100"/>
     </row>
     <row r="269" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A269" s="107"/>
+      <c r="A269" s="96"/>
       <c r="B269" s="90"/>
       <c r="C269" s="91"/>
       <c r="D269" s="71"/>
@@ -38249,12 +38249,12 @@
       <c r="V269" s="61"/>
       <c r="W269" s="34"/>
       <c r="X269" s="33"/>
-      <c r="Y269" s="111"/>
-      <c r="Z269" s="111"/>
-      <c r="AA269" s="111"/>
+      <c r="Y269" s="100"/>
+      <c r="Z269" s="100"/>
+      <c r="AA269" s="100"/>
     </row>
     <row r="270" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A270" s="107"/>
+      <c r="A270" s="96"/>
       <c r="B270" s="90"/>
       <c r="C270" s="86"/>
       <c r="D270" s="66"/>
@@ -38278,12 +38278,12 @@
       <c r="V270" s="61"/>
       <c r="W270" s="33"/>
       <c r="X270" s="33"/>
-      <c r="Y270" s="111"/>
-      <c r="Z270" s="111"/>
-      <c r="AA270" s="111"/>
+      <c r="Y270" s="100"/>
+      <c r="Z270" s="100"/>
+      <c r="AA270" s="100"/>
     </row>
     <row r="271" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A271" s="107"/>
+      <c r="A271" s="96"/>
       <c r="B271" s="90"/>
       <c r="C271" s="86"/>
       <c r="D271" s="66"/>
@@ -38307,12 +38307,12 @@
       <c r="V271" s="61"/>
       <c r="W271" s="31"/>
       <c r="X271" s="33"/>
-      <c r="Y271" s="111"/>
-      <c r="Z271" s="111"/>
-      <c r="AA271" s="111"/>
+      <c r="Y271" s="100"/>
+      <c r="Z271" s="100"/>
+      <c r="AA271" s="100"/>
     </row>
     <row r="272" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A272" s="107"/>
+      <c r="A272" s="96"/>
       <c r="B272" s="90"/>
       <c r="C272" s="86"/>
       <c r="D272" s="66"/>
@@ -38336,12 +38336,12 @@
       <c r="V272" s="61"/>
       <c r="W272" s="31"/>
       <c r="X272" s="33"/>
-      <c r="Y272" s="111"/>
-      <c r="Z272" s="111"/>
-      <c r="AA272" s="111"/>
+      <c r="Y272" s="100"/>
+      <c r="Z272" s="100"/>
+      <c r="AA272" s="100"/>
     </row>
     <row r="273" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="107"/>
+      <c r="A273" s="96"/>
       <c r="B273" s="90"/>
       <c r="C273" s="86"/>
       <c r="D273" s="66"/>
@@ -38365,12 +38365,12 @@
       <c r="V273" s="61"/>
       <c r="W273" s="31"/>
       <c r="X273" s="33"/>
-      <c r="Y273" s="111"/>
-      <c r="Z273" s="111"/>
-      <c r="AA273" s="111"/>
+      <c r="Y273" s="100"/>
+      <c r="Z273" s="100"/>
+      <c r="AA273" s="100"/>
     </row>
     <row r="274" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A274" s="107"/>
+      <c r="A274" s="96"/>
       <c r="B274" s="90"/>
       <c r="C274" s="86"/>
       <c r="D274" s="66"/>
@@ -38394,12 +38394,12 @@
       <c r="V274" s="61"/>
       <c r="W274" s="31"/>
       <c r="X274" s="33"/>
-      <c r="Y274" s="111"/>
-      <c r="Z274" s="111"/>
-      <c r="AA274" s="111"/>
+      <c r="Y274" s="100"/>
+      <c r="Z274" s="100"/>
+      <c r="AA274" s="100"/>
     </row>
     <row r="275" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A275" s="107"/>
+      <c r="A275" s="96"/>
       <c r="B275" s="90"/>
       <c r="C275" s="86"/>
       <c r="D275" s="66"/>
@@ -38423,12 +38423,12 @@
       <c r="V275" s="61"/>
       <c r="W275" s="31"/>
       <c r="X275" s="33"/>
-      <c r="Y275" s="111"/>
-      <c r="Z275" s="111"/>
-      <c r="AA275" s="111"/>
+      <c r="Y275" s="100"/>
+      <c r="Z275" s="100"/>
+      <c r="AA275" s="100"/>
     </row>
     <row r="276" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A276" s="107"/>
+      <c r="A276" s="96"/>
       <c r="B276" s="90"/>
       <c r="C276" s="86"/>
       <c r="D276" s="66"/>
@@ -38452,12 +38452,12 @@
       <c r="V276" s="61"/>
       <c r="W276" s="31"/>
       <c r="X276" s="33"/>
-      <c r="Y276" s="111"/>
-      <c r="Z276" s="111"/>
-      <c r="AA276" s="111"/>
+      <c r="Y276" s="100"/>
+      <c r="Z276" s="100"/>
+      <c r="AA276" s="100"/>
     </row>
     <row r="277" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A277" s="107"/>
+      <c r="A277" s="96"/>
       <c r="B277" s="90"/>
       <c r="C277" s="91"/>
       <c r="D277" s="71"/>
@@ -38481,12 +38481,12 @@
       <c r="V277" s="61"/>
       <c r="W277" s="34"/>
       <c r="X277" s="33"/>
-      <c r="Y277" s="111"/>
-      <c r="Z277" s="111"/>
-      <c r="AA277" s="111"/>
+      <c r="Y277" s="100"/>
+      <c r="Z277" s="100"/>
+      <c r="AA277" s="100"/>
     </row>
     <row r="278" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A278" s="107"/>
+      <c r="A278" s="96"/>
       <c r="B278" s="90"/>
       <c r="C278" s="86"/>
       <c r="D278" s="66"/>
@@ -38510,12 +38510,12 @@
       <c r="V278" s="61"/>
       <c r="W278" s="33"/>
       <c r="X278" s="33"/>
-      <c r="Y278" s="111"/>
-      <c r="Z278" s="111"/>
-      <c r="AA278" s="111"/>
+      <c r="Y278" s="100"/>
+      <c r="Z278" s="100"/>
+      <c r="AA278" s="100"/>
     </row>
     <row r="279" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A279" s="107"/>
+      <c r="A279" s="96"/>
       <c r="B279" s="90"/>
       <c r="C279" s="86"/>
       <c r="D279" s="66"/>
@@ -38539,12 +38539,12 @@
       <c r="V279" s="61"/>
       <c r="W279" s="31"/>
       <c r="X279" s="33"/>
-      <c r="Y279" s="111"/>
-      <c r="Z279" s="111"/>
-      <c r="AA279" s="111"/>
+      <c r="Y279" s="100"/>
+      <c r="Z279" s="100"/>
+      <c r="AA279" s="100"/>
     </row>
     <row r="280" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A280" s="107"/>
+      <c r="A280" s="96"/>
       <c r="B280" s="90"/>
       <c r="C280" s="86"/>
       <c r="D280" s="66"/>
@@ -38568,12 +38568,12 @@
       <c r="V280" s="61"/>
       <c r="W280" s="31"/>
       <c r="X280" s="33"/>
-      <c r="Y280" s="111"/>
-      <c r="Z280" s="111"/>
-      <c r="AA280" s="111"/>
+      <c r="Y280" s="100"/>
+      <c r="Z280" s="100"/>
+      <c r="AA280" s="100"/>
     </row>
     <row r="281" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A281" s="107"/>
+      <c r="A281" s="96"/>
       <c r="B281" s="90"/>
       <c r="C281" s="86"/>
       <c r="D281" s="66"/>
@@ -38597,12 +38597,12 @@
       <c r="V281" s="61"/>
       <c r="W281" s="31"/>
       <c r="X281" s="33"/>
-      <c r="Y281" s="111"/>
-      <c r="Z281" s="111"/>
-      <c r="AA281" s="111"/>
+      <c r="Y281" s="100"/>
+      <c r="Z281" s="100"/>
+      <c r="AA281" s="100"/>
     </row>
     <row r="282" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A282" s="107"/>
+      <c r="A282" s="96"/>
       <c r="B282" s="90"/>
       <c r="C282" s="86"/>
       <c r="D282" s="66"/>
@@ -38626,12 +38626,12 @@
       <c r="V282" s="61"/>
       <c r="W282" s="31"/>
       <c r="X282" s="33"/>
-      <c r="Y282" s="111"/>
-      <c r="Z282" s="111"/>
-      <c r="AA282" s="111"/>
+      <c r="Y282" s="100"/>
+      <c r="Z282" s="100"/>
+      <c r="AA282" s="100"/>
     </row>
     <row r="283" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A283" s="107"/>
+      <c r="A283" s="96"/>
       <c r="B283" s="90"/>
       <c r="C283" s="91"/>
       <c r="D283" s="71"/>
@@ -38655,12 +38655,12 @@
       <c r="V283" s="61"/>
       <c r="W283" s="34"/>
       <c r="X283" s="33"/>
-      <c r="Y283" s="111"/>
-      <c r="Z283" s="111"/>
-      <c r="AA283" s="111"/>
+      <c r="Y283" s="100"/>
+      <c r="Z283" s="100"/>
+      <c r="AA283" s="100"/>
     </row>
     <row r="284" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A284" s="107"/>
+      <c r="A284" s="96"/>
       <c r="B284" s="90"/>
       <c r="C284" s="86"/>
       <c r="D284" s="66"/>
@@ -38684,12 +38684,12 @@
       <c r="V284" s="61"/>
       <c r="W284" s="33"/>
       <c r="X284" s="33"/>
-      <c r="Y284" s="111"/>
-      <c r="Z284" s="111"/>
-      <c r="AA284" s="111"/>
+      <c r="Y284" s="100"/>
+      <c r="Z284" s="100"/>
+      <c r="AA284" s="100"/>
     </row>
     <row r="285" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A285" s="107"/>
+      <c r="A285" s="96"/>
       <c r="B285" s="90"/>
       <c r="C285" s="86"/>
       <c r="D285" s="66"/>
@@ -38713,12 +38713,12 @@
       <c r="V285" s="61"/>
       <c r="W285" s="31"/>
       <c r="X285" s="33"/>
-      <c r="Y285" s="111"/>
-      <c r="Z285" s="111"/>
-      <c r="AA285" s="111"/>
+      <c r="Y285" s="100"/>
+      <c r="Z285" s="100"/>
+      <c r="AA285" s="100"/>
     </row>
     <row r="286" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A286" s="107"/>
+      <c r="A286" s="96"/>
       <c r="B286" s="90"/>
       <c r="C286" s="86"/>
       <c r="D286" s="66"/>
@@ -38742,12 +38742,12 @@
       <c r="V286" s="61"/>
       <c r="W286" s="31"/>
       <c r="X286" s="33"/>
-      <c r="Y286" s="111"/>
-      <c r="Z286" s="111"/>
-      <c r="AA286" s="111"/>
+      <c r="Y286" s="100"/>
+      <c r="Z286" s="100"/>
+      <c r="AA286" s="100"/>
     </row>
     <row r="287" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A287" s="107"/>
+      <c r="A287" s="96"/>
       <c r="B287" s="90"/>
       <c r="C287" s="86"/>
       <c r="D287" s="66"/>
@@ -38771,12 +38771,12 @@
       <c r="V287" s="61"/>
       <c r="W287" s="31"/>
       <c r="X287" s="33"/>
-      <c r="Y287" s="111"/>
-      <c r="Z287" s="111"/>
-      <c r="AA287" s="111"/>
+      <c r="Y287" s="100"/>
+      <c r="Z287" s="100"/>
+      <c r="AA287" s="100"/>
     </row>
     <row r="288" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A288" s="107"/>
+      <c r="A288" s="96"/>
       <c r="B288" s="90"/>
       <c r="C288" s="86"/>
       <c r="D288" s="66"/>
@@ -38800,12 +38800,12 @@
       <c r="V288" s="61"/>
       <c r="W288" s="31"/>
       <c r="X288" s="33"/>
-      <c r="Y288" s="111"/>
-      <c r="Z288" s="111"/>
-      <c r="AA288" s="111"/>
+      <c r="Y288" s="100"/>
+      <c r="Z288" s="100"/>
+      <c r="AA288" s="100"/>
     </row>
     <row r="289" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A289" s="107"/>
+      <c r="A289" s="96"/>
       <c r="B289" s="90"/>
       <c r="C289" s="86"/>
       <c r="D289" s="66"/>
@@ -38829,12 +38829,12 @@
       <c r="V289" s="61"/>
       <c r="W289" s="31"/>
       <c r="X289" s="33"/>
-      <c r="Y289" s="111"/>
-      <c r="Z289" s="111"/>
-      <c r="AA289" s="111"/>
+      <c r="Y289" s="100"/>
+      <c r="Z289" s="100"/>
+      <c r="AA289" s="100"/>
     </row>
     <row r="290" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A290" s="107"/>
+      <c r="A290" s="96"/>
       <c r="B290" s="90"/>
       <c r="C290" s="86"/>
       <c r="D290" s="66"/>
@@ -38858,12 +38858,12 @@
       <c r="V290" s="61"/>
       <c r="W290" s="31"/>
       <c r="X290" s="33"/>
-      <c r="Y290" s="111"/>
-      <c r="Z290" s="111"/>
-      <c r="AA290" s="111"/>
+      <c r="Y290" s="100"/>
+      <c r="Z290" s="100"/>
+      <c r="AA290" s="100"/>
     </row>
     <row r="291" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A291" s="107"/>
+      <c r="A291" s="96"/>
       <c r="B291" s="90"/>
       <c r="C291" s="91"/>
       <c r="D291" s="71"/>
@@ -38887,12 +38887,12 @@
       <c r="V291" s="61"/>
       <c r="W291" s="34"/>
       <c r="X291" s="33"/>
-      <c r="Y291" s="111"/>
-      <c r="Z291" s="111"/>
-      <c r="AA291" s="111"/>
+      <c r="Y291" s="100"/>
+      <c r="Z291" s="100"/>
+      <c r="AA291" s="100"/>
     </row>
     <row r="292" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A292" s="107"/>
+      <c r="A292" s="96"/>
       <c r="B292" s="90"/>
       <c r="C292" s="86"/>
       <c r="D292" s="66"/>
@@ -38916,12 +38916,12 @@
       <c r="V292" s="61"/>
       <c r="W292" s="33"/>
       <c r="X292" s="33"/>
-      <c r="Y292" s="111"/>
-      <c r="Z292" s="111"/>
-      <c r="AA292" s="111"/>
+      <c r="Y292" s="100"/>
+      <c r="Z292" s="100"/>
+      <c r="AA292" s="100"/>
     </row>
     <row r="293" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A293" s="107"/>
+      <c r="A293" s="96"/>
       <c r="B293" s="90"/>
       <c r="C293" s="86"/>
       <c r="D293" s="66"/>
@@ -38945,12 +38945,12 @@
       <c r="V293" s="61"/>
       <c r="W293" s="31"/>
       <c r="X293" s="33"/>
-      <c r="Y293" s="111"/>
-      <c r="Z293" s="111"/>
-      <c r="AA293" s="111"/>
+      <c r="Y293" s="100"/>
+      <c r="Z293" s="100"/>
+      <c r="AA293" s="100"/>
     </row>
     <row r="294" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A294" s="107"/>
+      <c r="A294" s="96"/>
       <c r="B294" s="90"/>
       <c r="C294" s="86"/>
       <c r="D294" s="66"/>
@@ -38974,12 +38974,12 @@
       <c r="V294" s="61"/>
       <c r="W294" s="31"/>
       <c r="X294" s="33"/>
-      <c r="Y294" s="111"/>
-      <c r="Z294" s="111"/>
-      <c r="AA294" s="111"/>
+      <c r="Y294" s="100"/>
+      <c r="Z294" s="100"/>
+      <c r="AA294" s="100"/>
     </row>
     <row r="295" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A295" s="107"/>
+      <c r="A295" s="96"/>
       <c r="B295" s="90"/>
       <c r="C295" s="86"/>
       <c r="D295" s="66"/>
@@ -39003,12 +39003,12 @@
       <c r="V295" s="61"/>
       <c r="W295" s="31"/>
       <c r="X295" s="33"/>
-      <c r="Y295" s="111"/>
-      <c r="Z295" s="111"/>
-      <c r="AA295" s="111"/>
+      <c r="Y295" s="100"/>
+      <c r="Z295" s="100"/>
+      <c r="AA295" s="100"/>
     </row>
     <row r="296" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A296" s="107"/>
+      <c r="A296" s="96"/>
       <c r="B296" s="90"/>
       <c r="C296" s="86"/>
       <c r="D296" s="66"/>
@@ -39032,12 +39032,12 @@
       <c r="V296" s="61"/>
       <c r="W296" s="31"/>
       <c r="X296" s="33"/>
-      <c r="Y296" s="111"/>
-      <c r="Z296" s="111"/>
-      <c r="AA296" s="111"/>
+      <c r="Y296" s="100"/>
+      <c r="Z296" s="100"/>
+      <c r="AA296" s="100"/>
     </row>
     <row r="297" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A297" s="107"/>
+      <c r="A297" s="96"/>
       <c r="B297" s="90"/>
       <c r="C297" s="91"/>
       <c r="D297" s="71"/>
@@ -39061,12 +39061,12 @@
       <c r="V297" s="61"/>
       <c r="W297" s="34"/>
       <c r="X297" s="33"/>
-      <c r="Y297" s="111"/>
-      <c r="Z297" s="111"/>
-      <c r="AA297" s="111"/>
+      <c r="Y297" s="100"/>
+      <c r="Z297" s="100"/>
+      <c r="AA297" s="100"/>
     </row>
     <row r="298" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A298" s="107"/>
+      <c r="A298" s="96"/>
       <c r="B298" s="90"/>
       <c r="C298" s="86"/>
       <c r="D298" s="66"/>
@@ -39090,12 +39090,12 @@
       <c r="V298" s="61"/>
       <c r="W298" s="33"/>
       <c r="X298" s="33"/>
-      <c r="Y298" s="111"/>
-      <c r="Z298" s="111"/>
-      <c r="AA298" s="111"/>
+      <c r="Y298" s="100"/>
+      <c r="Z298" s="100"/>
+      <c r="AA298" s="100"/>
     </row>
     <row r="299" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A299" s="107"/>
+      <c r="A299" s="96"/>
       <c r="B299" s="90"/>
       <c r="C299" s="86"/>
       <c r="D299" s="66"/>
@@ -39119,12 +39119,12 @@
       <c r="V299" s="61"/>
       <c r="W299" s="31"/>
       <c r="X299" s="33"/>
-      <c r="Y299" s="111"/>
-      <c r="Z299" s="111"/>
-      <c r="AA299" s="111"/>
+      <c r="Y299" s="100"/>
+      <c r="Z299" s="100"/>
+      <c r="AA299" s="100"/>
     </row>
     <row r="300" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A300" s="107"/>
+      <c r="A300" s="96"/>
       <c r="B300" s="90"/>
       <c r="C300" s="86"/>
       <c r="D300" s="66"/>
@@ -39148,12 +39148,12 @@
       <c r="V300" s="61"/>
       <c r="W300" s="31"/>
       <c r="X300" s="33"/>
-      <c r="Y300" s="111"/>
-      <c r="Z300" s="111"/>
-      <c r="AA300" s="111"/>
+      <c r="Y300" s="100"/>
+      <c r="Z300" s="100"/>
+      <c r="AA300" s="100"/>
     </row>
     <row r="301" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A301" s="107"/>
+      <c r="A301" s="96"/>
       <c r="B301" s="90"/>
       <c r="C301" s="86"/>
       <c r="D301" s="66"/>
@@ -39177,12 +39177,12 @@
       <c r="V301" s="61"/>
       <c r="W301" s="31"/>
       <c r="X301" s="33"/>
-      <c r="Y301" s="111"/>
-      <c r="Z301" s="111"/>
-      <c r="AA301" s="111"/>
+      <c r="Y301" s="100"/>
+      <c r="Z301" s="100"/>
+      <c r="AA301" s="100"/>
     </row>
     <row r="302" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A302" s="107"/>
+      <c r="A302" s="96"/>
       <c r="B302" s="90"/>
       <c r="C302" s="86"/>
       <c r="D302" s="66"/>
@@ -39206,12 +39206,12 @@
       <c r="V302" s="61"/>
       <c r="W302" s="31"/>
       <c r="X302" s="33"/>
-      <c r="Y302" s="111"/>
-      <c r="Z302" s="111"/>
-      <c r="AA302" s="111"/>
+      <c r="Y302" s="100"/>
+      <c r="Z302" s="100"/>
+      <c r="AA302" s="100"/>
     </row>
     <row r="303" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A303" s="107"/>
+      <c r="A303" s="96"/>
       <c r="B303" s="90"/>
       <c r="C303" s="86"/>
       <c r="D303" s="66"/>
@@ -39235,12 +39235,12 @@
       <c r="V303" s="61"/>
       <c r="W303" s="31"/>
       <c r="X303" s="33"/>
-      <c r="Y303" s="111"/>
-      <c r="Z303" s="111"/>
-      <c r="AA303" s="111"/>
+      <c r="Y303" s="100"/>
+      <c r="Z303" s="100"/>
+      <c r="AA303" s="100"/>
     </row>
     <row r="304" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A304" s="107"/>
+      <c r="A304" s="96"/>
       <c r="B304" s="90"/>
       <c r="C304" s="86"/>
       <c r="D304" s="66"/>
@@ -39264,12 +39264,12 @@
       <c r="V304" s="61"/>
       <c r="W304" s="31"/>
       <c r="X304" s="33"/>
-      <c r="Y304" s="111"/>
-      <c r="Z304" s="111"/>
-      <c r="AA304" s="111"/>
+      <c r="Y304" s="100"/>
+      <c r="Z304" s="100"/>
+      <c r="AA304" s="100"/>
     </row>
     <row r="305" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A305" s="107"/>
+      <c r="A305" s="96"/>
       <c r="B305" s="90"/>
       <c r="C305" s="91"/>
       <c r="D305" s="71"/>
@@ -39293,12 +39293,12 @@
       <c r="V305" s="61"/>
       <c r="W305" s="34"/>
       <c r="X305" s="33"/>
-      <c r="Y305" s="111"/>
-      <c r="Z305" s="111"/>
-      <c r="AA305" s="111"/>
+      <c r="Y305" s="100"/>
+      <c r="Z305" s="100"/>
+      <c r="AA305" s="100"/>
     </row>
     <row r="306" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A306" s="107"/>
+      <c r="A306" s="96"/>
       <c r="B306" s="90"/>
       <c r="C306" s="86"/>
       <c r="D306" s="66"/>
@@ -39322,12 +39322,12 @@
       <c r="V306" s="61"/>
       <c r="W306" s="33"/>
       <c r="X306" s="33"/>
-      <c r="Y306" s="111"/>
-      <c r="Z306" s="111"/>
-      <c r="AA306" s="111"/>
+      <c r="Y306" s="100"/>
+      <c r="Z306" s="100"/>
+      <c r="AA306" s="100"/>
     </row>
     <row r="307" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A307" s="107"/>
+      <c r="A307" s="96"/>
       <c r="B307" s="90"/>
       <c r="C307" s="86"/>
       <c r="D307" s="66"/>
@@ -39351,12 +39351,12 @@
       <c r="V307" s="61"/>
       <c r="W307" s="31"/>
       <c r="X307" s="33"/>
-      <c r="Y307" s="111"/>
-      <c r="Z307" s="111"/>
-      <c r="AA307" s="111"/>
+      <c r="Y307" s="100"/>
+      <c r="Z307" s="100"/>
+      <c r="AA307" s="100"/>
     </row>
     <row r="308" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A308" s="107"/>
+      <c r="A308" s="96"/>
       <c r="B308" s="90"/>
       <c r="C308" s="86"/>
       <c r="D308" s="66"/>
@@ -39380,12 +39380,12 @@
       <c r="V308" s="61"/>
       <c r="W308" s="31"/>
       <c r="X308" s="33"/>
-      <c r="Y308" s="111"/>
-      <c r="Z308" s="111"/>
-      <c r="AA308" s="111"/>
+      <c r="Y308" s="100"/>
+      <c r="Z308" s="100"/>
+      <c r="AA308" s="100"/>
     </row>
     <row r="309" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A309" s="107"/>
+      <c r="A309" s="96"/>
       <c r="B309" s="90"/>
       <c r="C309" s="86"/>
       <c r="D309" s="66"/>
@@ -39409,12 +39409,12 @@
       <c r="V309" s="61"/>
       <c r="W309" s="31"/>
       <c r="X309" s="33"/>
-      <c r="Y309" s="111"/>
-      <c r="Z309" s="111"/>
-      <c r="AA309" s="111"/>
+      <c r="Y309" s="100"/>
+      <c r="Z309" s="100"/>
+      <c r="AA309" s="100"/>
     </row>
     <row r="310" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A310" s="107"/>
+      <c r="A310" s="96"/>
       <c r="B310" s="90"/>
       <c r="C310" s="86"/>
       <c r="D310" s="66"/>
@@ -39438,12 +39438,12 @@
       <c r="V310" s="61"/>
       <c r="W310" s="31"/>
       <c r="X310" s="33"/>
-      <c r="Y310" s="111"/>
-      <c r="Z310" s="111"/>
-      <c r="AA310" s="111"/>
+      <c r="Y310" s="100"/>
+      <c r="Z310" s="100"/>
+      <c r="AA310" s="100"/>
     </row>
     <row r="311" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A311" s="107"/>
+      <c r="A311" s="96"/>
       <c r="B311" s="90"/>
       <c r="C311" s="91"/>
       <c r="D311" s="71"/>
@@ -39467,12 +39467,12 @@
       <c r="V311" s="61"/>
       <c r="W311" s="34"/>
       <c r="X311" s="33"/>
-      <c r="Y311" s="111"/>
-      <c r="Z311" s="111"/>
-      <c r="AA311" s="111"/>
+      <c r="Y311" s="100"/>
+      <c r="Z311" s="100"/>
+      <c r="AA311" s="100"/>
     </row>
     <row r="312" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A312" s="107"/>
+      <c r="A312" s="96"/>
       <c r="B312" s="90"/>
       <c r="C312" s="86"/>
       <c r="D312" s="66"/>
@@ -39496,12 +39496,12 @@
       <c r="V312" s="61"/>
       <c r="W312" s="33"/>
       <c r="X312" s="33"/>
-      <c r="Y312" s="111"/>
-      <c r="Z312" s="111"/>
-      <c r="AA312" s="111"/>
+      <c r="Y312" s="100"/>
+      <c r="Z312" s="100"/>
+      <c r="AA312" s="100"/>
     </row>
     <row r="313" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A313" s="107"/>
+      <c r="A313" s="96"/>
       <c r="B313" s="90"/>
       <c r="C313" s="86"/>
       <c r="D313" s="66"/>
@@ -39525,12 +39525,12 @@
       <c r="V313" s="61"/>
       <c r="W313" s="31"/>
       <c r="X313" s="33"/>
-      <c r="Y313" s="111"/>
-      <c r="Z313" s="111"/>
-      <c r="AA313" s="111"/>
+      <c r="Y313" s="100"/>
+      <c r="Z313" s="100"/>
+      <c r="AA313" s="100"/>
     </row>
     <row r="314" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A314" s="107"/>
+      <c r="A314" s="96"/>
       <c r="B314" s="90"/>
       <c r="C314" s="86"/>
       <c r="D314" s="66"/>
@@ -39554,12 +39554,12 @@
       <c r="V314" s="61"/>
       <c r="W314" s="31"/>
       <c r="X314" s="33"/>
-      <c r="Y314" s="111"/>
-      <c r="Z314" s="111"/>
-      <c r="AA314" s="111"/>
+      <c r="Y314" s="100"/>
+      <c r="Z314" s="100"/>
+      <c r="AA314" s="100"/>
     </row>
     <row r="315" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A315" s="107"/>
+      <c r="A315" s="96"/>
       <c r="B315" s="90"/>
       <c r="C315" s="86"/>
       <c r="D315" s="66"/>
@@ -39583,12 +39583,12 @@
       <c r="V315" s="61"/>
       <c r="W315" s="31"/>
       <c r="X315" s="33"/>
-      <c r="Y315" s="111"/>
-      <c r="Z315" s="111"/>
-      <c r="AA315" s="111"/>
+      <c r="Y315" s="100"/>
+      <c r="Z315" s="100"/>
+      <c r="AA315" s="100"/>
     </row>
     <row r="316" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A316" s="107"/>
+      <c r="A316" s="96"/>
       <c r="B316" s="90"/>
       <c r="C316" s="86"/>
       <c r="D316" s="66"/>
@@ -39612,12 +39612,12 @@
       <c r="V316" s="61"/>
       <c r="W316" s="31"/>
       <c r="X316" s="33"/>
-      <c r="Y316" s="111"/>
-      <c r="Z316" s="111"/>
-      <c r="AA316" s="111"/>
+      <c r="Y316" s="100"/>
+      <c r="Z316" s="100"/>
+      <c r="AA316" s="100"/>
     </row>
     <row r="317" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A317" s="107"/>
+      <c r="A317" s="96"/>
       <c r="B317" s="90"/>
       <c r="C317" s="86"/>
       <c r="D317" s="66"/>
@@ -39641,12 +39641,12 @@
       <c r="V317" s="61"/>
       <c r="W317" s="31"/>
       <c r="X317" s="33"/>
-      <c r="Y317" s="111"/>
-      <c r="Z317" s="111"/>
-      <c r="AA317" s="111"/>
+      <c r="Y317" s="100"/>
+      <c r="Z317" s="100"/>
+      <c r="AA317" s="100"/>
     </row>
     <row r="318" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A318" s="107"/>
+      <c r="A318" s="96"/>
       <c r="B318" s="90"/>
       <c r="C318" s="86"/>
       <c r="D318" s="66"/>
@@ -39670,12 +39670,12 @@
       <c r="V318" s="61"/>
       <c r="W318" s="31"/>
       <c r="X318" s="33"/>
-      <c r="Y318" s="111"/>
-      <c r="Z318" s="111"/>
-      <c r="AA318" s="111"/>
+      <c r="Y318" s="100"/>
+      <c r="Z318" s="100"/>
+      <c r="AA318" s="100"/>
     </row>
     <row r="319" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A319" s="107"/>
+      <c r="A319" s="96"/>
       <c r="B319" s="90"/>
       <c r="C319" s="91"/>
       <c r="D319" s="71"/>
@@ -39699,12 +39699,12 @@
       <c r="V319" s="61"/>
       <c r="W319" s="34"/>
       <c r="X319" s="33"/>
-      <c r="Y319" s="111"/>
-      <c r="Z319" s="111"/>
-      <c r="AA319" s="111"/>
+      <c r="Y319" s="100"/>
+      <c r="Z319" s="100"/>
+      <c r="AA319" s="100"/>
     </row>
     <row r="320" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A320" s="107"/>
+      <c r="A320" s="96"/>
       <c r="B320" s="90"/>
       <c r="C320" s="86"/>
       <c r="D320" s="66"/>
@@ -39728,12 +39728,12 @@
       <c r="V320" s="61"/>
       <c r="W320" s="33"/>
       <c r="X320" s="33"/>
-      <c r="Y320" s="111"/>
-      <c r="Z320" s="111"/>
-      <c r="AA320" s="111"/>
+      <c r="Y320" s="100"/>
+      <c r="Z320" s="100"/>
+      <c r="AA320" s="100"/>
     </row>
     <row r="321" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A321" s="107"/>
+      <c r="A321" s="96"/>
       <c r="B321" s="90"/>
       <c r="C321" s="86"/>
       <c r="D321" s="66"/>
@@ -39757,12 +39757,12 @@
       <c r="V321" s="61"/>
       <c r="W321" s="31"/>
       <c r="X321" s="33"/>
-      <c r="Y321" s="111"/>
-      <c r="Z321" s="111"/>
-      <c r="AA321" s="111"/>
+      <c r="Y321" s="100"/>
+      <c r="Z321" s="100"/>
+      <c r="AA321" s="100"/>
     </row>
     <row r="322" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A322" s="107"/>
+      <c r="A322" s="96"/>
       <c r="B322" s="90"/>
       <c r="C322" s="86"/>
       <c r="D322" s="66"/>
@@ -39786,12 +39786,12 @@
       <c r="V322" s="61"/>
       <c r="W322" s="31"/>
       <c r="X322" s="33"/>
-      <c r="Y322" s="111"/>
-      <c r="Z322" s="111"/>
-      <c r="AA322" s="111"/>
+      <c r="Y322" s="100"/>
+      <c r="Z322" s="100"/>
+      <c r="AA322" s="100"/>
     </row>
     <row r="323" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A323" s="107"/>
+      <c r="A323" s="96"/>
       <c r="B323" s="90"/>
       <c r="C323" s="86"/>
       <c r="D323" s="66"/>
@@ -39815,12 +39815,12 @@
       <c r="V323" s="61"/>
       <c r="W323" s="31"/>
       <c r="X323" s="33"/>
-      <c r="Y323" s="111"/>
-      <c r="Z323" s="111"/>
-      <c r="AA323" s="111"/>
+      <c r="Y323" s="100"/>
+      <c r="Z323" s="100"/>
+      <c r="AA323" s="100"/>
     </row>
     <row r="324" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A324" s="107"/>
+      <c r="A324" s="96"/>
       <c r="B324" s="90"/>
       <c r="C324" s="86"/>
       <c r="D324" s="66"/>
@@ -39844,12 +39844,12 @@
       <c r="V324" s="61"/>
       <c r="W324" s="31"/>
       <c r="X324" s="33"/>
-      <c r="Y324" s="111"/>
-      <c r="Z324" s="111"/>
-      <c r="AA324" s="111"/>
+      <c r="Y324" s="100"/>
+      <c r="Z324" s="100"/>
+      <c r="AA324" s="100"/>
     </row>
     <row r="325" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A325" s="107"/>
+      <c r="A325" s="96"/>
       <c r="B325" s="90"/>
       <c r="C325" s="91"/>
       <c r="D325" s="71"/>
@@ -39873,12 +39873,12 @@
       <c r="V325" s="61"/>
       <c r="W325" s="34"/>
       <c r="X325" s="33"/>
-      <c r="Y325" s="111"/>
-      <c r="Z325" s="111"/>
-      <c r="AA325" s="111"/>
+      <c r="Y325" s="100"/>
+      <c r="Z325" s="100"/>
+      <c r="AA325" s="100"/>
     </row>
     <row r="326" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A326" s="107"/>
+      <c r="A326" s="96"/>
       <c r="B326" s="90"/>
       <c r="C326" s="86"/>
       <c r="D326" s="66"/>
@@ -39902,12 +39902,12 @@
       <c r="V326" s="61"/>
       <c r="W326" s="33"/>
       <c r="X326" s="33"/>
-      <c r="Y326" s="111"/>
-      <c r="Z326" s="111"/>
-      <c r="AA326" s="111"/>
+      <c r="Y326" s="100"/>
+      <c r="Z326" s="100"/>
+      <c r="AA326" s="100"/>
     </row>
     <row r="327" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A327" s="107"/>
+      <c r="A327" s="96"/>
       <c r="B327" s="90"/>
       <c r="C327" s="86"/>
       <c r="D327" s="66"/>
@@ -39931,12 +39931,12 @@
       <c r="V327" s="61"/>
       <c r="W327" s="31"/>
       <c r="X327" s="33"/>
-      <c r="Y327" s="111"/>
-      <c r="Z327" s="111"/>
-      <c r="AA327" s="111"/>
+      <c r="Y327" s="100"/>
+      <c r="Z327" s="100"/>
+      <c r="AA327" s="100"/>
     </row>
     <row r="328" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A328" s="107"/>
+      <c r="A328" s="96"/>
       <c r="B328" s="90"/>
       <c r="C328" s="86"/>
       <c r="D328" s="66"/>
@@ -39960,12 +39960,12 @@
       <c r="V328" s="61"/>
       <c r="W328" s="31"/>
       <c r="X328" s="33"/>
-      <c r="Y328" s="111"/>
-      <c r="Z328" s="111"/>
-      <c r="AA328" s="111"/>
+      <c r="Y328" s="100"/>
+      <c r="Z328" s="100"/>
+      <c r="AA328" s="100"/>
     </row>
     <row r="329" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A329" s="107"/>
+      <c r="A329" s="96"/>
       <c r="B329" s="90"/>
       <c r="C329" s="86"/>
       <c r="D329" s="66"/>
@@ -39989,12 +39989,12 @@
       <c r="V329" s="61"/>
       <c r="W329" s="31"/>
       <c r="X329" s="33"/>
-      <c r="Y329" s="111"/>
-      <c r="Z329" s="111"/>
-      <c r="AA329" s="111"/>
+      <c r="Y329" s="100"/>
+      <c r="Z329" s="100"/>
+      <c r="AA329" s="100"/>
     </row>
     <row r="330" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A330" s="107"/>
+      <c r="A330" s="96"/>
       <c r="B330" s="90"/>
       <c r="C330" s="86"/>
       <c r="D330" s="66"/>
@@ -40018,12 +40018,12 @@
       <c r="V330" s="61"/>
       <c r="W330" s="31"/>
       <c r="X330" s="33"/>
-      <c r="Y330" s="111"/>
-      <c r="Z330" s="111"/>
-      <c r="AA330" s="111"/>
+      <c r="Y330" s="100"/>
+      <c r="Z330" s="100"/>
+      <c r="AA330" s="100"/>
     </row>
     <row r="331" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A331" s="107"/>
+      <c r="A331" s="96"/>
       <c r="B331" s="90"/>
       <c r="C331" s="86"/>
       <c r="D331" s="66"/>
@@ -40047,12 +40047,12 @@
       <c r="V331" s="61"/>
       <c r="W331" s="31"/>
       <c r="X331" s="33"/>
-      <c r="Y331" s="111"/>
-      <c r="Z331" s="111"/>
-      <c r="AA331" s="111"/>
+      <c r="Y331" s="100"/>
+      <c r="Z331" s="100"/>
+      <c r="AA331" s="100"/>
     </row>
     <row r="332" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A332" s="107"/>
+      <c r="A332" s="96"/>
       <c r="B332" s="90"/>
       <c r="C332" s="86"/>
       <c r="D332" s="66"/>
@@ -40076,12 +40076,12 @@
       <c r="V332" s="61"/>
       <c r="W332" s="31"/>
       <c r="X332" s="33"/>
-      <c r="Y332" s="111"/>
-      <c r="Z332" s="111"/>
-      <c r="AA332" s="111"/>
+      <c r="Y332" s="100"/>
+      <c r="Z332" s="100"/>
+      <c r="AA332" s="100"/>
     </row>
     <row r="333" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A333" s="107"/>
+      <c r="A333" s="96"/>
       <c r="B333" s="90"/>
       <c r="C333" s="91"/>
       <c r="D333" s="71"/>
@@ -40105,12 +40105,12 @@
       <c r="V333" s="61"/>
       <c r="W333" s="34"/>
       <c r="X333" s="33"/>
-      <c r="Y333" s="111"/>
-      <c r="Z333" s="111"/>
-      <c r="AA333" s="111"/>
+      <c r="Y333" s="100"/>
+      <c r="Z333" s="100"/>
+      <c r="AA333" s="100"/>
     </row>
     <row r="334" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A334" s="107"/>
+      <c r="A334" s="96"/>
       <c r="B334" s="90"/>
       <c r="C334" s="86"/>
       <c r="D334" s="66"/>
@@ -40134,12 +40134,12 @@
       <c r="V334" s="61"/>
       <c r="W334" s="33"/>
       <c r="X334" s="33"/>
-      <c r="Y334" s="111"/>
-      <c r="Z334" s="111"/>
-      <c r="AA334" s="111"/>
+      <c r="Y334" s="100"/>
+      <c r="Z334" s="100"/>
+      <c r="AA334" s="100"/>
     </row>
     <row r="335" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A335" s="107"/>
+      <c r="A335" s="96"/>
       <c r="B335" s="90"/>
       <c r="C335" s="86"/>
       <c r="D335" s="66"/>
@@ -40163,12 +40163,12 @@
       <c r="V335" s="61"/>
       <c r="W335" s="31"/>
       <c r="X335" s="33"/>
-      <c r="Y335" s="111"/>
-      <c r="Z335" s="111"/>
-      <c r="AA335" s="111"/>
+      <c r="Y335" s="100"/>
+      <c r="Z335" s="100"/>
+      <c r="AA335" s="100"/>
     </row>
     <row r="336" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A336" s="107"/>
+      <c r="A336" s="96"/>
       <c r="B336" s="90"/>
       <c r="C336" s="86"/>
       <c r="D336" s="66"/>
@@ -40192,12 +40192,12 @@
       <c r="V336" s="61"/>
       <c r="W336" s="31"/>
       <c r="X336" s="33"/>
-      <c r="Y336" s="111"/>
-      <c r="Z336" s="111"/>
-      <c r="AA336" s="111"/>
+      <c r="Y336" s="100"/>
+      <c r="Z336" s="100"/>
+      <c r="AA336" s="100"/>
     </row>
     <row r="337" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A337" s="107"/>
+      <c r="A337" s="96"/>
       <c r="B337" s="90"/>
       <c r="C337" s="86"/>
       <c r="D337" s="66"/>
@@ -40221,12 +40221,12 @@
       <c r="V337" s="61"/>
       <c r="W337" s="31"/>
       <c r="X337" s="33"/>
-      <c r="Y337" s="111"/>
-      <c r="Z337" s="111"/>
-      <c r="AA337" s="111"/>
+      <c r="Y337" s="100"/>
+      <c r="Z337" s="100"/>
+      <c r="AA337" s="100"/>
     </row>
     <row r="338" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A338" s="107"/>
+      <c r="A338" s="96"/>
       <c r="B338" s="90"/>
       <c r="C338" s="86"/>
       <c r="D338" s="66"/>
@@ -40250,12 +40250,12 @@
       <c r="V338" s="61"/>
       <c r="W338" s="31"/>
       <c r="X338" s="33"/>
-      <c r="Y338" s="111"/>
-      <c r="Z338" s="111"/>
-      <c r="AA338" s="111"/>
+      <c r="Y338" s="100"/>
+      <c r="Z338" s="100"/>
+      <c r="AA338" s="100"/>
     </row>
     <row r="339" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A339" s="107"/>
+      <c r="A339" s="96"/>
       <c r="B339" s="90"/>
       <c r="C339" s="91"/>
       <c r="D339" s="71"/>
@@ -40279,12 +40279,12 @@
       <c r="V339" s="61"/>
       <c r="W339" s="34"/>
       <c r="X339" s="33"/>
-      <c r="Y339" s="111"/>
-      <c r="Z339" s="111"/>
-      <c r="AA339" s="111"/>
+      <c r="Y339" s="100"/>
+      <c r="Z339" s="100"/>
+      <c r="AA339" s="100"/>
     </row>
     <row r="340" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A340" s="107"/>
+      <c r="A340" s="96"/>
       <c r="B340" s="90"/>
       <c r="C340" s="86"/>
       <c r="D340" s="66"/>
@@ -40308,12 +40308,12 @@
       <c r="V340" s="61"/>
       <c r="W340" s="33"/>
       <c r="X340" s="33"/>
-      <c r="Y340" s="111"/>
-      <c r="Z340" s="111"/>
-      <c r="AA340" s="111"/>
+      <c r="Y340" s="100"/>
+      <c r="Z340" s="100"/>
+      <c r="AA340" s="100"/>
     </row>
     <row r="341" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A341" s="107"/>
+      <c r="A341" s="96"/>
       <c r="B341" s="90"/>
       <c r="C341" s="86"/>
       <c r="D341" s="66"/>
@@ -40337,12 +40337,12 @@
       <c r="V341" s="61"/>
       <c r="W341" s="31"/>
       <c r="X341" s="33"/>
-      <c r="Y341" s="111"/>
-      <c r="Z341" s="111"/>
-      <c r="AA341" s="111"/>
+      <c r="Y341" s="100"/>
+      <c r="Z341" s="100"/>
+      <c r="AA341" s="100"/>
     </row>
     <row r="342" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A342" s="107"/>
+      <c r="A342" s="96"/>
       <c r="B342" s="90"/>
       <c r="C342" s="86"/>
       <c r="D342" s="66"/>
@@ -40366,12 +40366,12 @@
       <c r="V342" s="61"/>
       <c r="W342" s="31"/>
       <c r="X342" s="33"/>
-      <c r="Y342" s="111"/>
-      <c r="Z342" s="111"/>
-      <c r="AA342" s="111"/>
+      <c r="Y342" s="100"/>
+      <c r="Z342" s="100"/>
+      <c r="AA342" s="100"/>
     </row>
     <row r="343" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A343" s="107"/>
+      <c r="A343" s="96"/>
       <c r="B343" s="90"/>
       <c r="C343" s="86"/>
       <c r="D343" s="66"/>
@@ -40395,12 +40395,12 @@
       <c r="V343" s="61"/>
       <c r="W343" s="31"/>
       <c r="X343" s="33"/>
-      <c r="Y343" s="111"/>
-      <c r="Z343" s="111"/>
-      <c r="AA343" s="111"/>
+      <c r="Y343" s="100"/>
+      <c r="Z343" s="100"/>
+      <c r="AA343" s="100"/>
     </row>
     <row r="344" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A344" s="107"/>
+      <c r="A344" s="96"/>
       <c r="B344" s="90"/>
       <c r="C344" s="86"/>
       <c r="D344" s="66"/>
@@ -40424,12 +40424,12 @@
       <c r="V344" s="61"/>
       <c r="W344" s="31"/>
       <c r="X344" s="33"/>
-      <c r="Y344" s="111"/>
-      <c r="Z344" s="111"/>
-      <c r="AA344" s="111"/>
+      <c r="Y344" s="100"/>
+      <c r="Z344" s="100"/>
+      <c r="AA344" s="100"/>
     </row>
     <row r="345" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A345" s="107"/>
+      <c r="A345" s="96"/>
       <c r="B345" s="90"/>
       <c r="C345" s="86"/>
       <c r="D345" s="66"/>
@@ -40453,12 +40453,12 @@
       <c r="V345" s="61"/>
       <c r="W345" s="31"/>
       <c r="X345" s="33"/>
-      <c r="Y345" s="111"/>
-      <c r="Z345" s="111"/>
-      <c r="AA345" s="111"/>
+      <c r="Y345" s="100"/>
+      <c r="Z345" s="100"/>
+      <c r="AA345" s="100"/>
     </row>
     <row r="346" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A346" s="107"/>
+      <c r="A346" s="96"/>
       <c r="B346" s="90"/>
       <c r="C346" s="86"/>
       <c r="D346" s="66"/>
@@ -40482,12 +40482,12 @@
       <c r="V346" s="61"/>
       <c r="W346" s="31"/>
       <c r="X346" s="33"/>
-      <c r="Y346" s="111"/>
-      <c r="Z346" s="111"/>
-      <c r="AA346" s="111"/>
+      <c r="Y346" s="100"/>
+      <c r="Z346" s="100"/>
+      <c r="AA346" s="100"/>
     </row>
     <row r="347" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A347" s="107"/>
+      <c r="A347" s="96"/>
       <c r="B347" s="90"/>
       <c r="C347" s="91"/>
       <c r="D347" s="71"/>
@@ -40511,12 +40511,12 @@
       <c r="V347" s="61"/>
       <c r="W347" s="34"/>
       <c r="X347" s="33"/>
-      <c r="Y347" s="111"/>
-      <c r="Z347" s="111"/>
-      <c r="AA347" s="111"/>
+      <c r="Y347" s="100"/>
+      <c r="Z347" s="100"/>
+      <c r="AA347" s="100"/>
     </row>
     <row r="348" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A348" s="107"/>
+      <c r="A348" s="96"/>
       <c r="B348" s="90"/>
       <c r="C348" s="86"/>
       <c r="D348" s="66"/>
@@ -40540,12 +40540,12 @@
       <c r="V348" s="61"/>
       <c r="W348" s="33"/>
       <c r="X348" s="33"/>
-      <c r="Y348" s="111"/>
-      <c r="Z348" s="111"/>
-      <c r="AA348" s="111"/>
+      <c r="Y348" s="100"/>
+      <c r="Z348" s="100"/>
+      <c r="AA348" s="100"/>
     </row>
     <row r="349" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A349" s="107"/>
+      <c r="A349" s="96"/>
       <c r="B349" s="90"/>
       <c r="C349" s="86"/>
       <c r="D349" s="66"/>
@@ -40569,12 +40569,12 @@
       <c r="V349" s="61"/>
       <c r="W349" s="31"/>
       <c r="X349" s="33"/>
-      <c r="Y349" s="111"/>
-      <c r="Z349" s="111"/>
-      <c r="AA349" s="111"/>
+      <c r="Y349" s="100"/>
+      <c r="Z349" s="100"/>
+      <c r="AA349" s="100"/>
     </row>
     <row r="350" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A350" s="107"/>
+      <c r="A350" s="96"/>
       <c r="B350" s="90"/>
       <c r="C350" s="86"/>
       <c r="D350" s="66"/>
@@ -40598,12 +40598,12 @@
       <c r="V350" s="61"/>
       <c r="W350" s="31"/>
       <c r="X350" s="33"/>
-      <c r="Y350" s="111"/>
-      <c r="Z350" s="111"/>
-      <c r="AA350" s="111"/>
+      <c r="Y350" s="100"/>
+      <c r="Z350" s="100"/>
+      <c r="AA350" s="100"/>
     </row>
     <row r="351" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A351" s="107"/>
+      <c r="A351" s="96"/>
       <c r="B351" s="90"/>
       <c r="C351" s="86"/>
       <c r="D351" s="66"/>
@@ -40627,12 +40627,12 @@
       <c r="V351" s="61"/>
       <c r="W351" s="31"/>
       <c r="X351" s="33"/>
-      <c r="Y351" s="111"/>
-      <c r="Z351" s="111"/>
-      <c r="AA351" s="111"/>
+      <c r="Y351" s="100"/>
+      <c r="Z351" s="100"/>
+      <c r="AA351" s="100"/>
     </row>
     <row r="352" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A352" s="107"/>
+      <c r="A352" s="96"/>
       <c r="B352" s="90"/>
       <c r="C352" s="86"/>
       <c r="D352" s="66"/>
@@ -40656,12 +40656,12 @@
       <c r="V352" s="61"/>
       <c r="W352" s="31"/>
       <c r="X352" s="33"/>
-      <c r="Y352" s="111"/>
-      <c r="Z352" s="111"/>
-      <c r="AA352" s="111"/>
+      <c r="Y352" s="100"/>
+      <c r="Z352" s="100"/>
+      <c r="AA352" s="100"/>
     </row>
     <row r="353" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A353" s="107"/>
+      <c r="A353" s="96"/>
       <c r="B353" s="90"/>
       <c r="C353" s="91"/>
       <c r="D353" s="71"/>
@@ -40685,12 +40685,12 @@
       <c r="V353" s="61"/>
       <c r="W353" s="34"/>
       <c r="X353" s="33"/>
-      <c r="Y353" s="111"/>
-      <c r="Z353" s="111"/>
-      <c r="AA353" s="111"/>
+      <c r="Y353" s="100"/>
+      <c r="Z353" s="100"/>
+      <c r="AA353" s="100"/>
     </row>
     <row r="354" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A354" s="107"/>
+      <c r="A354" s="96"/>
       <c r="B354" s="90"/>
       <c r="C354" s="86"/>
       <c r="D354" s="66"/>
@@ -40714,12 +40714,12 @@
       <c r="V354" s="61"/>
       <c r="W354" s="33"/>
       <c r="X354" s="33"/>
-      <c r="Y354" s="111"/>
-      <c r="Z354" s="111"/>
-      <c r="AA354" s="111"/>
+      <c r="Y354" s="100"/>
+      <c r="Z354" s="100"/>
+      <c r="AA354" s="100"/>
     </row>
     <row r="355" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A355" s="107"/>
+      <c r="A355" s="96"/>
       <c r="B355" s="90"/>
       <c r="C355" s="86"/>
       <c r="D355" s="66"/>
@@ -40743,12 +40743,12 @@
       <c r="V355" s="61"/>
       <c r="W355" s="31"/>
       <c r="X355" s="33"/>
-      <c r="Y355" s="111"/>
-      <c r="Z355" s="111"/>
-      <c r="AA355" s="111"/>
+      <c r="Y355" s="100"/>
+      <c r="Z355" s="100"/>
+      <c r="AA355" s="100"/>
     </row>
     <row r="356" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A356" s="107"/>
+      <c r="A356" s="96"/>
       <c r="B356" s="90"/>
       <c r="C356" s="86"/>
       <c r="D356" s="66"/>
@@ -40772,12 +40772,12 @@
       <c r="V356" s="61"/>
       <c r="W356" s="31"/>
       <c r="X356" s="33"/>
-      <c r="Y356" s="111"/>
-      <c r="Z356" s="111"/>
-      <c r="AA356" s="111"/>
+      <c r="Y356" s="100"/>
+      <c r="Z356" s="100"/>
+      <c r="AA356" s="100"/>
     </row>
     <row r="357" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A357" s="107"/>
+      <c r="A357" s="96"/>
       <c r="B357" s="90"/>
       <c r="C357" s="86"/>
       <c r="D357" s="66"/>
@@ -40801,12 +40801,12 @@
       <c r="V357" s="61"/>
       <c r="W357" s="31"/>
       <c r="X357" s="33"/>
-      <c r="Y357" s="111"/>
-      <c r="Z357" s="111"/>
-      <c r="AA357" s="111"/>
+      <c r="Y357" s="100"/>
+      <c r="Z357" s="100"/>
+      <c r="AA357" s="100"/>
     </row>
     <row r="358" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A358" s="107"/>
+      <c r="A358" s="96"/>
       <c r="B358" s="90"/>
       <c r="C358" s="86"/>
       <c r="D358" s="66"/>
@@ -40830,12 +40830,12 @@
       <c r="V358" s="61"/>
       <c r="W358" s="31"/>
       <c r="X358" s="33"/>
-      <c r="Y358" s="111"/>
-      <c r="Z358" s="111"/>
-      <c r="AA358" s="111"/>
+      <c r="Y358" s="100"/>
+      <c r="Z358" s="100"/>
+      <c r="AA358" s="100"/>
     </row>
     <row r="359" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A359" s="107"/>
+      <c r="A359" s="96"/>
       <c r="B359" s="90"/>
       <c r="C359" s="86"/>
       <c r="D359" s="66"/>
@@ -40859,12 +40859,12 @@
       <c r="V359" s="61"/>
       <c r="W359" s="31"/>
       <c r="X359" s="33"/>
-      <c r="Y359" s="111"/>
-      <c r="Z359" s="111"/>
-      <c r="AA359" s="111"/>
+      <c r="Y359" s="100"/>
+      <c r="Z359" s="100"/>
+      <c r="AA359" s="100"/>
     </row>
     <row r="360" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A360" s="107"/>
+      <c r="A360" s="96"/>
       <c r="B360" s="90"/>
       <c r="C360" s="86"/>
       <c r="D360" s="66"/>
@@ -40888,12 +40888,12 @@
       <c r="V360" s="61"/>
       <c r="W360" s="31"/>
       <c r="X360" s="33"/>
-      <c r="Y360" s="111"/>
-      <c r="Z360" s="111"/>
-      <c r="AA360" s="111"/>
+      <c r="Y360" s="100"/>
+      <c r="Z360" s="100"/>
+      <c r="AA360" s="100"/>
     </row>
     <row r="361" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A361" s="107"/>
+      <c r="A361" s="96"/>
       <c r="B361" s="90"/>
       <c r="C361" s="91"/>
       <c r="D361" s="71"/>
@@ -40917,12 +40917,12 @@
       <c r="V361" s="61"/>
       <c r="W361" s="34"/>
       <c r="X361" s="33"/>
-      <c r="Y361" s="111"/>
-      <c r="Z361" s="111"/>
-      <c r="AA361" s="111"/>
+      <c r="Y361" s="100"/>
+      <c r="Z361" s="100"/>
+      <c r="AA361" s="100"/>
     </row>
     <row r="362" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A362" s="107"/>
+      <c r="A362" s="96"/>
       <c r="B362" s="90"/>
       <c r="C362" s="86"/>
       <c r="D362" s="66"/>
@@ -40946,12 +40946,12 @@
       <c r="V362" s="61"/>
       <c r="W362" s="33"/>
       <c r="X362" s="33"/>
-      <c r="Y362" s="111"/>
-      <c r="Z362" s="111"/>
-      <c r="AA362" s="111"/>
+      <c r="Y362" s="100"/>
+      <c r="Z362" s="100"/>
+      <c r="AA362" s="100"/>
     </row>
     <row r="363" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A363" s="107"/>
+      <c r="A363" s="96"/>
       <c r="B363" s="90"/>
       <c r="C363" s="86"/>
       <c r="D363" s="66"/>
@@ -40975,12 +40975,12 @@
       <c r="V363" s="61"/>
       <c r="W363" s="31"/>
       <c r="X363" s="33"/>
-      <c r="Y363" s="111"/>
-      <c r="Z363" s="111"/>
-      <c r="AA363" s="111"/>
+      <c r="Y363" s="100"/>
+      <c r="Z363" s="100"/>
+      <c r="AA363" s="100"/>
     </row>
     <row r="364" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A364" s="107"/>
+      <c r="A364" s="96"/>
       <c r="B364" s="90"/>
       <c r="C364" s="86"/>
       <c r="D364" s="66"/>
@@ -41004,12 +41004,12 @@
       <c r="V364" s="61"/>
       <c r="W364" s="31"/>
       <c r="X364" s="33"/>
-      <c r="Y364" s="111"/>
-      <c r="Z364" s="111"/>
-      <c r="AA364" s="111"/>
+      <c r="Y364" s="100"/>
+      <c r="Z364" s="100"/>
+      <c r="AA364" s="100"/>
     </row>
     <row r="365" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A365" s="107"/>
+      <c r="A365" s="96"/>
       <c r="B365" s="90"/>
       <c r="C365" s="86"/>
       <c r="D365" s="66"/>
@@ -41033,12 +41033,12 @@
       <c r="V365" s="61"/>
       <c r="W365" s="31"/>
       <c r="X365" s="33"/>
-      <c r="Y365" s="111"/>
-      <c r="Z365" s="111"/>
-      <c r="AA365" s="111"/>
+      <c r="Y365" s="100"/>
+      <c r="Z365" s="100"/>
+      <c r="AA365" s="100"/>
     </row>
     <row r="366" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A366" s="107"/>
+      <c r="A366" s="96"/>
       <c r="B366" s="90"/>
       <c r="C366" s="86"/>
       <c r="D366" s="66"/>
@@ -41062,12 +41062,12 @@
       <c r="V366" s="61"/>
       <c r="W366" s="31"/>
       <c r="X366" s="33"/>
-      <c r="Y366" s="111"/>
-      <c r="Z366" s="111"/>
-      <c r="AA366" s="111"/>
+      <c r="Y366" s="100"/>
+      <c r="Z366" s="100"/>
+      <c r="AA366" s="100"/>
     </row>
     <row r="367" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A367" s="107"/>
+      <c r="A367" s="96"/>
       <c r="B367" s="90"/>
       <c r="C367" s="91"/>
       <c r="D367" s="71"/>
@@ -41091,12 +41091,12 @@
       <c r="V367" s="61"/>
       <c r="W367" s="34"/>
       <c r="X367" s="33"/>
-      <c r="Y367" s="111"/>
-      <c r="Z367" s="111"/>
-      <c r="AA367" s="111"/>
+      <c r="Y367" s="100"/>
+      <c r="Z367" s="100"/>
+      <c r="AA367" s="100"/>
     </row>
     <row r="368" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A368" s="107"/>
+      <c r="A368" s="96"/>
       <c r="B368" s="90"/>
       <c r="C368" s="86"/>
       <c r="D368" s="66"/>
@@ -41120,12 +41120,12 @@
       <c r="V368" s="61"/>
       <c r="W368" s="33"/>
       <c r="X368" s="33"/>
-      <c r="Y368" s="111"/>
-      <c r="Z368" s="111"/>
-      <c r="AA368" s="111"/>
+      <c r="Y368" s="100"/>
+      <c r="Z368" s="100"/>
+      <c r="AA368" s="100"/>
     </row>
     <row r="369" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A369" s="107"/>
+      <c r="A369" s="96"/>
       <c r="B369" s="90"/>
       <c r="C369" s="86"/>
       <c r="D369" s="66"/>
@@ -41149,12 +41149,12 @@
       <c r="V369" s="61"/>
       <c r="W369" s="31"/>
       <c r="X369" s="33"/>
-      <c r="Y369" s="111"/>
-      <c r="Z369" s="111"/>
-      <c r="AA369" s="111"/>
+      <c r="Y369" s="100"/>
+      <c r="Z369" s="100"/>
+      <c r="AA369" s="100"/>
     </row>
     <row r="370" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A370" s="107"/>
+      <c r="A370" s="96"/>
       <c r="B370" s="90"/>
       <c r="C370" s="86"/>
       <c r="D370" s="66"/>
@@ -41178,12 +41178,12 @@
       <c r="V370" s="61"/>
       <c r="W370" s="31"/>
       <c r="X370" s="33"/>
-      <c r="Y370" s="111"/>
-      <c r="Z370" s="111"/>
-      <c r="AA370" s="111"/>
+      <c r="Y370" s="100"/>
+      <c r="Z370" s="100"/>
+      <c r="AA370" s="100"/>
     </row>
     <row r="371" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A371" s="107"/>
+      <c r="A371" s="96"/>
       <c r="B371" s="90"/>
       <c r="C371" s="86"/>
       <c r="D371" s="66"/>
@@ -41207,12 +41207,12 @@
       <c r="V371" s="61"/>
       <c r="W371" s="31"/>
       <c r="X371" s="33"/>
-      <c r="Y371" s="111"/>
-      <c r="Z371" s="111"/>
-      <c r="AA371" s="111"/>
+      <c r="Y371" s="100"/>
+      <c r="Z371" s="100"/>
+      <c r="AA371" s="100"/>
     </row>
     <row r="372" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A372" s="107"/>
+      <c r="A372" s="96"/>
       <c r="B372" s="90"/>
       <c r="C372" s="86"/>
       <c r="D372" s="66"/>
@@ -41236,12 +41236,12 @@
       <c r="V372" s="61"/>
       <c r="W372" s="31"/>
       <c r="X372" s="33"/>
-      <c r="Y372" s="111"/>
-      <c r="Z372" s="111"/>
-      <c r="AA372" s="111"/>
+      <c r="Y372" s="100"/>
+      <c r="Z372" s="100"/>
+      <c r="AA372" s="100"/>
     </row>
     <row r="373" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A373" s="107"/>
+      <c r="A373" s="96"/>
       <c r="B373" s="90"/>
       <c r="C373" s="86"/>
       <c r="D373" s="66"/>
@@ -41265,12 +41265,12 @@
       <c r="V373" s="61"/>
       <c r="W373" s="31"/>
       <c r="X373" s="33"/>
-      <c r="Y373" s="111"/>
-      <c r="Z373" s="111"/>
-      <c r="AA373" s="111"/>
+      <c r="Y373" s="100"/>
+      <c r="Z373" s="100"/>
+      <c r="AA373" s="100"/>
     </row>
     <row r="374" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A374" s="107"/>
+      <c r="A374" s="96"/>
       <c r="B374" s="90"/>
       <c r="C374" s="86"/>
       <c r="D374" s="66"/>
@@ -41294,12 +41294,12 @@
       <c r="V374" s="61"/>
       <c r="W374" s="31"/>
       <c r="X374" s="33"/>
-      <c r="Y374" s="111"/>
-      <c r="Z374" s="111"/>
-      <c r="AA374" s="111"/>
+      <c r="Y374" s="100"/>
+      <c r="Z374" s="100"/>
+      <c r="AA374" s="100"/>
     </row>
     <row r="375" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A375" s="107"/>
+      <c r="A375" s="96"/>
       <c r="B375" s="90"/>
       <c r="C375" s="91"/>
       <c r="D375" s="71"/>
@@ -41323,12 +41323,12 @@
       <c r="V375" s="61"/>
       <c r="W375" s="34"/>
       <c r="X375" s="33"/>
-      <c r="Y375" s="111"/>
-      <c r="Z375" s="111"/>
-      <c r="AA375" s="111"/>
+      <c r="Y375" s="100"/>
+      <c r="Z375" s="100"/>
+      <c r="AA375" s="100"/>
     </row>
     <row r="376" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A376" s="107"/>
+      <c r="A376" s="96"/>
       <c r="B376" s="90"/>
       <c r="C376" s="86"/>
       <c r="D376" s="66"/>
@@ -41352,12 +41352,12 @@
       <c r="V376" s="61"/>
       <c r="W376" s="33"/>
       <c r="X376" s="33"/>
-      <c r="Y376" s="111"/>
-      <c r="Z376" s="111"/>
-      <c r="AA376" s="111"/>
+      <c r="Y376" s="100"/>
+      <c r="Z376" s="100"/>
+      <c r="AA376" s="100"/>
     </row>
     <row r="377" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A377" s="107"/>
+      <c r="A377" s="96"/>
       <c r="B377" s="90"/>
       <c r="C377" s="86"/>
       <c r="D377" s="66"/>
@@ -41381,12 +41381,12 @@
       <c r="V377" s="61"/>
       <c r="W377" s="31"/>
       <c r="X377" s="33"/>
-      <c r="Y377" s="111"/>
-      <c r="Z377" s="111"/>
-      <c r="AA377" s="111"/>
+      <c r="Y377" s="100"/>
+      <c r="Z377" s="100"/>
+      <c r="AA377" s="100"/>
     </row>
     <row r="378" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A378" s="107"/>
+      <c r="A378" s="96"/>
       <c r="B378" s="90"/>
       <c r="C378" s="86"/>
       <c r="D378" s="66"/>
@@ -41410,12 +41410,12 @@
       <c r="V378" s="61"/>
       <c r="W378" s="31"/>
       <c r="X378" s="33"/>
-      <c r="Y378" s="111"/>
-      <c r="Z378" s="111"/>
-      <c r="AA378" s="111"/>
+      <c r="Y378" s="100"/>
+      <c r="Z378" s="100"/>
+      <c r="AA378" s="100"/>
     </row>
     <row r="379" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A379" s="107"/>
+      <c r="A379" s="96"/>
       <c r="B379" s="90"/>
       <c r="C379" s="86"/>
       <c r="D379" s="66"/>
@@ -41439,12 +41439,12 @@
       <c r="V379" s="61"/>
       <c r="W379" s="31"/>
       <c r="X379" s="33"/>
-      <c r="Y379" s="111"/>
-      <c r="Z379" s="111"/>
-      <c r="AA379" s="111"/>
+      <c r="Y379" s="100"/>
+      <c r="Z379" s="100"/>
+      <c r="AA379" s="100"/>
     </row>
     <row r="380" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A380" s="107"/>
+      <c r="A380" s="96"/>
       <c r="B380" s="90"/>
       <c r="C380" s="86"/>
       <c r="D380" s="66"/>
@@ -41468,12 +41468,12 @@
       <c r="V380" s="61"/>
       <c r="W380" s="31"/>
       <c r="X380" s="33"/>
-      <c r="Y380" s="111"/>
-      <c r="Z380" s="111"/>
-      <c r="AA380" s="111"/>
+      <c r="Y380" s="100"/>
+      <c r="Z380" s="100"/>
+      <c r="AA380" s="100"/>
     </row>
     <row r="381" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A381" s="107"/>
+      <c r="A381" s="96"/>
       <c r="B381" s="90"/>
       <c r="C381" s="91"/>
       <c r="D381" s="71"/>
@@ -41497,12 +41497,12 @@
       <c r="V381" s="61"/>
       <c r="W381" s="34"/>
       <c r="X381" s="33"/>
-      <c r="Y381" s="111"/>
-      <c r="Z381" s="111"/>
-      <c r="AA381" s="111"/>
+      <c r="Y381" s="100"/>
+      <c r="Z381" s="100"/>
+      <c r="AA381" s="100"/>
     </row>
     <row r="382" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A382" s="107"/>
+      <c r="A382" s="96"/>
       <c r="B382" s="90"/>
       <c r="C382" s="86"/>
       <c r="D382" s="66"/>
@@ -41526,12 +41526,12 @@
       <c r="V382" s="61"/>
       <c r="W382" s="33"/>
       <c r="X382" s="33"/>
-      <c r="Y382" s="111"/>
-      <c r="Z382" s="111"/>
-      <c r="AA382" s="111"/>
+      <c r="Y382" s="100"/>
+      <c r="Z382" s="100"/>
+      <c r="AA382" s="100"/>
     </row>
     <row r="383" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A383" s="107"/>
+      <c r="A383" s="96"/>
       <c r="B383" s="90"/>
       <c r="C383" s="86"/>
       <c r="D383" s="66"/>
@@ -41555,12 +41555,12 @@
       <c r="V383" s="61"/>
       <c r="W383" s="31"/>
       <c r="X383" s="33"/>
-      <c r="Y383" s="111"/>
-      <c r="Z383" s="111"/>
-      <c r="AA383" s="111"/>
+      <c r="Y383" s="100"/>
+      <c r="Z383" s="100"/>
+      <c r="AA383" s="100"/>
     </row>
     <row r="384" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A384" s="107"/>
+      <c r="A384" s="96"/>
       <c r="B384" s="90"/>
       <c r="C384" s="86"/>
       <c r="D384" s="66"/>
@@ -41584,12 +41584,12 @@
       <c r="V384" s="61"/>
       <c r="W384" s="31"/>
       <c r="X384" s="33"/>
-      <c r="Y384" s="111"/>
-      <c r="Z384" s="111"/>
-      <c r="AA384" s="111"/>
+      <c r="Y384" s="100"/>
+      <c r="Z384" s="100"/>
+      <c r="AA384" s="100"/>
     </row>
     <row r="385" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A385" s="107"/>
+      <c r="A385" s="96"/>
       <c r="B385" s="90"/>
       <c r="C385" s="86"/>
       <c r="D385" s="66"/>
@@ -41613,12 +41613,12 @@
       <c r="V385" s="61"/>
       <c r="W385" s="31"/>
       <c r="X385" s="33"/>
-      <c r="Y385" s="111"/>
-      <c r="Z385" s="111"/>
-      <c r="AA385" s="111"/>
+      <c r="Y385" s="100"/>
+      <c r="Z385" s="100"/>
+      <c r="AA385" s="100"/>
     </row>
     <row r="386" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A386" s="107"/>
+      <c r="A386" s="96"/>
       <c r="B386" s="90"/>
       <c r="C386" s="86"/>
       <c r="D386" s="66"/>
@@ -41642,12 +41642,12 @@
       <c r="V386" s="61"/>
       <c r="W386" s="31"/>
       <c r="X386" s="33"/>
-      <c r="Y386" s="111"/>
-      <c r="Z386" s="111"/>
-      <c r="AA386" s="111"/>
+      <c r="Y386" s="100"/>
+      <c r="Z386" s="100"/>
+      <c r="AA386" s="100"/>
     </row>
     <row r="387" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A387" s="107"/>
+      <c r="A387" s="96"/>
       <c r="B387" s="90"/>
       <c r="C387" s="86"/>
       <c r="D387" s="66"/>
@@ -41671,12 +41671,12 @@
       <c r="V387" s="61"/>
       <c r="W387" s="31"/>
       <c r="X387" s="33"/>
-      <c r="Y387" s="111"/>
-      <c r="Z387" s="111"/>
-      <c r="AA387" s="111"/>
+      <c r="Y387" s="100"/>
+      <c r="Z387" s="100"/>
+      <c r="AA387" s="100"/>
     </row>
     <row r="388" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A388" s="107"/>
+      <c r="A388" s="96"/>
       <c r="B388" s="90"/>
       <c r="C388" s="86"/>
       <c r="D388" s="66"/>
@@ -41700,12 +41700,12 @@
       <c r="V388" s="61"/>
       <c r="W388" s="31"/>
       <c r="X388" s="33"/>
-      <c r="Y388" s="111"/>
-      <c r="Z388" s="111"/>
-      <c r="AA388" s="111"/>
+      <c r="Y388" s="100"/>
+      <c r="Z388" s="100"/>
+      <c r="AA388" s="100"/>
     </row>
     <row r="389" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A389" s="107"/>
+      <c r="A389" s="96"/>
       <c r="B389" s="90"/>
       <c r="C389" s="91"/>
       <c r="D389" s="71"/>
@@ -41729,12 +41729,12 @@
       <c r="V389" s="61"/>
       <c r="W389" s="34"/>
       <c r="X389" s="33"/>
-      <c r="Y389" s="111"/>
-      <c r="Z389" s="111"/>
-      <c r="AA389" s="111"/>
+      <c r="Y389" s="100"/>
+      <c r="Z389" s="100"/>
+      <c r="AA389" s="100"/>
     </row>
     <row r="390" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A390" s="107"/>
+      <c r="A390" s="96"/>
       <c r="B390" s="90"/>
       <c r="C390" s="86"/>
       <c r="D390" s="66"/>
@@ -41758,12 +41758,12 @@
       <c r="V390" s="61"/>
       <c r="W390" s="33"/>
       <c r="X390" s="33"/>
-      <c r="Y390" s="111"/>
-      <c r="Z390" s="111"/>
-      <c r="AA390" s="111"/>
+      <c r="Y390" s="100"/>
+      <c r="Z390" s="100"/>
+      <c r="AA390" s="100"/>
     </row>
     <row r="391" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A391" s="107"/>
+      <c r="A391" s="96"/>
       <c r="B391" s="90"/>
       <c r="C391" s="86"/>
       <c r="D391" s="66"/>
@@ -41787,12 +41787,12 @@
       <c r="V391" s="61"/>
       <c r="W391" s="31"/>
       <c r="X391" s="33"/>
-      <c r="Y391" s="111"/>
-      <c r="Z391" s="111"/>
-      <c r="AA391" s="111"/>
+      <c r="Y391" s="100"/>
+      <c r="Z391" s="100"/>
+      <c r="AA391" s="100"/>
     </row>
     <row r="392" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A392" s="107"/>
+      <c r="A392" s="96"/>
       <c r="B392" s="90"/>
       <c r="C392" s="86"/>
       <c r="D392" s="66"/>
@@ -41816,12 +41816,12 @@
       <c r="V392" s="61"/>
       <c r="W392" s="31"/>
       <c r="X392" s="33"/>
-      <c r="Y392" s="111"/>
-      <c r="Z392" s="111"/>
-      <c r="AA392" s="111"/>
+      <c r="Y392" s="100"/>
+      <c r="Z392" s="100"/>
+      <c r="AA392" s="100"/>
     </row>
     <row r="393" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A393" s="107"/>
+      <c r="A393" s="96"/>
       <c r="B393" s="90"/>
       <c r="C393" s="86"/>
       <c r="D393" s="66"/>
@@ -41845,12 +41845,12 @@
       <c r="V393" s="61"/>
       <c r="W393" s="31"/>
       <c r="X393" s="33"/>
-      <c r="Y393" s="111"/>
-      <c r="Z393" s="111"/>
-      <c r="AA393" s="111"/>
+      <c r="Y393" s="100"/>
+      <c r="Z393" s="100"/>
+      <c r="AA393" s="100"/>
     </row>
     <row r="394" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A394" s="107"/>
+      <c r="A394" s="96"/>
       <c r="B394" s="90"/>
       <c r="C394" s="86"/>
       <c r="D394" s="66"/>
@@ -41874,12 +41874,12 @@
       <c r="V394" s="61"/>
       <c r="W394" s="31"/>
       <c r="X394" s="33"/>
-      <c r="Y394" s="111"/>
-      <c r="Z394" s="111"/>
-      <c r="AA394" s="111"/>
+      <c r="Y394" s="100"/>
+      <c r="Z394" s="100"/>
+      <c r="AA394" s="100"/>
     </row>
     <row r="395" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A395" s="107"/>
+      <c r="A395" s="96"/>
       <c r="B395" s="90"/>
       <c r="C395" s="91"/>
       <c r="D395" s="71"/>
@@ -41903,12 +41903,12 @@
       <c r="V395" s="61"/>
       <c r="W395" s="34"/>
       <c r="X395" s="33"/>
-      <c r="Y395" s="111"/>
-      <c r="Z395" s="111"/>
-      <c r="AA395" s="111"/>
+      <c r="Y395" s="100"/>
+      <c r="Z395" s="100"/>
+      <c r="AA395" s="100"/>
     </row>
     <row r="396" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A396" s="107"/>
+      <c r="A396" s="96"/>
       <c r="B396" s="90"/>
       <c r="C396" s="86"/>
       <c r="D396" s="66"/>
@@ -41932,12 +41932,12 @@
       <c r="V396" s="61"/>
       <c r="W396" s="33"/>
       <c r="X396" s="33"/>
-      <c r="Y396" s="111"/>
-      <c r="Z396" s="111"/>
-      <c r="AA396" s="111"/>
+      <c r="Y396" s="100"/>
+      <c r="Z396" s="100"/>
+      <c r="AA396" s="100"/>
     </row>
     <row r="397" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A397" s="107"/>
+      <c r="A397" s="96"/>
       <c r="B397" s="90"/>
       <c r="C397" s="86"/>
       <c r="D397" s="66"/>
@@ -41961,12 +41961,12 @@
       <c r="V397" s="61"/>
       <c r="W397" s="31"/>
       <c r="X397" s="33"/>
-      <c r="Y397" s="111"/>
-      <c r="Z397" s="111"/>
-      <c r="AA397" s="111"/>
+      <c r="Y397" s="100"/>
+      <c r="Z397" s="100"/>
+      <c r="AA397" s="100"/>
     </row>
     <row r="398" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A398" s="107"/>
+      <c r="A398" s="96"/>
       <c r="B398" s="90"/>
       <c r="C398" s="86"/>
       <c r="D398" s="66"/>
@@ -41990,12 +41990,12 @@
       <c r="V398" s="61"/>
       <c r="W398" s="31"/>
       <c r="X398" s="33"/>
-      <c r="Y398" s="111"/>
-      <c r="Z398" s="111"/>
-      <c r="AA398" s="111"/>
+      <c r="Y398" s="100"/>
+      <c r="Z398" s="100"/>
+      <c r="AA398" s="100"/>
     </row>
     <row r="399" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A399" s="107"/>
+      <c r="A399" s="96"/>
       <c r="B399" s="90"/>
       <c r="C399" s="86"/>
       <c r="D399" s="66"/>
@@ -42019,12 +42019,12 @@
       <c r="V399" s="61"/>
       <c r="W399" s="31"/>
       <c r="X399" s="33"/>
-      <c r="Y399" s="111"/>
-      <c r="Z399" s="111"/>
-      <c r="AA399" s="111"/>
+      <c r="Y399" s="100"/>
+      <c r="Z399" s="100"/>
+      <c r="AA399" s="100"/>
     </row>
     <row r="400" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A400" s="107"/>
+      <c r="A400" s="96"/>
       <c r="B400" s="90"/>
       <c r="C400" s="86"/>
       <c r="D400" s="66"/>
@@ -42048,12 +42048,12 @@
       <c r="V400" s="61"/>
       <c r="W400" s="31"/>
       <c r="X400" s="33"/>
-      <c r="Y400" s="111"/>
-      <c r="Z400" s="111"/>
-      <c r="AA400" s="111"/>
+      <c r="Y400" s="100"/>
+      <c r="Z400" s="100"/>
+      <c r="AA400" s="100"/>
     </row>
     <row r="401" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A401" s="107"/>
+      <c r="A401" s="96"/>
       <c r="B401" s="90"/>
       <c r="C401" s="86"/>
       <c r="D401" s="66"/>
@@ -42077,12 +42077,12 @@
       <c r="V401" s="61"/>
       <c r="W401" s="31"/>
       <c r="X401" s="33"/>
-      <c r="Y401" s="111"/>
-      <c r="Z401" s="111"/>
-      <c r="AA401" s="111"/>
+      <c r="Y401" s="100"/>
+      <c r="Z401" s="100"/>
+      <c r="AA401" s="100"/>
     </row>
     <row r="402" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A402" s="107"/>
+      <c r="A402" s="96"/>
       <c r="B402" s="90"/>
       <c r="C402" s="86"/>
       <c r="D402" s="66"/>
@@ -42106,12 +42106,12 @@
       <c r="V402" s="61"/>
       <c r="W402" s="31"/>
       <c r="X402" s="33"/>
-      <c r="Y402" s="111"/>
-      <c r="Z402" s="111"/>
-      <c r="AA402" s="111"/>
+      <c r="Y402" s="100"/>
+      <c r="Z402" s="100"/>
+      <c r="AA402" s="100"/>
     </row>
     <row r="403" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A403" s="107"/>
+      <c r="A403" s="96"/>
       <c r="B403" s="90"/>
       <c r="C403" s="91"/>
       <c r="D403" s="71"/>
@@ -42135,12 +42135,12 @@
       <c r="V403" s="61"/>
       <c r="W403" s="34"/>
       <c r="X403" s="33"/>
-      <c r="Y403" s="111"/>
-      <c r="Z403" s="111"/>
-      <c r="AA403" s="111"/>
+      <c r="Y403" s="100"/>
+      <c r="Z403" s="100"/>
+      <c r="AA403" s="100"/>
     </row>
     <row r="404" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A404" s="107"/>
+      <c r="A404" s="96"/>
       <c r="B404" s="90"/>
       <c r="C404" s="86"/>
       <c r="D404" s="66"/>
@@ -42164,12 +42164,12 @@
       <c r="V404" s="61"/>
       <c r="W404" s="33"/>
       <c r="X404" s="33"/>
-      <c r="Y404" s="111"/>
-      <c r="Z404" s="111"/>
-      <c r="AA404" s="111"/>
+      <c r="Y404" s="100"/>
+      <c r="Z404" s="100"/>
+      <c r="AA404" s="100"/>
     </row>
     <row r="405" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A405" s="107"/>
+      <c r="A405" s="96"/>
       <c r="B405" s="90"/>
       <c r="C405" s="86"/>
       <c r="D405" s="66"/>
@@ -42193,12 +42193,12 @@
       <c r="V405" s="61"/>
       <c r="W405" s="31"/>
       <c r="X405" s="33"/>
-      <c r="Y405" s="111"/>
-      <c r="Z405" s="111"/>
-      <c r="AA405" s="111"/>
+      <c r="Y405" s="100"/>
+      <c r="Z405" s="100"/>
+      <c r="AA405" s="100"/>
     </row>
     <row r="406" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A406" s="107"/>
+      <c r="A406" s="96"/>
       <c r="B406" s="90"/>
       <c r="C406" s="86"/>
       <c r="D406" s="66"/>
@@ -42222,12 +42222,12 @@
       <c r="V406" s="61"/>
       <c r="W406" s="31"/>
       <c r="X406" s="33"/>
-      <c r="Y406" s="111"/>
-      <c r="Z406" s="111"/>
-      <c r="AA406" s="111"/>
+      <c r="Y406" s="100"/>
+      <c r="Z406" s="100"/>
+      <c r="AA406" s="100"/>
     </row>
     <row r="407" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A407" s="107"/>
+      <c r="A407" s="96"/>
       <c r="B407" s="90"/>
       <c r="C407" s="86"/>
       <c r="D407" s="66"/>
@@ -42251,12 +42251,12 @@
       <c r="V407" s="61"/>
       <c r="W407" s="31"/>
       <c r="X407" s="33"/>
-      <c r="Y407" s="111"/>
-      <c r="Z407" s="111"/>
-      <c r="AA407" s="111"/>
+      <c r="Y407" s="100"/>
+      <c r="Z407" s="100"/>
+      <c r="AA407" s="100"/>
     </row>
     <row r="408" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A408" s="107"/>
+      <c r="A408" s="96"/>
       <c r="B408" s="90"/>
       <c r="C408" s="86"/>
       <c r="D408" s="66"/>
@@ -42280,12 +42280,12 @@
       <c r="V408" s="61"/>
       <c r="W408" s="31"/>
       <c r="X408" s="33"/>
-      <c r="Y408" s="111"/>
-      <c r="Z408" s="111"/>
-      <c r="AA408" s="111"/>
+      <c r="Y408" s="100"/>
+      <c r="Z408" s="100"/>
+      <c r="AA408" s="100"/>
     </row>
     <row r="409" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A409" s="107"/>
+      <c r="A409" s="96"/>
       <c r="B409" s="90"/>
       <c r="C409" s="91"/>
       <c r="D409" s="71"/>
@@ -42309,12 +42309,12 @@
       <c r="V409" s="61"/>
       <c r="W409" s="34"/>
       <c r="X409" s="33"/>
-      <c r="Y409" s="111"/>
-      <c r="Z409" s="111"/>
-      <c r="AA409" s="111"/>
+      <c r="Y409" s="100"/>
+      <c r="Z409" s="100"/>
+      <c r="AA409" s="100"/>
     </row>
     <row r="410" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A410" s="107"/>
+      <c r="A410" s="96"/>
       <c r="B410" s="90"/>
       <c r="C410" s="86"/>
       <c r="D410" s="66"/>
@@ -42338,12 +42338,12 @@
       <c r="V410" s="61"/>
       <c r="W410" s="33"/>
       <c r="X410" s="33"/>
-      <c r="Y410" s="111"/>
-      <c r="Z410" s="111"/>
-      <c r="AA410" s="111"/>
+      <c r="Y410" s="100"/>
+      <c r="Z410" s="100"/>
+      <c r="AA410" s="100"/>
     </row>
     <row r="411" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A411" s="107"/>
+      <c r="A411" s="96"/>
       <c r="B411" s="90"/>
       <c r="C411" s="86"/>
       <c r="D411" s="66"/>
@@ -42367,12 +42367,12 @@
       <c r="V411" s="61"/>
       <c r="W411" s="31"/>
       <c r="X411" s="33"/>
-      <c r="Y411" s="111"/>
-      <c r="Z411" s="111"/>
-      <c r="AA411" s="111"/>
+      <c r="Y411" s="100"/>
+      <c r="Z411" s="100"/>
+      <c r="AA411" s="100"/>
     </row>
     <row r="412" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A412" s="107"/>
+      <c r="A412" s="96"/>
       <c r="B412" s="90"/>
       <c r="C412" s="86"/>
       <c r="D412" s="66"/>
@@ -42396,12 +42396,12 @@
       <c r="V412" s="61"/>
       <c r="W412" s="31"/>
       <c r="X412" s="33"/>
-      <c r="Y412" s="111"/>
-      <c r="Z412" s="111"/>
-      <c r="AA412" s="111"/>
+      <c r="Y412" s="100"/>
+      <c r="Z412" s="100"/>
+      <c r="AA412" s="100"/>
     </row>
     <row r="413" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A413" s="107"/>
+      <c r="A413" s="96"/>
       <c r="B413" s="90"/>
       <c r="C413" s="86"/>
       <c r="D413" s="66"/>
@@ -42425,12 +42425,12 @@
       <c r="V413" s="61"/>
       <c r="W413" s="31"/>
       <c r="X413" s="33"/>
-      <c r="Y413" s="111"/>
-      <c r="Z413" s="111"/>
-      <c r="AA413" s="111"/>
+      <c r="Y413" s="100"/>
+      <c r="Z413" s="100"/>
+      <c r="AA413" s="100"/>
     </row>
     <row r="414" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A414" s="107"/>
+      <c r="A414" s="96"/>
       <c r="B414" s="90"/>
       <c r="C414" s="86"/>
       <c r="D414" s="66"/>
@@ -42454,12 +42454,12 @@
       <c r="V414" s="61"/>
       <c r="W414" s="31"/>
       <c r="X414" s="33"/>
-      <c r="Y414" s="111"/>
-      <c r="Z414" s="111"/>
-      <c r="AA414" s="111"/>
+      <c r="Y414" s="100"/>
+      <c r="Z414" s="100"/>
+      <c r="AA414" s="100"/>
     </row>
     <row r="415" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A415" s="107"/>
+      <c r="A415" s="96"/>
       <c r="B415" s="90"/>
       <c r="C415" s="86"/>
       <c r="D415" s="66"/>
@@ -42483,12 +42483,12 @@
       <c r="V415" s="61"/>
       <c r="W415" s="31"/>
       <c r="X415" s="33"/>
-      <c r="Y415" s="111"/>
-      <c r="Z415" s="111"/>
-      <c r="AA415" s="111"/>
+      <c r="Y415" s="100"/>
+      <c r="Z415" s="100"/>
+      <c r="AA415" s="100"/>
     </row>
     <row r="416" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A416" s="107"/>
+      <c r="A416" s="96"/>
       <c r="B416" s="90"/>
       <c r="C416" s="86"/>
       <c r="D416" s="66"/>
@@ -42512,12 +42512,12 @@
       <c r="V416" s="61"/>
       <c r="W416" s="31"/>
       <c r="X416" s="33"/>
-      <c r="Y416" s="111"/>
-      <c r="Z416" s="111"/>
-      <c r="AA416" s="111"/>
+      <c r="Y416" s="100"/>
+      <c r="Z416" s="100"/>
+      <c r="AA416" s="100"/>
     </row>
     <row r="417" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A417" s="107"/>
+      <c r="A417" s="96"/>
       <c r="B417" s="90"/>
       <c r="C417" s="91"/>
       <c r="D417" s="71"/>
@@ -42541,12 +42541,12 @@
       <c r="V417" s="61"/>
       <c r="W417" s="34"/>
       <c r="X417" s="33"/>
-      <c r="Y417" s="111"/>
-      <c r="Z417" s="111"/>
-      <c r="AA417" s="111"/>
+      <c r="Y417" s="100"/>
+      <c r="Z417" s="100"/>
+      <c r="AA417" s="100"/>
     </row>
     <row r="418" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A418" s="107"/>
+      <c r="A418" s="96"/>
       <c r="B418" s="90"/>
       <c r="C418" s="86"/>
       <c r="D418" s="66"/>
@@ -42570,12 +42570,12 @@
       <c r="V418" s="61"/>
       <c r="W418" s="33"/>
       <c r="X418" s="33"/>
-      <c r="Y418" s="111"/>
-      <c r="Z418" s="111"/>
-      <c r="AA418" s="111"/>
+      <c r="Y418" s="100"/>
+      <c r="Z418" s="100"/>
+      <c r="AA418" s="100"/>
     </row>
     <row r="419" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A419" s="107"/>
+      <c r="A419" s="96"/>
       <c r="B419" s="90"/>
       <c r="C419" s="86"/>
       <c r="D419" s="66"/>
@@ -42599,9 +42599,9 @@
       <c r="V419" s="61"/>
       <c r="W419" s="31"/>
       <c r="X419" s="33"/>
-      <c r="Y419" s="111"/>
-      <c r="Z419" s="111"/>
-      <c r="AA419" s="111"/>
+      <c r="Y419" s="100"/>
+      <c r="Z419" s="100"/>
+      <c r="AA419" s="100"/>
     </row>
   </sheetData>
   <pageMargins left="0.78740157480314965" right="0.78740157480314965" top="0.55118110236220474" bottom="0.98425196850393704" header="0" footer="0"/>

--- a/METRADO_PLANTILLA_5.xlsx
+++ b/METRADO_PLANTILLA_5.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr filterPrivacy="1"/>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CB753F4-05E6-4EB4-84FC-AA6BC3F01C74}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
@@ -732,8 +732,8 @@
   <numFmts count="4">
     <numFmt numFmtId="164" formatCode="[$-F800]dddd\,\ mmmm\ dddd\,\ yyyy"/>
     <numFmt numFmtId="165" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="168" formatCode="#,##0.00_);\-#,##0.00"/>
-    <numFmt numFmtId="169" formatCode="dd/mm/yyyy&quot;  &quot;hh&quot;:&quot;mm&quot;:&quot;ss\ AM/PM"/>
+    <numFmt numFmtId="166" formatCode="#,##0.00_);\-#,##0.00"/>
+    <numFmt numFmtId="167" formatCode="dd/mm/yyyy&quot;  &quot;hh&quot;:&quot;mm&quot;:&quot;ss\ AM/PM"/>
   </numFmts>
   <fonts count="18" x14ac:knownFonts="1">
     <font>
@@ -1124,16 +1124,16 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="10" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1141,6 +1141,45 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1164,45 +1203,6 @@
     <xf numFmtId="2" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="11" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1214,10 +1214,74 @@
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
+        <name val="Arial Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="hair">
+          <color rgb="FF000000"/>
+        </left>
+        <right/>
+        <top style="hair">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="hair">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="8"/>
-        <color rgb="FFC00000"/>
+        <color auto="1"/>
+        <name val="Arial Narrow"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="2" formatCode="0.00"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0">
+        <left style="hair">
+          <color rgb="FF000000"/>
+        </left>
+        <right style="hair">
+          <color rgb="FF000000"/>
+        </right>
+        <top style="hair">
+          <color rgb="FF000000"/>
+        </top>
+        <bottom style="hair">
+          <color rgb="FF000000"/>
+        </bottom>
+        <vertical/>
+        <horizontal/>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <sz val="8"/>
+        <color auto="1"/>
         <name val="Arial Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
@@ -1239,12 +1303,14 @@
     </dxf>
     <dxf>
       <font>
+        <b/>
         <strike val="0"/>
         <outline val="0"/>
         <shadow val="0"/>
+        <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="8"/>
-        <color auto="1"/>
+        <color rgb="FFC00000"/>
         <name val="Arial Narrow"/>
         <family val="2"/>
         <scheme val="none"/>
@@ -1319,72 +1385,6 @@
         <bottom style="hair">
           <color rgb="FF000000"/>
         </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="hair">
-          <color rgb="FF000000"/>
-        </left>
-        <right/>
-        <top style="hair">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="hair">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="8"/>
-        <color auto="1"/>
-        <name val="Arial Narrow"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <numFmt numFmtId="2" formatCode="0.00"/>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0">
-        <left style="hair">
-          <color rgb="FF000000"/>
-        </left>
-        <right style="hair">
-          <color rgb="FF000000"/>
-        </right>
-        <top style="hair">
-          <color rgb="FF000000"/>
-        </top>
-        <bottom style="hair">
-          <color rgb="FF000000"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
       </border>
     </dxf>
     <dxf>
@@ -2026,6 +2026,15 @@
       </border>
     </dxf>
     <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <vertAlign val="baseline"/>
+        <color auto="1"/>
+      </font>
+    </dxf>
+    <dxf>
       <border outline="0">
         <left style="hair">
           <color rgb="FF000000"/>
@@ -2040,15 +2049,6 @@
           <color rgb="FF000000"/>
         </bottom>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <vertAlign val="baseline"/>
-        <color auto="1"/>
-      </font>
     </dxf>
     <dxf>
       <font>
@@ -2161,7 +2161,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="B7:AA419" headerRowCount="0" headerRowDxfId="28" totalsRowDxfId="27" tableBorderDxfId="26">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table_1" displayName="Table_1" ref="B7:AA419" headerRowCount="0" headerRowDxfId="28" totalsRowDxfId="26" tableBorderDxfId="27">
   <tableColumns count="26">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="GRADO" dataDxfId="25"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="FECHA" dataDxfId="24"/>
@@ -2183,12 +2183,12 @@
     <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="PARCIAL" dataDxfId="8"/>
     <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="N° VECES" dataDxfId="7"/>
     <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="ACERO" dataDxfId="6"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="TOTAL" dataDxfId="3"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="TOTAL 2" dataDxfId="2"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="UNIDAD" dataDxfId="0"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="MODIF." dataDxfId="1"/>
-    <tableColumn id="25" xr3:uid="{3865C319-53D6-41C8-9C4C-31FA4F4E0948}" name="Columna1" dataDxfId="5"/>
-    <tableColumn id="26" xr3:uid="{F0183D40-AE54-4413-976E-0B00C7B637A5}" name="Columna2" dataDxfId="4"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="TOTAL" dataDxfId="5"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="TOTAL 2" dataDxfId="4"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="UNIDAD" dataDxfId="3"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="MODIF." dataDxfId="2"/>
+    <tableColumn id="25" xr3:uid="{3865C319-53D6-41C8-9C4C-31FA4F4E0948}" name="Columna1" dataDxfId="1"/>
+    <tableColumn id="26" xr3:uid="{F0183D40-AE54-4413-976E-0B00C7B637A5}" name="Columna2" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo showFirstColumn="1" showLastColumn="1" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2418,19 +2418,19 @@
       <c r="E1" s="2"/>
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
-      <c r="H1" s="42" t="s">
+      <c r="H1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-      <c r="M1" s="43"/>
-      <c r="N1" s="43"/>
-      <c r="O1" s="43"/>
-      <c r="P1" s="43"/>
-      <c r="Q1" s="43"/>
-      <c r="R1" s="43"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="56"/>
+      <c r="K1" s="56"/>
+      <c r="L1" s="56"/>
+      <c r="M1" s="56"/>
+      <c r="N1" s="56"/>
+      <c r="O1" s="56"/>
+      <c r="P1" s="56"/>
+      <c r="Q1" s="56"/>
+      <c r="R1" s="56"/>
       <c r="S1" s="1"/>
       <c r="T1" s="1"/>
       <c r="U1" s="1"/>
@@ -2500,25 +2500,25 @@
     </row>
     <row r="4" spans="1:26" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
-      <c r="B4" s="44">
+      <c r="B4" s="57">
         <v>45809</v>
       </c>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="45"/>
-      <c r="G4" s="45"/>
-      <c r="H4" s="45"/>
-      <c r="I4" s="45"/>
-      <c r="J4" s="45"/>
-      <c r="K4" s="45"/>
-      <c r="L4" s="45"/>
-      <c r="M4" s="45"/>
-      <c r="N4" s="45"/>
-      <c r="O4" s="45"/>
-      <c r="P4" s="45"/>
-      <c r="Q4" s="45"/>
-      <c r="R4" s="45"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58"/>
+      <c r="M4" s="58"/>
+      <c r="N4" s="58"/>
+      <c r="O4" s="58"/>
+      <c r="P4" s="58"/>
+      <c r="Q4" s="58"/>
+      <c r="R4" s="58"/>
       <c r="S4" s="1"/>
       <c r="T4" s="1"/>
       <c r="U4" s="1"/>
@@ -2530,38 +2530,38 @@
     </row>
     <row r="5" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="B5" s="49" t="s">
+      <c r="B5" s="62" t="s">
         <v>2</v>
       </c>
-      <c r="C5" s="51" t="s">
+      <c r="C5" s="64" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="49" t="s">
+      <c r="D5" s="62" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="52" t="s">
+      <c r="E5" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="F5" s="52" t="s">
+      <c r="F5" s="65" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="52" t="s">
+      <c r="G5" s="65" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="52" t="s">
+      <c r="H5" s="65" t="s">
         <v>8</v>
       </c>
-      <c r="I5" s="52" t="s">
+      <c r="I5" s="65" t="s">
         <v>9</v>
       </c>
-      <c r="J5" s="46" t="s">
+      <c r="J5" s="59" t="s">
         <v>10</v>
       </c>
-      <c r="K5" s="47"/>
-      <c r="L5" s="47"/>
-      <c r="M5" s="47"/>
-      <c r="N5" s="47"/>
-      <c r="O5" s="48"/>
+      <c r="K5" s="60"/>
+      <c r="L5" s="60"/>
+      <c r="M5" s="60"/>
+      <c r="N5" s="60"/>
+      <c r="O5" s="61"/>
       <c r="P5" s="4"/>
       <c r="Q5" s="5"/>
       <c r="R5" s="6"/>
@@ -2576,14 +2576,14 @@
     </row>
     <row r="6" spans="1:26" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
-      <c r="B6" s="50"/>
-      <c r="C6" s="50"/>
-      <c r="D6" s="50"/>
-      <c r="E6" s="50"/>
-      <c r="F6" s="50"/>
-      <c r="G6" s="50"/>
-      <c r="H6" s="50"/>
-      <c r="I6" s="50"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="63"/>
+      <c r="I6" s="63"/>
       <c r="J6" s="7" t="s">
         <v>11</v>
       </c>
@@ -30782,1934 +30782,1934 @@
     <col min="28" max="16384" width="12.69921875" style="40"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" s="59" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" s="48" customFormat="1" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="41"/>
-      <c r="B1" s="58"/>
-      <c r="C1" s="58"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
-      <c r="J1" s="58"/>
-      <c r="K1" s="58"/>
-      <c r="L1" s="58"/>
-      <c r="M1" s="58"/>
-      <c r="N1" s="58"/>
-      <c r="O1" s="58"/>
-      <c r="P1" s="58"/>
-      <c r="Q1" s="58"/>
-      <c r="R1" s="58"/>
-      <c r="S1" s="58"/>
-      <c r="T1" s="58"/>
-      <c r="U1" s="58"/>
-      <c r="V1" s="58"/>
-      <c r="W1" s="64"/>
-      <c r="X1" s="64"/>
-      <c r="Y1" s="58"/>
-      <c r="Z1" s="58" t="s">
+      <c r="B1" s="47"/>
+      <c r="C1" s="47"/>
+      <c r="D1" s="47"/>
+      <c r="E1" s="47"/>
+      <c r="F1" s="47"/>
+      <c r="G1" s="47"/>
+      <c r="H1" s="47"/>
+      <c r="I1" s="47"/>
+      <c r="J1" s="47"/>
+      <c r="K1" s="47"/>
+      <c r="L1" s="47"/>
+      <c r="M1" s="47"/>
+      <c r="N1" s="47"/>
+      <c r="O1" s="47"/>
+      <c r="P1" s="47"/>
+      <c r="Q1" s="47"/>
+      <c r="R1" s="47"/>
+      <c r="S1" s="47"/>
+      <c r="T1" s="47"/>
+      <c r="U1" s="47"/>
+      <c r="V1" s="47"/>
+      <c r="W1" s="53"/>
+      <c r="X1" s="53"/>
+      <c r="Y1" s="47"/>
+      <c r="Z1" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="AA1" s="58"/>
+      <c r="AA1" s="47"/>
     </row>
     <row r="2" spans="1:27" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
-      <c r="J2" s="58"/>
-      <c r="K2" s="58"/>
-      <c r="L2" s="58"/>
-      <c r="M2" s="58"/>
-      <c r="N2" s="58"/>
-      <c r="O2" s="58"/>
-      <c r="P2" s="58"/>
-      <c r="Q2" s="58"/>
-      <c r="R2" s="58"/>
-      <c r="S2" s="58"/>
-      <c r="T2" s="58"/>
-      <c r="U2" s="58"/>
-      <c r="V2" s="58"/>
-      <c r="W2" s="64"/>
-      <c r="X2" s="64"/>
-      <c r="Y2" s="58"/>
-      <c r="Z2" s="58" t="s">
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+      <c r="M2" s="47"/>
+      <c r="N2" s="47"/>
+      <c r="O2" s="47"/>
+      <c r="P2" s="47"/>
+      <c r="Q2" s="47"/>
+      <c r="R2" s="47"/>
+      <c r="S2" s="47"/>
+      <c r="T2" s="47"/>
+      <c r="U2" s="47"/>
+      <c r="V2" s="47"/>
+      <c r="W2" s="53"/>
+      <c r="X2" s="53"/>
+      <c r="Y2" s="47"/>
+      <c r="Z2" s="47" t="s">
         <v>28</v>
       </c>
-      <c r="AA2" s="58"/>
+      <c r="AA2" s="47"/>
     </row>
     <row r="3" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="58"/>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
-      <c r="J3" s="58"/>
-      <c r="K3" s="58"/>
-      <c r="L3" s="58"/>
-      <c r="M3" s="58"/>
-      <c r="N3" s="58"/>
-      <c r="O3" s="58"/>
-      <c r="P3" s="58"/>
-      <c r="Q3" s="58"/>
-      <c r="R3" s="58"/>
-      <c r="S3" s="58"/>
-      <c r="T3" s="58"/>
-      <c r="U3" s="58"/>
-      <c r="V3" s="58"/>
-      <c r="W3" s="64"/>
-      <c r="X3" s="64"/>
-      <c r="Y3" s="58"/>
-      <c r="Z3" s="58"/>
-      <c r="AA3" s="58"/>
+      <c r="B3" s="47"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="47"/>
+      <c r="J3" s="47"/>
+      <c r="K3" s="47"/>
+      <c r="L3" s="47"/>
+      <c r="M3" s="47"/>
+      <c r="N3" s="47"/>
+      <c r="O3" s="47"/>
+      <c r="P3" s="47"/>
+      <c r="Q3" s="47"/>
+      <c r="R3" s="47"/>
+      <c r="S3" s="47"/>
+      <c r="T3" s="47"/>
+      <c r="U3" s="47"/>
+      <c r="V3" s="47"/>
+      <c r="W3" s="53"/>
+      <c r="X3" s="53"/>
+      <c r="Y3" s="47"/>
+      <c r="Z3" s="47"/>
+      <c r="AA3" s="47"/>
     </row>
     <row r="4" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B4" s="59" t="s">
+      <c r="B4" s="48" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
-      <c r="J4" s="58"/>
-      <c r="K4" s="58"/>
-      <c r="L4" s="58"/>
-      <c r="M4" s="58"/>
-      <c r="N4" s="58"/>
-      <c r="O4" s="58"/>
-      <c r="P4" s="58"/>
-      <c r="Q4" s="58"/>
-      <c r="R4" s="58"/>
-      <c r="S4" s="58"/>
-      <c r="T4" s="58"/>
-      <c r="U4" s="58"/>
-      <c r="V4" s="58"/>
-      <c r="W4" s="64"/>
-      <c r="X4" s="64"/>
-      <c r="Y4" s="58"/>
-      <c r="Z4" s="58"/>
-      <c r="AA4" s="58"/>
+      <c r="C4" s="47"/>
+      <c r="D4" s="47"/>
+      <c r="E4" s="47"/>
+      <c r="F4" s="47"/>
+      <c r="G4" s="47"/>
+      <c r="H4" s="47"/>
+      <c r="I4" s="47"/>
+      <c r="J4" s="47"/>
+      <c r="K4" s="47"/>
+      <c r="L4" s="47"/>
+      <c r="M4" s="47"/>
+      <c r="N4" s="47"/>
+      <c r="O4" s="47"/>
+      <c r="P4" s="47"/>
+      <c r="Q4" s="47"/>
+      <c r="R4" s="47"/>
+      <c r="S4" s="47"/>
+      <c r="T4" s="47"/>
+      <c r="U4" s="47"/>
+      <c r="V4" s="47"/>
+      <c r="W4" s="53"/>
+      <c r="X4" s="53"/>
+      <c r="Y4" s="47"/>
+      <c r="Z4" s="47"/>
+      <c r="AA4" s="47"/>
     </row>
     <row r="5" spans="1:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B5" s="58"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="58"/>
-      <c r="L5" s="58"/>
-      <c r="M5" s="58"/>
-      <c r="N5" s="58"/>
-      <c r="O5" s="58"/>
-      <c r="P5" s="58"/>
-      <c r="Q5" s="58"/>
-      <c r="R5" s="58"/>
-      <c r="S5" s="58"/>
-      <c r="T5" s="58"/>
-      <c r="U5" s="58"/>
-      <c r="V5" s="58"/>
-      <c r="W5" s="64"/>
-      <c r="X5" s="64"/>
-      <c r="Y5" s="58"/>
-      <c r="Z5" s="58" t="s">
+      <c r="B5" s="47"/>
+      <c r="C5" s="47"/>
+      <c r="D5" s="47"/>
+      <c r="E5" s="47"/>
+      <c r="F5" s="47"/>
+      <c r="G5" s="47"/>
+      <c r="H5" s="47"/>
+      <c r="I5" s="47"/>
+      <c r="J5" s="47"/>
+      <c r="K5" s="47"/>
+      <c r="L5" s="47"/>
+      <c r="M5" s="47"/>
+      <c r="N5" s="47"/>
+      <c r="O5" s="47"/>
+      <c r="P5" s="47"/>
+      <c r="Q5" s="47"/>
+      <c r="R5" s="47"/>
+      <c r="S5" s="47"/>
+      <c r="T5" s="47"/>
+      <c r="U5" s="47"/>
+      <c r="V5" s="47"/>
+      <c r="W5" s="53"/>
+      <c r="X5" s="53"/>
+      <c r="Y5" s="47"/>
+      <c r="Z5" s="47" t="s">
         <v>30</v>
       </c>
-      <c r="AA5" s="58"/>
+      <c r="AA5" s="47"/>
     </row>
     <row r="6" spans="1:27" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="58"/>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
-      <c r="J6" s="58"/>
-      <c r="K6" s="58"/>
-      <c r="L6" s="58"/>
-      <c r="M6" s="58"/>
-      <c r="N6" s="58"/>
-      <c r="O6" s="58"/>
-      <c r="P6" s="58"/>
-      <c r="Q6" s="58"/>
-      <c r="R6" s="58"/>
-      <c r="S6" s="58"/>
-      <c r="T6" s="58"/>
-      <c r="U6" s="58"/>
-      <c r="V6" s="58"/>
-      <c r="W6" s="64"/>
-      <c r="X6" s="64"/>
-      <c r="Y6" s="58"/>
-      <c r="Z6" s="58"/>
-      <c r="AA6" s="58"/>
+      <c r="B6" s="47"/>
+      <c r="C6" s="47"/>
+      <c r="D6" s="47"/>
+      <c r="E6" s="47"/>
+      <c r="F6" s="47"/>
+      <c r="G6" s="47"/>
+      <c r="H6" s="47"/>
+      <c r="I6" s="47"/>
+      <c r="J6" s="47"/>
+      <c r="K6" s="47"/>
+      <c r="L6" s="47"/>
+      <c r="M6" s="47"/>
+      <c r="N6" s="47"/>
+      <c r="O6" s="47"/>
+      <c r="P6" s="47"/>
+      <c r="Q6" s="47"/>
+      <c r="R6" s="47"/>
+      <c r="S6" s="47"/>
+      <c r="T6" s="47"/>
+      <c r="U6" s="47"/>
+      <c r="V6" s="47"/>
+      <c r="W6" s="53"/>
+      <c r="X6" s="53"/>
+      <c r="Y6" s="47"/>
+      <c r="Z6" s="47"/>
+      <c r="AA6" s="47"/>
     </row>
     <row r="7" spans="1:27" ht="25.2" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="60" t="s">
+      <c r="B7" s="49" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="61" t="s">
+      <c r="C7" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="61" t="s">
+      <c r="D7" s="50" t="s">
         <v>33</v>
       </c>
-      <c r="E7" s="61" t="s">
+      <c r="E7" s="50" t="s">
         <v>34</v>
       </c>
-      <c r="F7" s="61" t="s">
+      <c r="F7" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="G7" s="61" t="s">
+      <c r="G7" s="50" t="s">
         <v>36</v>
       </c>
-      <c r="H7" s="61" t="s">
+      <c r="H7" s="50" t="s">
         <v>37</v>
       </c>
-      <c r="I7" s="61" t="s">
+      <c r="I7" s="50" t="s">
         <v>38</v>
       </c>
-      <c r="J7" s="61" t="s">
+      <c r="J7" s="50" t="s">
         <v>39</v>
       </c>
-      <c r="K7" s="61" t="s">
+      <c r="K7" s="50" t="s">
         <v>40</v>
       </c>
-      <c r="L7" s="61" t="s">
+      <c r="L7" s="50" t="s">
         <v>41</v>
       </c>
-      <c r="M7" s="61" t="s">
+      <c r="M7" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="N7" s="61" t="s">
+      <c r="N7" s="50" t="s">
         <v>42</v>
       </c>
-      <c r="O7" s="61" t="s">
+      <c r="O7" s="50" t="s">
         <v>4</v>
       </c>
-      <c r="P7" s="61" t="s">
+      <c r="P7" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="Q7" s="61" t="s">
+      <c r="Q7" s="50" t="s">
         <v>22</v>
       </c>
-      <c r="R7" s="61" t="s">
+      <c r="R7" s="50" t="s">
         <v>23</v>
       </c>
-      <c r="S7" s="61" t="s">
+      <c r="S7" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="T7" s="61" t="s">
+      <c r="T7" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="U7" s="61" t="s">
+      <c r="U7" s="50" t="s">
         <v>44</v>
       </c>
-      <c r="V7" s="61" t="s">
+      <c r="V7" s="50" t="s">
         <v>18</v>
       </c>
-      <c r="W7" s="63" t="s">
+      <c r="W7" s="52" t="s">
         <v>45</v>
       </c>
-      <c r="X7" s="63" t="s">
+      <c r="X7" s="52" t="s">
         <v>46</v>
       </c>
-      <c r="Y7" s="61" t="s">
+      <c r="Y7" s="50" t="s">
         <v>47</v>
       </c>
-      <c r="Z7" s="61" t="s">
+      <c r="Z7" s="50" t="s">
         <v>228</v>
       </c>
-      <c r="AA7" s="62" t="s">
+      <c r="AA7" s="51" t="s">
         <v>229</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="53"/>
-      <c r="AA8" s="54"/>
+      <c r="B8" s="42"/>
+      <c r="AA8" s="43"/>
     </row>
     <row r="9" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="53"/>
-      <c r="AA9" s="54"/>
+      <c r="B9" s="42"/>
+      <c r="AA9" s="43"/>
     </row>
     <row r="10" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="53"/>
-      <c r="AA10" s="54"/>
+      <c r="B10" s="42"/>
+      <c r="AA10" s="43"/>
     </row>
     <row r="11" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="53"/>
-      <c r="AA11" s="54"/>
+      <c r="B11" s="42"/>
+      <c r="AA11" s="43"/>
     </row>
     <row r="12" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="53"/>
-      <c r="AA12" s="54"/>
+      <c r="B12" s="42"/>
+      <c r="AA12" s="43"/>
     </row>
     <row r="13" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="53"/>
-      <c r="AA13" s="54"/>
+      <c r="B13" s="42"/>
+      <c r="AA13" s="43"/>
     </row>
     <row r="14" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="53"/>
-      <c r="AA14" s="54"/>
+      <c r="B14" s="42"/>
+      <c r="AA14" s="43"/>
     </row>
     <row r="15" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="53"/>
-      <c r="AA15" s="54"/>
+      <c r="B15" s="42"/>
+      <c r="AA15" s="43"/>
     </row>
     <row r="16" spans="1:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="53"/>
-      <c r="AA16" s="54"/>
+      <c r="B16" s="42"/>
+      <c r="AA16" s="43"/>
     </row>
     <row r="17" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="53"/>
-      <c r="AA17" s="54"/>
+      <c r="B17" s="42"/>
+      <c r="AA17" s="43"/>
     </row>
     <row r="18" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="53"/>
-      <c r="AA18" s="54"/>
+      <c r="B18" s="42"/>
+      <c r="AA18" s="43"/>
     </row>
     <row r="19" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="53"/>
-      <c r="AA19" s="54"/>
+      <c r="B19" s="42"/>
+      <c r="AA19" s="43"/>
     </row>
     <row r="20" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="53"/>
-      <c r="AA20" s="54"/>
+      <c r="B20" s="42"/>
+      <c r="AA20" s="43"/>
     </row>
     <row r="21" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="53"/>
-      <c r="AA21" s="54"/>
+      <c r="B21" s="42"/>
+      <c r="AA21" s="43"/>
     </row>
     <row r="22" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="53"/>
-      <c r="AA22" s="54"/>
+      <c r="B22" s="42"/>
+      <c r="AA22" s="43"/>
     </row>
     <row r="23" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="53"/>
-      <c r="AA23" s="54"/>
+      <c r="B23" s="42"/>
+      <c r="AA23" s="43"/>
     </row>
     <row r="24" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="53"/>
-      <c r="AA24" s="54"/>
+      <c r="B24" s="42"/>
+      <c r="AA24" s="43"/>
     </row>
     <row r="25" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B25" s="53"/>
-      <c r="AA25" s="54"/>
+      <c r="B25" s="42"/>
+      <c r="AA25" s="43"/>
     </row>
     <row r="26" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="53"/>
-      <c r="AA26" s="54"/>
+      <c r="B26" s="42"/>
+      <c r="AA26" s="43"/>
     </row>
     <row r="27" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B27" s="53"/>
-      <c r="AA27" s="54"/>
+      <c r="B27" s="42"/>
+      <c r="AA27" s="43"/>
     </row>
     <row r="28" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="53"/>
-      <c r="AA28" s="54"/>
+      <c r="B28" s="42"/>
+      <c r="AA28" s="43"/>
     </row>
     <row r="29" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="53"/>
-      <c r="AA29" s="54"/>
+      <c r="B29" s="42"/>
+      <c r="AA29" s="43"/>
     </row>
     <row r="30" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="53"/>
-      <c r="AA30" s="54"/>
+      <c r="B30" s="42"/>
+      <c r="AA30" s="43"/>
     </row>
     <row r="31" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="53"/>
-      <c r="AA31" s="54"/>
+      <c r="B31" s="42"/>
+      <c r="AA31" s="43"/>
     </row>
     <row r="32" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="53"/>
-      <c r="AA32" s="54"/>
+      <c r="B32" s="42"/>
+      <c r="AA32" s="43"/>
     </row>
     <row r="33" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="53"/>
-      <c r="AA33" s="54"/>
+      <c r="B33" s="42"/>
+      <c r="AA33" s="43"/>
     </row>
     <row r="34" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="53"/>
-      <c r="AA34" s="54"/>
+      <c r="B34" s="42"/>
+      <c r="AA34" s="43"/>
     </row>
     <row r="35" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="53"/>
-      <c r="AA35" s="54"/>
+      <c r="B35" s="42"/>
+      <c r="AA35" s="43"/>
     </row>
     <row r="36" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="53"/>
-      <c r="AA36" s="54"/>
+      <c r="B36" s="42"/>
+      <c r="AA36" s="43"/>
     </row>
     <row r="37" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B37" s="53"/>
-      <c r="AA37" s="54"/>
+      <c r="B37" s="42"/>
+      <c r="AA37" s="43"/>
     </row>
     <row r="38" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="53"/>
-      <c r="AA38" s="54"/>
+      <c r="B38" s="42"/>
+      <c r="AA38" s="43"/>
     </row>
     <row r="39" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B39" s="53"/>
-      <c r="AA39" s="54"/>
+      <c r="B39" s="42"/>
+      <c r="AA39" s="43"/>
     </row>
     <row r="40" spans="2:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="53"/>
-      <c r="AA40" s="54"/>
+      <c r="B40" s="42"/>
+      <c r="AA40" s="43"/>
     </row>
     <row r="41" spans="2:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="53"/>
-      <c r="AA41" s="54"/>
+      <c r="B41" s="42"/>
+      <c r="AA41" s="43"/>
     </row>
     <row r="42" spans="2:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="53"/>
-      <c r="AA42" s="54"/>
+      <c r="B42" s="42"/>
+      <c r="AA42" s="43"/>
     </row>
     <row r="43" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="53"/>
-      <c r="AA43" s="54"/>
+      <c r="B43" s="42"/>
+      <c r="AA43" s="43"/>
     </row>
     <row r="44" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="53"/>
-      <c r="AA44" s="54"/>
+      <c r="B44" s="42"/>
+      <c r="AA44" s="43"/>
     </row>
     <row r="45" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="53"/>
-      <c r="AA45" s="54"/>
+      <c r="B45" s="42"/>
+      <c r="AA45" s="43"/>
     </row>
     <row r="46" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="53"/>
-      <c r="AA46" s="54"/>
+      <c r="B46" s="42"/>
+      <c r="AA46" s="43"/>
     </row>
     <row r="47" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B47" s="53"/>
-      <c r="AA47" s="54"/>
+      <c r="B47" s="42"/>
+      <c r="AA47" s="43"/>
     </row>
     <row r="48" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B48" s="53"/>
-      <c r="AA48" s="54"/>
+      <c r="B48" s="42"/>
+      <c r="AA48" s="43"/>
     </row>
     <row r="49" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B49" s="53"/>
-      <c r="AA49" s="54"/>
+      <c r="B49" s="42"/>
+      <c r="AA49" s="43"/>
     </row>
     <row r="50" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B50" s="53"/>
-      <c r="AA50" s="54"/>
+      <c r="B50" s="42"/>
+      <c r="AA50" s="43"/>
     </row>
     <row r="51" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="53"/>
-      <c r="AA51" s="54"/>
+      <c r="B51" s="42"/>
+      <c r="AA51" s="43"/>
     </row>
     <row r="52" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="53"/>
-      <c r="AA52" s="54"/>
+      <c r="B52" s="42"/>
+      <c r="AA52" s="43"/>
     </row>
     <row r="53" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="53"/>
-      <c r="AA53" s="54"/>
+      <c r="B53" s="42"/>
+      <c r="AA53" s="43"/>
     </row>
     <row r="54" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B54" s="53"/>
-      <c r="AA54" s="54"/>
+      <c r="B54" s="42"/>
+      <c r="AA54" s="43"/>
     </row>
     <row r="55" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B55" s="53"/>
-      <c r="AA55" s="54"/>
+      <c r="B55" s="42"/>
+      <c r="AA55" s="43"/>
     </row>
     <row r="56" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B56" s="53"/>
-      <c r="AA56" s="54"/>
+      <c r="B56" s="42"/>
+      <c r="AA56" s="43"/>
     </row>
     <row r="57" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B57" s="53"/>
-      <c r="AA57" s="54"/>
+      <c r="B57" s="42"/>
+      <c r="AA57" s="43"/>
     </row>
     <row r="58" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B58" s="53"/>
-      <c r="AA58" s="54"/>
+      <c r="B58" s="42"/>
+      <c r="AA58" s="43"/>
     </row>
     <row r="59" spans="2:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="53"/>
-      <c r="AA59" s="54"/>
+      <c r="B59" s="42"/>
+      <c r="AA59" s="43"/>
     </row>
     <row r="60" spans="2:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B60" s="53"/>
-      <c r="AA60" s="54"/>
+      <c r="B60" s="42"/>
+      <c r="AA60" s="43"/>
     </row>
     <row r="61" spans="2:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="53"/>
-      <c r="AA61" s="54"/>
+      <c r="B61" s="42"/>
+      <c r="AA61" s="43"/>
     </row>
     <row r="62" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="53"/>
-      <c r="AA62" s="54"/>
+      <c r="B62" s="42"/>
+      <c r="AA62" s="43"/>
     </row>
     <row r="63" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="53"/>
-      <c r="AA63" s="54"/>
+      <c r="B63" s="42"/>
+      <c r="AA63" s="43"/>
     </row>
     <row r="64" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B64" s="53"/>
-      <c r="AA64" s="54"/>
+      <c r="B64" s="42"/>
+      <c r="AA64" s="43"/>
     </row>
     <row r="65" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="53"/>
-      <c r="AA65" s="54"/>
+      <c r="B65" s="42"/>
+      <c r="AA65" s="43"/>
     </row>
     <row r="66" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B66" s="53"/>
-      <c r="AA66" s="54"/>
+      <c r="B66" s="42"/>
+      <c r="AA66" s="43"/>
     </row>
     <row r="67" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B67" s="53"/>
-      <c r="AA67" s="54"/>
+      <c r="B67" s="42"/>
+      <c r="AA67" s="43"/>
     </row>
     <row r="68" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B68" s="53"/>
-      <c r="AA68" s="54"/>
+      <c r="B68" s="42"/>
+      <c r="AA68" s="43"/>
     </row>
     <row r="69" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="53"/>
-      <c r="AA69" s="54"/>
+      <c r="B69" s="42"/>
+      <c r="AA69" s="43"/>
     </row>
     <row r="70" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="53"/>
-      <c r="AA70" s="54"/>
+      <c r="B70" s="42"/>
+      <c r="AA70" s="43"/>
     </row>
     <row r="71" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="53"/>
-      <c r="AA71" s="54"/>
+      <c r="B71" s="42"/>
+      <c r="AA71" s="43"/>
     </row>
     <row r="72" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="53"/>
-      <c r="AA72" s="54"/>
+      <c r="B72" s="42"/>
+      <c r="AA72" s="43"/>
     </row>
     <row r="73" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="53"/>
-      <c r="AA73" s="54"/>
+      <c r="B73" s="42"/>
+      <c r="AA73" s="43"/>
     </row>
     <row r="74" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="53"/>
-      <c r="AA74" s="54"/>
+      <c r="B74" s="42"/>
+      <c r="AA74" s="43"/>
     </row>
     <row r="75" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="53"/>
-      <c r="AA75" s="54"/>
+      <c r="B75" s="42"/>
+      <c r="AA75" s="43"/>
     </row>
     <row r="76" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B76" s="53"/>
-      <c r="AA76" s="54"/>
+      <c r="B76" s="42"/>
+      <c r="AA76" s="43"/>
     </row>
     <row r="77" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="53"/>
-      <c r="AA77" s="54"/>
+      <c r="B77" s="42"/>
+      <c r="AA77" s="43"/>
     </row>
     <row r="78" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B78" s="53"/>
-      <c r="AA78" s="54"/>
+      <c r="B78" s="42"/>
+      <c r="AA78" s="43"/>
     </row>
     <row r="79" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B79" s="53"/>
-      <c r="AA79" s="54"/>
+      <c r="B79" s="42"/>
+      <c r="AA79" s="43"/>
     </row>
     <row r="80" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B80" s="53"/>
-      <c r="AA80" s="54"/>
+      <c r="B80" s="42"/>
+      <c r="AA80" s="43"/>
     </row>
     <row r="81" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="53"/>
-      <c r="AA81" s="54"/>
+      <c r="B81" s="42"/>
+      <c r="AA81" s="43"/>
     </row>
     <row r="82" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="53"/>
-      <c r="AA82" s="54"/>
+      <c r="B82" s="42"/>
+      <c r="AA82" s="43"/>
     </row>
     <row r="83" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="53"/>
-      <c r="AA83" s="54"/>
+      <c r="B83" s="42"/>
+      <c r="AA83" s="43"/>
     </row>
     <row r="84" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="53"/>
-      <c r="AA84" s="54"/>
+      <c r="B84" s="42"/>
+      <c r="AA84" s="43"/>
     </row>
     <row r="85" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="53"/>
-      <c r="AA85" s="54"/>
+      <c r="B85" s="42"/>
+      <c r="AA85" s="43"/>
     </row>
     <row r="86" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="53"/>
-      <c r="AA86" s="54"/>
+      <c r="B86" s="42"/>
+      <c r="AA86" s="43"/>
     </row>
     <row r="87" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="53"/>
-      <c r="AA87" s="54"/>
+      <c r="B87" s="42"/>
+      <c r="AA87" s="43"/>
     </row>
     <row r="88" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B88" s="53"/>
-      <c r="AA88" s="54"/>
+      <c r="B88" s="42"/>
+      <c r="AA88" s="43"/>
     </row>
     <row r="89" spans="2:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="53"/>
-      <c r="AA89" s="54"/>
+      <c r="B89" s="42"/>
+      <c r="AA89" s="43"/>
     </row>
     <row r="90" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B90" s="53"/>
-      <c r="AA90" s="54"/>
+      <c r="B90" s="42"/>
+      <c r="AA90" s="43"/>
     </row>
     <row r="91" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B91" s="53"/>
-      <c r="AA91" s="54"/>
+      <c r="B91" s="42"/>
+      <c r="AA91" s="43"/>
     </row>
     <row r="92" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B92" s="53"/>
-      <c r="AA92" s="54"/>
+      <c r="B92" s="42"/>
+      <c r="AA92" s="43"/>
     </row>
     <row r="93" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="53"/>
-      <c r="AA93" s="54"/>
+      <c r="B93" s="42"/>
+      <c r="AA93" s="43"/>
     </row>
     <row r="94" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B94" s="53"/>
-      <c r="AA94" s="54"/>
+      <c r="B94" s="42"/>
+      <c r="AA94" s="43"/>
     </row>
     <row r="95" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="53"/>
-      <c r="AA95" s="54"/>
+      <c r="B95" s="42"/>
+      <c r="AA95" s="43"/>
     </row>
     <row r="96" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B96" s="53"/>
-      <c r="AA96" s="54"/>
+      <c r="B96" s="42"/>
+      <c r="AA96" s="43"/>
     </row>
     <row r="97" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B97" s="53"/>
-      <c r="AA97" s="54"/>
+      <c r="B97" s="42"/>
+      <c r="AA97" s="43"/>
     </row>
     <row r="98" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B98" s="53"/>
-      <c r="AA98" s="54"/>
+      <c r="B98" s="42"/>
+      <c r="AA98" s="43"/>
     </row>
     <row r="99" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B99" s="53"/>
-      <c r="AA99" s="54"/>
+      <c r="B99" s="42"/>
+      <c r="AA99" s="43"/>
     </row>
     <row r="100" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B100" s="53"/>
-      <c r="AA100" s="54"/>
+      <c r="B100" s="42"/>
+      <c r="AA100" s="43"/>
     </row>
     <row r="101" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B101" s="53"/>
-      <c r="AA101" s="54"/>
+      <c r="B101" s="42"/>
+      <c r="AA101" s="43"/>
     </row>
     <row r="102" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B102" s="53"/>
-      <c r="AA102" s="54"/>
+      <c r="B102" s="42"/>
+      <c r="AA102" s="43"/>
     </row>
     <row r="103" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B103" s="53"/>
-      <c r="AA103" s="54"/>
+      <c r="B103" s="42"/>
+      <c r="AA103" s="43"/>
     </row>
     <row r="104" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B104" s="53"/>
-      <c r="AA104" s="54"/>
+      <c r="B104" s="42"/>
+      <c r="AA104" s="43"/>
     </row>
     <row r="105" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B105" s="53"/>
-      <c r="AA105" s="54"/>
+      <c r="B105" s="42"/>
+      <c r="AA105" s="43"/>
     </row>
     <row r="106" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="53"/>
-      <c r="AA106" s="54"/>
+      <c r="B106" s="42"/>
+      <c r="AA106" s="43"/>
     </row>
     <row r="107" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B107" s="53"/>
-      <c r="AA107" s="54"/>
+      <c r="B107" s="42"/>
+      <c r="AA107" s="43"/>
     </row>
     <row r="108" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B108" s="53"/>
-      <c r="AA108" s="54"/>
+      <c r="B108" s="42"/>
+      <c r="AA108" s="43"/>
     </row>
     <row r="109" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B109" s="53"/>
-      <c r="AA109" s="54"/>
+      <c r="B109" s="42"/>
+      <c r="AA109" s="43"/>
     </row>
     <row r="110" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B110" s="53"/>
-      <c r="AA110" s="54"/>
+      <c r="B110" s="42"/>
+      <c r="AA110" s="43"/>
     </row>
     <row r="111" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B111" s="53"/>
-      <c r="AA111" s="54"/>
+      <c r="B111" s="42"/>
+      <c r="AA111" s="43"/>
     </row>
     <row r="112" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B112" s="53"/>
-      <c r="AA112" s="54"/>
+      <c r="B112" s="42"/>
+      <c r="AA112" s="43"/>
     </row>
     <row r="113" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B113" s="53"/>
-      <c r="AA113" s="54"/>
+      <c r="B113" s="42"/>
+      <c r="AA113" s="43"/>
     </row>
     <row r="114" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B114" s="53"/>
-      <c r="AA114" s="54"/>
+      <c r="B114" s="42"/>
+      <c r="AA114" s="43"/>
     </row>
     <row r="115" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B115" s="53"/>
-      <c r="AA115" s="54"/>
+      <c r="B115" s="42"/>
+      <c r="AA115" s="43"/>
     </row>
     <row r="116" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B116" s="53"/>
-      <c r="AA116" s="54"/>
+      <c r="B116" s="42"/>
+      <c r="AA116" s="43"/>
     </row>
     <row r="117" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B117" s="53"/>
-      <c r="AA117" s="54"/>
+      <c r="B117" s="42"/>
+      <c r="AA117" s="43"/>
     </row>
     <row r="118" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B118" s="53"/>
-      <c r="AA118" s="54"/>
+      <c r="B118" s="42"/>
+      <c r="AA118" s="43"/>
     </row>
     <row r="119" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B119" s="53"/>
-      <c r="AA119" s="54"/>
+      <c r="B119" s="42"/>
+      <c r="AA119" s="43"/>
     </row>
     <row r="120" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="53"/>
-      <c r="AA120" s="54"/>
+      <c r="B120" s="42"/>
+      <c r="AA120" s="43"/>
     </row>
     <row r="121" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B121" s="53"/>
-      <c r="AA121" s="54"/>
+      <c r="B121" s="42"/>
+      <c r="AA121" s="43"/>
     </row>
     <row r="122" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B122" s="53"/>
-      <c r="AA122" s="54"/>
+      <c r="B122" s="42"/>
+      <c r="AA122" s="43"/>
     </row>
     <row r="123" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="53"/>
-      <c r="AA123" s="54"/>
+      <c r="B123" s="42"/>
+      <c r="AA123" s="43"/>
     </row>
     <row r="124" spans="2:27" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="53"/>
-      <c r="AA124" s="54"/>
+      <c r="B124" s="42"/>
+      <c r="AA124" s="43"/>
     </row>
     <row r="125" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="53"/>
-      <c r="AA125" s="54"/>
+      <c r="B125" s="42"/>
+      <c r="AA125" s="43"/>
     </row>
     <row r="126" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B126" s="53"/>
-      <c r="AA126" s="54"/>
+      <c r="B126" s="42"/>
+      <c r="AA126" s="43"/>
     </row>
     <row r="127" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B127" s="53"/>
-      <c r="AA127" s="54"/>
+      <c r="B127" s="42"/>
+      <c r="AA127" s="43"/>
     </row>
     <row r="128" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B128" s="53"/>
-      <c r="AA128" s="54"/>
+      <c r="B128" s="42"/>
+      <c r="AA128" s="43"/>
     </row>
     <row r="129" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B129" s="53"/>
-      <c r="AA129" s="54"/>
+      <c r="B129" s="42"/>
+      <c r="AA129" s="43"/>
     </row>
     <row r="130" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B130" s="53"/>
-      <c r="AA130" s="54"/>
+      <c r="B130" s="42"/>
+      <c r="AA130" s="43"/>
     </row>
     <row r="131" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B131" s="53"/>
-      <c r="AA131" s="54"/>
+      <c r="B131" s="42"/>
+      <c r="AA131" s="43"/>
     </row>
     <row r="132" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B132" s="53"/>
-      <c r="AA132" s="54"/>
+      <c r="B132" s="42"/>
+      <c r="AA132" s="43"/>
     </row>
     <row r="133" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B133" s="53"/>
-      <c r="AA133" s="54"/>
+      <c r="B133" s="42"/>
+      <c r="AA133" s="43"/>
     </row>
     <row r="134" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B134" s="53"/>
-      <c r="AA134" s="54"/>
+      <c r="B134" s="42"/>
+      <c r="AA134" s="43"/>
     </row>
     <row r="135" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B135" s="53"/>
-      <c r="AA135" s="54"/>
+      <c r="B135" s="42"/>
+      <c r="AA135" s="43"/>
     </row>
     <row r="136" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B136" s="53"/>
-      <c r="AA136" s="54"/>
+      <c r="B136" s="42"/>
+      <c r="AA136" s="43"/>
     </row>
     <row r="137" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B137" s="53"/>
-      <c r="AA137" s="54"/>
+      <c r="B137" s="42"/>
+      <c r="AA137" s="43"/>
     </row>
     <row r="138" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B138" s="53"/>
-      <c r="AA138" s="54"/>
+      <c r="B138" s="42"/>
+      <c r="AA138" s="43"/>
     </row>
     <row r="139" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B139" s="53"/>
-      <c r="AA139" s="54"/>
+      <c r="B139" s="42"/>
+      <c r="AA139" s="43"/>
     </row>
     <row r="140" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B140" s="53"/>
-      <c r="AA140" s="54"/>
+      <c r="B140" s="42"/>
+      <c r="AA140" s="43"/>
     </row>
     <row r="141" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B141" s="53"/>
-      <c r="AA141" s="54"/>
+      <c r="B141" s="42"/>
+      <c r="AA141" s="43"/>
     </row>
     <row r="142" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B142" s="53"/>
-      <c r="AA142" s="54"/>
+      <c r="B142" s="42"/>
+      <c r="AA142" s="43"/>
     </row>
     <row r="143" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B143" s="53"/>
-      <c r="AA143" s="54"/>
+      <c r="B143" s="42"/>
+      <c r="AA143" s="43"/>
     </row>
     <row r="144" spans="2:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B144" s="53"/>
-      <c r="AA144" s="54"/>
+      <c r="B144" s="42"/>
+      <c r="AA144" s="43"/>
     </row>
     <row r="145" spans="2:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B145" s="53"/>
-      <c r="AA145" s="54"/>
+      <c r="B145" s="42"/>
+      <c r="AA145" s="43"/>
     </row>
     <row r="146" spans="2:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B146" s="53"/>
-      <c r="AA146" s="54"/>
+      <c r="B146" s="42"/>
+      <c r="AA146" s="43"/>
     </row>
     <row r="147" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B147" s="53"/>
-      <c r="AA147" s="54"/>
+      <c r="B147" s="42"/>
+      <c r="AA147" s="43"/>
     </row>
     <row r="148" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B148" s="53"/>
-      <c r="AA148" s="54"/>
+      <c r="B148" s="42"/>
+      <c r="AA148" s="43"/>
     </row>
     <row r="149" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B149" s="53"/>
-      <c r="AA149" s="54"/>
+      <c r="B149" s="42"/>
+      <c r="AA149" s="43"/>
     </row>
     <row r="150" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B150" s="53"/>
-      <c r="AA150" s="54"/>
+      <c r="B150" s="42"/>
+      <c r="AA150" s="43"/>
     </row>
     <row r="151" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B151" s="53"/>
-      <c r="AA151" s="54"/>
+      <c r="B151" s="42"/>
+      <c r="AA151" s="43"/>
     </row>
     <row r="152" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B152" s="53"/>
-      <c r="AA152" s="54"/>
+      <c r="B152" s="42"/>
+      <c r="AA152" s="43"/>
     </row>
     <row r="153" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B153" s="53"/>
-      <c r="AA153" s="54"/>
+      <c r="B153" s="42"/>
+      <c r="AA153" s="43"/>
     </row>
     <row r="154" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B154" s="53"/>
-      <c r="AA154" s="54"/>
+      <c r="B154" s="42"/>
+      <c r="AA154" s="43"/>
     </row>
     <row r="155" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B155" s="53"/>
-      <c r="AA155" s="54"/>
+      <c r="B155" s="42"/>
+      <c r="AA155" s="43"/>
     </row>
     <row r="156" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B156" s="53"/>
-      <c r="AA156" s="54"/>
+      <c r="B156" s="42"/>
+      <c r="AA156" s="43"/>
     </row>
     <row r="157" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B157" s="53"/>
-      <c r="AA157" s="54"/>
+      <c r="B157" s="42"/>
+      <c r="AA157" s="43"/>
     </row>
     <row r="158" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B158" s="53"/>
-      <c r="AA158" s="54"/>
+      <c r="B158" s="42"/>
+      <c r="AA158" s="43"/>
     </row>
     <row r="159" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B159" s="53"/>
-      <c r="AA159" s="54"/>
+      <c r="B159" s="42"/>
+      <c r="AA159" s="43"/>
     </row>
     <row r="160" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B160" s="53"/>
-      <c r="AA160" s="54"/>
+      <c r="B160" s="42"/>
+      <c r="AA160" s="43"/>
     </row>
     <row r="161" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B161" s="53"/>
-      <c r="AA161" s="54"/>
+      <c r="B161" s="42"/>
+      <c r="AA161" s="43"/>
     </row>
     <row r="162" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B162" s="53"/>
-      <c r="AA162" s="54"/>
+      <c r="B162" s="42"/>
+      <c r="AA162" s="43"/>
     </row>
     <row r="163" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B163" s="53"/>
-      <c r="AA163" s="54"/>
+      <c r="B163" s="42"/>
+      <c r="AA163" s="43"/>
     </row>
     <row r="164" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B164" s="53"/>
-      <c r="AA164" s="54"/>
+      <c r="B164" s="42"/>
+      <c r="AA164" s="43"/>
     </row>
     <row r="165" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B165" s="53"/>
-      <c r="AA165" s="54"/>
+      <c r="B165" s="42"/>
+      <c r="AA165" s="43"/>
     </row>
     <row r="166" spans="2:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B166" s="53"/>
-      <c r="AA166" s="54"/>
+      <c r="B166" s="42"/>
+      <c r="AA166" s="43"/>
     </row>
     <row r="167" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B167" s="53"/>
-      <c r="AA167" s="54"/>
+      <c r="B167" s="42"/>
+      <c r="AA167" s="43"/>
     </row>
     <row r="168" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B168" s="53"/>
-      <c r="AA168" s="54"/>
+      <c r="B168" s="42"/>
+      <c r="AA168" s="43"/>
     </row>
     <row r="169" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B169" s="53"/>
-      <c r="AA169" s="54"/>
+      <c r="B169" s="42"/>
+      <c r="AA169" s="43"/>
     </row>
     <row r="170" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B170" s="53"/>
-      <c r="AA170" s="54"/>
+      <c r="B170" s="42"/>
+      <c r="AA170" s="43"/>
     </row>
     <row r="171" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B171" s="53"/>
-      <c r="AA171" s="54"/>
+      <c r="B171" s="42"/>
+      <c r="AA171" s="43"/>
     </row>
     <row r="172" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B172" s="53"/>
-      <c r="AA172" s="54"/>
+      <c r="B172" s="42"/>
+      <c r="AA172" s="43"/>
     </row>
     <row r="173" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B173" s="53"/>
-      <c r="AA173" s="54"/>
+      <c r="B173" s="42"/>
+      <c r="AA173" s="43"/>
     </row>
     <row r="174" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B174" s="53"/>
-      <c r="AA174" s="54"/>
+      <c r="B174" s="42"/>
+      <c r="AA174" s="43"/>
     </row>
     <row r="175" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B175" s="53"/>
-      <c r="AA175" s="54"/>
+      <c r="B175" s="42"/>
+      <c r="AA175" s="43"/>
     </row>
     <row r="176" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B176" s="53"/>
-      <c r="AA176" s="54"/>
+      <c r="B176" s="42"/>
+      <c r="AA176" s="43"/>
     </row>
     <row r="177" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B177" s="53"/>
-      <c r="AA177" s="54"/>
+      <c r="B177" s="42"/>
+      <c r="AA177" s="43"/>
     </row>
     <row r="178" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B178" s="53"/>
-      <c r="AA178" s="54"/>
+      <c r="B178" s="42"/>
+      <c r="AA178" s="43"/>
     </row>
     <row r="179" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B179" s="53"/>
-      <c r="AA179" s="54"/>
+      <c r="B179" s="42"/>
+      <c r="AA179" s="43"/>
     </row>
     <row r="180" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B180" s="53"/>
-      <c r="AA180" s="54"/>
+      <c r="B180" s="42"/>
+      <c r="AA180" s="43"/>
     </row>
     <row r="181" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B181" s="53"/>
-      <c r="AA181" s="54"/>
+      <c r="B181" s="42"/>
+      <c r="AA181" s="43"/>
     </row>
     <row r="182" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B182" s="53"/>
-      <c r="AA182" s="54"/>
+      <c r="B182" s="42"/>
+      <c r="AA182" s="43"/>
     </row>
     <row r="183" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B183" s="53"/>
-      <c r="AA183" s="54"/>
+      <c r="B183" s="42"/>
+      <c r="AA183" s="43"/>
     </row>
     <row r="184" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B184" s="53"/>
-      <c r="AA184" s="54"/>
+      <c r="B184" s="42"/>
+      <c r="AA184" s="43"/>
     </row>
     <row r="185" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B185" s="53"/>
-      <c r="AA185" s="54"/>
+      <c r="B185" s="42"/>
+      <c r="AA185" s="43"/>
     </row>
     <row r="186" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B186" s="53"/>
-      <c r="AA186" s="54"/>
+      <c r="B186" s="42"/>
+      <c r="AA186" s="43"/>
     </row>
     <row r="187" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B187" s="53"/>
-      <c r="AA187" s="54"/>
+      <c r="B187" s="42"/>
+      <c r="AA187" s="43"/>
     </row>
     <row r="188" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B188" s="53"/>
-      <c r="AA188" s="54"/>
+      <c r="B188" s="42"/>
+      <c r="AA188" s="43"/>
     </row>
     <row r="189" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B189" s="53"/>
-      <c r="AA189" s="54"/>
+      <c r="B189" s="42"/>
+      <c r="AA189" s="43"/>
     </row>
     <row r="190" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B190" s="53"/>
-      <c r="AA190" s="54"/>
+      <c r="B190" s="42"/>
+      <c r="AA190" s="43"/>
     </row>
     <row r="191" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B191" s="53"/>
-      <c r="AA191" s="54"/>
+      <c r="B191" s="42"/>
+      <c r="AA191" s="43"/>
     </row>
     <row r="192" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B192" s="53"/>
-      <c r="AA192" s="54"/>
+      <c r="B192" s="42"/>
+      <c r="AA192" s="43"/>
     </row>
     <row r="193" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B193" s="53"/>
-      <c r="AA193" s="54"/>
+      <c r="B193" s="42"/>
+      <c r="AA193" s="43"/>
     </row>
     <row r="194" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B194" s="53"/>
-      <c r="AA194" s="54"/>
+      <c r="B194" s="42"/>
+      <c r="AA194" s="43"/>
     </row>
     <row r="195" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B195" s="53"/>
-      <c r="AA195" s="54"/>
+      <c r="B195" s="42"/>
+      <c r="AA195" s="43"/>
     </row>
     <row r="196" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B196" s="53"/>
-      <c r="AA196" s="54"/>
+      <c r="B196" s="42"/>
+      <c r="AA196" s="43"/>
     </row>
     <row r="197" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B197" s="53"/>
-      <c r="AA197" s="54"/>
+      <c r="B197" s="42"/>
+      <c r="AA197" s="43"/>
     </row>
     <row r="198" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B198" s="53"/>
-      <c r="AA198" s="54"/>
+      <c r="B198" s="42"/>
+      <c r="AA198" s="43"/>
     </row>
     <row r="199" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B199" s="53"/>
-      <c r="AA199" s="54"/>
+      <c r="B199" s="42"/>
+      <c r="AA199" s="43"/>
     </row>
     <row r="200" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B200" s="53"/>
-      <c r="AA200" s="54"/>
+      <c r="B200" s="42"/>
+      <c r="AA200" s="43"/>
     </row>
     <row r="201" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B201" s="53"/>
-      <c r="AA201" s="54"/>
+      <c r="B201" s="42"/>
+      <c r="AA201" s="43"/>
     </row>
     <row r="202" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B202" s="53"/>
-      <c r="AA202" s="54"/>
+      <c r="B202" s="42"/>
+      <c r="AA202" s="43"/>
     </row>
     <row r="203" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B203" s="53"/>
-      <c r="AA203" s="54"/>
+      <c r="B203" s="42"/>
+      <c r="AA203" s="43"/>
     </row>
     <row r="204" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B204" s="53"/>
-      <c r="AA204" s="54"/>
+      <c r="B204" s="42"/>
+      <c r="AA204" s="43"/>
     </row>
     <row r="205" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B205" s="53"/>
-      <c r="AA205" s="54"/>
+      <c r="B205" s="42"/>
+      <c r="AA205" s="43"/>
     </row>
     <row r="206" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B206" s="53"/>
-      <c r="AA206" s="54"/>
+      <c r="B206" s="42"/>
+      <c r="AA206" s="43"/>
     </row>
     <row r="207" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B207" s="53"/>
-      <c r="AA207" s="54"/>
+      <c r="B207" s="42"/>
+      <c r="AA207" s="43"/>
     </row>
     <row r="208" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B208" s="53"/>
-      <c r="AA208" s="54"/>
+      <c r="B208" s="42"/>
+      <c r="AA208" s="43"/>
     </row>
     <row r="209" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B209" s="53"/>
-      <c r="AA209" s="54"/>
+      <c r="B209" s="42"/>
+      <c r="AA209" s="43"/>
     </row>
     <row r="210" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B210" s="53"/>
-      <c r="AA210" s="54"/>
+      <c r="B210" s="42"/>
+      <c r="AA210" s="43"/>
     </row>
     <row r="211" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B211" s="53"/>
-      <c r="AA211" s="54"/>
+      <c r="B211" s="42"/>
+      <c r="AA211" s="43"/>
     </row>
     <row r="212" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B212" s="53"/>
-      <c r="AA212" s="54"/>
+      <c r="B212" s="42"/>
+      <c r="AA212" s="43"/>
     </row>
     <row r="213" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B213" s="53"/>
-      <c r="AA213" s="54"/>
+      <c r="B213" s="42"/>
+      <c r="AA213" s="43"/>
     </row>
     <row r="214" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B214" s="53"/>
-      <c r="AA214" s="54"/>
+      <c r="B214" s="42"/>
+      <c r="AA214" s="43"/>
     </row>
     <row r="215" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B215" s="53"/>
-      <c r="AA215" s="54"/>
+      <c r="B215" s="42"/>
+      <c r="AA215" s="43"/>
     </row>
     <row r="216" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B216" s="53"/>
-      <c r="AA216" s="54"/>
+      <c r="B216" s="42"/>
+      <c r="AA216" s="43"/>
     </row>
     <row r="217" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B217" s="53"/>
-      <c r="AA217" s="54"/>
+      <c r="B217" s="42"/>
+      <c r="AA217" s="43"/>
     </row>
     <row r="218" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B218" s="53"/>
-      <c r="AA218" s="54"/>
+      <c r="B218" s="42"/>
+      <c r="AA218" s="43"/>
     </row>
     <row r="219" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B219" s="53"/>
-      <c r="AA219" s="54"/>
+      <c r="B219" s="42"/>
+      <c r="AA219" s="43"/>
     </row>
     <row r="220" spans="2:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B220" s="53"/>
-      <c r="AA220" s="54"/>
+      <c r="B220" s="42"/>
+      <c r="AA220" s="43"/>
     </row>
     <row r="221" spans="2:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B221" s="53"/>
-      <c r="AA221" s="54"/>
+      <c r="B221" s="42"/>
+      <c r="AA221" s="43"/>
     </row>
     <row r="222" spans="2:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B222" s="53"/>
-      <c r="AA222" s="54"/>
+      <c r="B222" s="42"/>
+      <c r="AA222" s="43"/>
     </row>
     <row r="223" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B223" s="53"/>
-      <c r="AA223" s="54"/>
+      <c r="B223" s="42"/>
+      <c r="AA223" s="43"/>
     </row>
     <row r="224" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B224" s="53"/>
-      <c r="AA224" s="54"/>
+      <c r="B224" s="42"/>
+      <c r="AA224" s="43"/>
     </row>
     <row r="225" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B225" s="53"/>
-      <c r="AA225" s="54"/>
+      <c r="B225" s="42"/>
+      <c r="AA225" s="43"/>
     </row>
     <row r="226" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B226" s="53"/>
-      <c r="AA226" s="54"/>
+      <c r="B226" s="42"/>
+      <c r="AA226" s="43"/>
     </row>
     <row r="227" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B227" s="53"/>
-      <c r="AA227" s="54"/>
+      <c r="B227" s="42"/>
+      <c r="AA227" s="43"/>
     </row>
     <row r="228" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B228" s="53"/>
-      <c r="AA228" s="54"/>
+      <c r="B228" s="42"/>
+      <c r="AA228" s="43"/>
     </row>
     <row r="229" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B229" s="53"/>
-      <c r="AA229" s="54"/>
+      <c r="B229" s="42"/>
+      <c r="AA229" s="43"/>
     </row>
     <row r="230" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B230" s="53"/>
-      <c r="AA230" s="54"/>
+      <c r="B230" s="42"/>
+      <c r="AA230" s="43"/>
     </row>
     <row r="231" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B231" s="53"/>
-      <c r="AA231" s="54"/>
+      <c r="B231" s="42"/>
+      <c r="AA231" s="43"/>
     </row>
     <row r="232" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B232" s="53"/>
-      <c r="AA232" s="54"/>
+      <c r="B232" s="42"/>
+      <c r="AA232" s="43"/>
     </row>
     <row r="233" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B233" s="53"/>
-      <c r="AA233" s="54"/>
+      <c r="B233" s="42"/>
+      <c r="AA233" s="43"/>
     </row>
     <row r="234" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B234" s="53"/>
-      <c r="AA234" s="54"/>
+      <c r="B234" s="42"/>
+      <c r="AA234" s="43"/>
     </row>
     <row r="235" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B235" s="53"/>
-      <c r="AA235" s="54"/>
+      <c r="B235" s="42"/>
+      <c r="AA235" s="43"/>
     </row>
     <row r="236" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B236" s="53"/>
-      <c r="AA236" s="54"/>
+      <c r="B236" s="42"/>
+      <c r="AA236" s="43"/>
     </row>
     <row r="237" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B237" s="53"/>
-      <c r="AA237" s="54"/>
+      <c r="B237" s="42"/>
+      <c r="AA237" s="43"/>
     </row>
     <row r="238" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B238" s="53"/>
-      <c r="AA238" s="54"/>
+      <c r="B238" s="42"/>
+      <c r="AA238" s="43"/>
     </row>
     <row r="239" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B239" s="53"/>
-      <c r="AA239" s="54"/>
+      <c r="B239" s="42"/>
+      <c r="AA239" s="43"/>
     </row>
     <row r="240" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B240" s="53"/>
-      <c r="AA240" s="54"/>
+      <c r="B240" s="42"/>
+      <c r="AA240" s="43"/>
     </row>
     <row r="241" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B241" s="53"/>
-      <c r="AA241" s="54"/>
+      <c r="B241" s="42"/>
+      <c r="AA241" s="43"/>
     </row>
     <row r="242" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B242" s="53"/>
-      <c r="AA242" s="54"/>
+      <c r="B242" s="42"/>
+      <c r="AA242" s="43"/>
     </row>
     <row r="243" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B243" s="53"/>
-      <c r="AA243" s="54"/>
+      <c r="B243" s="42"/>
+      <c r="AA243" s="43"/>
     </row>
     <row r="244" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B244" s="53"/>
-      <c r="AA244" s="54"/>
+      <c r="B244" s="42"/>
+      <c r="AA244" s="43"/>
     </row>
     <row r="245" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B245" s="53"/>
-      <c r="AA245" s="54"/>
+      <c r="B245" s="42"/>
+      <c r="AA245" s="43"/>
     </row>
     <row r="246" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B246" s="53"/>
-      <c r="AA246" s="54"/>
+      <c r="B246" s="42"/>
+      <c r="AA246" s="43"/>
     </row>
     <row r="247" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B247" s="53"/>
-      <c r="AA247" s="54"/>
+      <c r="B247" s="42"/>
+      <c r="AA247" s="43"/>
     </row>
     <row r="248" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B248" s="53"/>
-      <c r="AA248" s="54"/>
+      <c r="B248" s="42"/>
+      <c r="AA248" s="43"/>
     </row>
     <row r="249" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B249" s="53"/>
-      <c r="AA249" s="54"/>
+      <c r="B249" s="42"/>
+      <c r="AA249" s="43"/>
     </row>
     <row r="250" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B250" s="53"/>
-      <c r="AA250" s="54"/>
+      <c r="B250" s="42"/>
+      <c r="AA250" s="43"/>
     </row>
     <row r="251" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B251" s="53"/>
-      <c r="AA251" s="54"/>
+      <c r="B251" s="42"/>
+      <c r="AA251" s="43"/>
     </row>
     <row r="252" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B252" s="53"/>
-      <c r="AA252" s="54"/>
+      <c r="B252" s="42"/>
+      <c r="AA252" s="43"/>
     </row>
     <row r="253" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B253" s="53"/>
-      <c r="AA253" s="54"/>
+      <c r="B253" s="42"/>
+      <c r="AA253" s="43"/>
     </row>
     <row r="254" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B254" s="53"/>
-      <c r="AA254" s="54"/>
+      <c r="B254" s="42"/>
+      <c r="AA254" s="43"/>
     </row>
     <row r="255" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B255" s="53"/>
-      <c r="AA255" s="54"/>
+      <c r="B255" s="42"/>
+      <c r="AA255" s="43"/>
     </row>
     <row r="256" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B256" s="53"/>
-      <c r="AA256" s="54"/>
+      <c r="B256" s="42"/>
+      <c r="AA256" s="43"/>
     </row>
     <row r="257" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B257" s="53"/>
-      <c r="AA257" s="54"/>
+      <c r="B257" s="42"/>
+      <c r="AA257" s="43"/>
     </row>
     <row r="258" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B258" s="53"/>
-      <c r="AA258" s="54"/>
+      <c r="B258" s="42"/>
+      <c r="AA258" s="43"/>
     </row>
     <row r="259" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B259" s="53"/>
-      <c r="AA259" s="54"/>
+      <c r="B259" s="42"/>
+      <c r="AA259" s="43"/>
     </row>
     <row r="260" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B260" s="53"/>
-      <c r="AA260" s="54"/>
+      <c r="B260" s="42"/>
+      <c r="AA260" s="43"/>
     </row>
     <row r="261" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B261" s="53"/>
-      <c r="AA261" s="54"/>
+      <c r="B261" s="42"/>
+      <c r="AA261" s="43"/>
     </row>
     <row r="262" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B262" s="53"/>
-      <c r="AA262" s="54"/>
+      <c r="B262" s="42"/>
+      <c r="AA262" s="43"/>
     </row>
     <row r="263" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B263" s="53"/>
-      <c r="AA263" s="54"/>
+      <c r="B263" s="42"/>
+      <c r="AA263" s="43"/>
     </row>
     <row r="264" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B264" s="53"/>
-      <c r="AA264" s="54"/>
+      <c r="B264" s="42"/>
+      <c r="AA264" s="43"/>
     </row>
     <row r="265" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B265" s="53"/>
-      <c r="AA265" s="54"/>
+      <c r="B265" s="42"/>
+      <c r="AA265" s="43"/>
     </row>
     <row r="266" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B266" s="53"/>
-      <c r="AA266" s="54"/>
+      <c r="B266" s="42"/>
+      <c r="AA266" s="43"/>
     </row>
     <row r="267" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B267" s="53"/>
-      <c r="AA267" s="54"/>
+      <c r="B267" s="42"/>
+      <c r="AA267" s="43"/>
     </row>
     <row r="268" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B268" s="53"/>
-      <c r="AA268" s="54"/>
+      <c r="B268" s="42"/>
+      <c r="AA268" s="43"/>
     </row>
     <row r="269" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B269" s="53"/>
-      <c r="AA269" s="54"/>
+      <c r="B269" s="42"/>
+      <c r="AA269" s="43"/>
     </row>
     <row r="270" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B270" s="53"/>
-      <c r="AA270" s="54"/>
+      <c r="B270" s="42"/>
+      <c r="AA270" s="43"/>
     </row>
     <row r="271" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B271" s="53"/>
-      <c r="AA271" s="54"/>
+      <c r="B271" s="42"/>
+      <c r="AA271" s="43"/>
     </row>
     <row r="272" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B272" s="53"/>
-      <c r="AA272" s="54"/>
+      <c r="B272" s="42"/>
+      <c r="AA272" s="43"/>
     </row>
     <row r="273" spans="2:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B273" s="53"/>
-      <c r="AA273" s="54"/>
+      <c r="B273" s="42"/>
+      <c r="AA273" s="43"/>
     </row>
     <row r="274" spans="2:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B274" s="53"/>
-      <c r="AA274" s="54"/>
+      <c r="B274" s="42"/>
+      <c r="AA274" s="43"/>
     </row>
     <row r="275" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B275" s="53"/>
-      <c r="AA275" s="54"/>
+      <c r="B275" s="42"/>
+      <c r="AA275" s="43"/>
     </row>
     <row r="276" spans="2:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B276" s="53"/>
-      <c r="AA276" s="54"/>
+      <c r="B276" s="42"/>
+      <c r="AA276" s="43"/>
     </row>
     <row r="277" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B277" s="53"/>
-      <c r="AA277" s="54"/>
+      <c r="B277" s="42"/>
+      <c r="AA277" s="43"/>
     </row>
     <row r="278" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B278" s="53"/>
-      <c r="AA278" s="54"/>
+      <c r="B278" s="42"/>
+      <c r="AA278" s="43"/>
     </row>
     <row r="279" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B279" s="53"/>
-      <c r="AA279" s="54"/>
+      <c r="B279" s="42"/>
+      <c r="AA279" s="43"/>
     </row>
     <row r="280" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B280" s="53"/>
-      <c r="AA280" s="54"/>
+      <c r="B280" s="42"/>
+      <c r="AA280" s="43"/>
     </row>
     <row r="281" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B281" s="53"/>
-      <c r="AA281" s="54"/>
+      <c r="B281" s="42"/>
+      <c r="AA281" s="43"/>
     </row>
     <row r="282" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B282" s="53"/>
-      <c r="AA282" s="54"/>
+      <c r="B282" s="42"/>
+      <c r="AA282" s="43"/>
     </row>
     <row r="283" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B283" s="53"/>
-      <c r="AA283" s="54"/>
+      <c r="B283" s="42"/>
+      <c r="AA283" s="43"/>
     </row>
     <row r="284" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B284" s="53"/>
-      <c r="AA284" s="54"/>
+      <c r="B284" s="42"/>
+      <c r="AA284" s="43"/>
     </row>
     <row r="285" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B285" s="53"/>
-      <c r="AA285" s="54"/>
+      <c r="B285" s="42"/>
+      <c r="AA285" s="43"/>
     </row>
     <row r="286" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B286" s="53"/>
-      <c r="AA286" s="54"/>
+      <c r="B286" s="42"/>
+      <c r="AA286" s="43"/>
     </row>
     <row r="287" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B287" s="53"/>
-      <c r="AA287" s="54"/>
+      <c r="B287" s="42"/>
+      <c r="AA287" s="43"/>
     </row>
     <row r="288" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B288" s="53"/>
-      <c r="AA288" s="54"/>
+      <c r="B288" s="42"/>
+      <c r="AA288" s="43"/>
     </row>
     <row r="289" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B289" s="53"/>
-      <c r="AA289" s="54"/>
+      <c r="B289" s="42"/>
+      <c r="AA289" s="43"/>
     </row>
     <row r="290" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B290" s="53"/>
-      <c r="AA290" s="54"/>
+      <c r="B290" s="42"/>
+      <c r="AA290" s="43"/>
     </row>
     <row r="291" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B291" s="53"/>
-      <c r="AA291" s="54"/>
+      <c r="B291" s="42"/>
+      <c r="AA291" s="43"/>
     </row>
     <row r="292" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B292" s="53"/>
-      <c r="AA292" s="54"/>
+      <c r="B292" s="42"/>
+      <c r="AA292" s="43"/>
     </row>
     <row r="293" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B293" s="53"/>
-      <c r="AA293" s="54"/>
+      <c r="B293" s="42"/>
+      <c r="AA293" s="43"/>
     </row>
     <row r="294" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B294" s="53"/>
-      <c r="AA294" s="54"/>
+      <c r="B294" s="42"/>
+      <c r="AA294" s="43"/>
     </row>
     <row r="295" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B295" s="53"/>
-      <c r="AA295" s="54"/>
+      <c r="B295" s="42"/>
+      <c r="AA295" s="43"/>
     </row>
     <row r="296" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B296" s="53"/>
-      <c r="AA296" s="54"/>
+      <c r="B296" s="42"/>
+      <c r="AA296" s="43"/>
     </row>
     <row r="297" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B297" s="53"/>
-      <c r="AA297" s="54"/>
+      <c r="B297" s="42"/>
+      <c r="AA297" s="43"/>
     </row>
     <row r="298" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B298" s="53"/>
-      <c r="AA298" s="54"/>
+      <c r="B298" s="42"/>
+      <c r="AA298" s="43"/>
     </row>
     <row r="299" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B299" s="53"/>
-      <c r="AA299" s="54"/>
+      <c r="B299" s="42"/>
+      <c r="AA299" s="43"/>
     </row>
     <row r="300" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B300" s="53"/>
-      <c r="AA300" s="54"/>
+      <c r="B300" s="42"/>
+      <c r="AA300" s="43"/>
     </row>
     <row r="301" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B301" s="53"/>
-      <c r="AA301" s="54"/>
+      <c r="B301" s="42"/>
+      <c r="AA301" s="43"/>
     </row>
     <row r="302" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B302" s="53"/>
-      <c r="AA302" s="54"/>
+      <c r="B302" s="42"/>
+      <c r="AA302" s="43"/>
     </row>
     <row r="303" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B303" s="53"/>
-      <c r="AA303" s="54"/>
+      <c r="B303" s="42"/>
+      <c r="AA303" s="43"/>
     </row>
     <row r="304" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B304" s="53"/>
-      <c r="AA304" s="54"/>
+      <c r="B304" s="42"/>
+      <c r="AA304" s="43"/>
     </row>
     <row r="305" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B305" s="53"/>
-      <c r="AA305" s="54"/>
+      <c r="B305" s="42"/>
+      <c r="AA305" s="43"/>
     </row>
     <row r="306" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B306" s="53"/>
-      <c r="AA306" s="54"/>
+      <c r="B306" s="42"/>
+      <c r="AA306" s="43"/>
     </row>
     <row r="307" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B307" s="53"/>
-      <c r="AA307" s="54"/>
+      <c r="B307" s="42"/>
+      <c r="AA307" s="43"/>
     </row>
     <row r="308" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B308" s="53"/>
-      <c r="AA308" s="54"/>
+      <c r="B308" s="42"/>
+      <c r="AA308" s="43"/>
     </row>
     <row r="309" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B309" s="53"/>
-      <c r="AA309" s="54"/>
+      <c r="B309" s="42"/>
+      <c r="AA309" s="43"/>
     </row>
     <row r="310" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B310" s="53"/>
-      <c r="AA310" s="54"/>
+      <c r="B310" s="42"/>
+      <c r="AA310" s="43"/>
     </row>
     <row r="311" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B311" s="53"/>
-      <c r="AA311" s="54"/>
+      <c r="B311" s="42"/>
+      <c r="AA311" s="43"/>
     </row>
     <row r="312" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B312" s="53"/>
-      <c r="AA312" s="54"/>
+      <c r="B312" s="42"/>
+      <c r="AA312" s="43"/>
     </row>
     <row r="313" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B313" s="53"/>
-      <c r="AA313" s="54"/>
+      <c r="B313" s="42"/>
+      <c r="AA313" s="43"/>
     </row>
     <row r="314" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B314" s="53"/>
-      <c r="AA314" s="54"/>
+      <c r="B314" s="42"/>
+      <c r="AA314" s="43"/>
     </row>
     <row r="315" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B315" s="53"/>
-      <c r="AA315" s="54"/>
+      <c r="B315" s="42"/>
+      <c r="AA315" s="43"/>
     </row>
     <row r="316" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B316" s="53"/>
-      <c r="AA316" s="54"/>
+      <c r="B316" s="42"/>
+      <c r="AA316" s="43"/>
     </row>
     <row r="317" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B317" s="53"/>
-      <c r="AA317" s="54"/>
+      <c r="B317" s="42"/>
+      <c r="AA317" s="43"/>
     </row>
     <row r="318" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B318" s="53"/>
-      <c r="AA318" s="54"/>
+      <c r="B318" s="42"/>
+      <c r="AA318" s="43"/>
     </row>
     <row r="319" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B319" s="53"/>
-      <c r="AA319" s="54"/>
+      <c r="B319" s="42"/>
+      <c r="AA319" s="43"/>
     </row>
     <row r="320" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B320" s="53"/>
-      <c r="AA320" s="54"/>
+      <c r="B320" s="42"/>
+      <c r="AA320" s="43"/>
     </row>
     <row r="321" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B321" s="53"/>
-      <c r="AA321" s="54"/>
+      <c r="B321" s="42"/>
+      <c r="AA321" s="43"/>
     </row>
     <row r="322" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B322" s="53"/>
-      <c r="AA322" s="54"/>
+      <c r="B322" s="42"/>
+      <c r="AA322" s="43"/>
     </row>
     <row r="323" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B323" s="53"/>
-      <c r="AA323" s="54"/>
+      <c r="B323" s="42"/>
+      <c r="AA323" s="43"/>
     </row>
     <row r="324" spans="2:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B324" s="53"/>
-      <c r="AA324" s="54"/>
+      <c r="B324" s="42"/>
+      <c r="AA324" s="43"/>
     </row>
     <row r="325" spans="2:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B325" s="53"/>
-      <c r="AA325" s="54"/>
+      <c r="B325" s="42"/>
+      <c r="AA325" s="43"/>
     </row>
     <row r="326" spans="2:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B326" s="53"/>
-      <c r="AA326" s="54"/>
+      <c r="B326" s="42"/>
+      <c r="AA326" s="43"/>
     </row>
     <row r="327" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B327" s="53"/>
-      <c r="AA327" s="54"/>
+      <c r="B327" s="42"/>
+      <c r="AA327" s="43"/>
     </row>
     <row r="328" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B328" s="53"/>
-      <c r="AA328" s="54"/>
+      <c r="B328" s="42"/>
+      <c r="AA328" s="43"/>
     </row>
     <row r="329" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B329" s="53"/>
-      <c r="AA329" s="54"/>
+      <c r="B329" s="42"/>
+      <c r="AA329" s="43"/>
     </row>
     <row r="330" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B330" s="53"/>
-      <c r="AA330" s="54"/>
+      <c r="B330" s="42"/>
+      <c r="AA330" s="43"/>
     </row>
     <row r="331" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B331" s="53"/>
-      <c r="AA331" s="54"/>
+      <c r="B331" s="42"/>
+      <c r="AA331" s="43"/>
     </row>
     <row r="332" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B332" s="53"/>
-      <c r="AA332" s="54"/>
+      <c r="B332" s="42"/>
+      <c r="AA332" s="43"/>
     </row>
     <row r="333" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B333" s="53"/>
-      <c r="AA333" s="54"/>
+      <c r="B333" s="42"/>
+      <c r="AA333" s="43"/>
     </row>
     <row r="334" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B334" s="53"/>
-      <c r="AA334" s="54"/>
+      <c r="B334" s="42"/>
+      <c r="AA334" s="43"/>
     </row>
     <row r="335" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B335" s="53"/>
-      <c r="AA335" s="54"/>
+      <c r="B335" s="42"/>
+      <c r="AA335" s="43"/>
     </row>
     <row r="336" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B336" s="53"/>
-      <c r="AA336" s="54"/>
+      <c r="B336" s="42"/>
+      <c r="AA336" s="43"/>
     </row>
     <row r="337" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B337" s="53"/>
-      <c r="AA337" s="54"/>
+      <c r="B337" s="42"/>
+      <c r="AA337" s="43"/>
     </row>
     <row r="338" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B338" s="53"/>
-      <c r="AA338" s="54"/>
+      <c r="B338" s="42"/>
+      <c r="AA338" s="43"/>
     </row>
     <row r="339" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B339" s="53"/>
-      <c r="AA339" s="54"/>
+      <c r="B339" s="42"/>
+      <c r="AA339" s="43"/>
     </row>
     <row r="340" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B340" s="53"/>
-      <c r="AA340" s="54"/>
+      <c r="B340" s="42"/>
+      <c r="AA340" s="43"/>
     </row>
     <row r="341" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B341" s="53"/>
-      <c r="AA341" s="54"/>
+      <c r="B341" s="42"/>
+      <c r="AA341" s="43"/>
     </row>
     <row r="342" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B342" s="53"/>
-      <c r="AA342" s="54"/>
+      <c r="B342" s="42"/>
+      <c r="AA342" s="43"/>
     </row>
     <row r="343" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B343" s="53"/>
-      <c r="AA343" s="54"/>
+      <c r="B343" s="42"/>
+      <c r="AA343" s="43"/>
     </row>
     <row r="344" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B344" s="53"/>
-      <c r="AA344" s="54"/>
+      <c r="B344" s="42"/>
+      <c r="AA344" s="43"/>
     </row>
     <row r="345" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B345" s="53"/>
-      <c r="AA345" s="54"/>
+      <c r="B345" s="42"/>
+      <c r="AA345" s="43"/>
     </row>
     <row r="346" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B346" s="53"/>
-      <c r="AA346" s="54"/>
+      <c r="B346" s="42"/>
+      <c r="AA346" s="43"/>
     </row>
     <row r="347" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B347" s="53"/>
-      <c r="AA347" s="54"/>
+      <c r="B347" s="42"/>
+      <c r="AA347" s="43"/>
     </row>
     <row r="348" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B348" s="53"/>
-      <c r="AA348" s="54"/>
+      <c r="B348" s="42"/>
+      <c r="AA348" s="43"/>
     </row>
     <row r="349" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B349" s="53"/>
-      <c r="AA349" s="54"/>
+      <c r="B349" s="42"/>
+      <c r="AA349" s="43"/>
     </row>
     <row r="350" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B350" s="53"/>
-      <c r="AA350" s="54"/>
+      <c r="B350" s="42"/>
+      <c r="AA350" s="43"/>
     </row>
     <row r="351" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B351" s="53"/>
-      <c r="AA351" s="54"/>
+      <c r="B351" s="42"/>
+      <c r="AA351" s="43"/>
     </row>
     <row r="352" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B352" s="53"/>
-      <c r="AA352" s="54"/>
+      <c r="B352" s="42"/>
+      <c r="AA352" s="43"/>
     </row>
     <row r="353" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B353" s="53"/>
-      <c r="AA353" s="54"/>
+      <c r="B353" s="42"/>
+      <c r="AA353" s="43"/>
     </row>
     <row r="354" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B354" s="53"/>
-      <c r="AA354" s="54"/>
+      <c r="B354" s="42"/>
+      <c r="AA354" s="43"/>
     </row>
     <row r="355" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B355" s="53"/>
-      <c r="AA355" s="54"/>
+      <c r="B355" s="42"/>
+      <c r="AA355" s="43"/>
     </row>
     <row r="356" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B356" s="53"/>
-      <c r="AA356" s="54"/>
+      <c r="B356" s="42"/>
+      <c r="AA356" s="43"/>
     </row>
     <row r="357" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B357" s="53"/>
-      <c r="AA357" s="54"/>
+      <c r="B357" s="42"/>
+      <c r="AA357" s="43"/>
     </row>
     <row r="358" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B358" s="53"/>
-      <c r="AA358" s="54"/>
+      <c r="B358" s="42"/>
+      <c r="AA358" s="43"/>
     </row>
     <row r="359" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B359" s="53"/>
-      <c r="AA359" s="54"/>
+      <c r="B359" s="42"/>
+      <c r="AA359" s="43"/>
     </row>
     <row r="360" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B360" s="53"/>
-      <c r="AA360" s="54"/>
+      <c r="B360" s="42"/>
+      <c r="AA360" s="43"/>
     </row>
     <row r="361" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B361" s="53"/>
-      <c r="AA361" s="54"/>
+      <c r="B361" s="42"/>
+      <c r="AA361" s="43"/>
     </row>
     <row r="362" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B362" s="53"/>
-      <c r="AA362" s="54"/>
+      <c r="B362" s="42"/>
+      <c r="AA362" s="43"/>
     </row>
     <row r="363" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B363" s="53"/>
-      <c r="AA363" s="54"/>
+      <c r="B363" s="42"/>
+      <c r="AA363" s="43"/>
     </row>
     <row r="364" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B364" s="53"/>
-      <c r="AA364" s="54"/>
+      <c r="B364" s="42"/>
+      <c r="AA364" s="43"/>
     </row>
     <row r="365" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B365" s="53"/>
-      <c r="AA365" s="54"/>
+      <c r="B365" s="42"/>
+      <c r="AA365" s="43"/>
     </row>
     <row r="366" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B366" s="53"/>
-      <c r="AA366" s="54"/>
+      <c r="B366" s="42"/>
+      <c r="AA366" s="43"/>
     </row>
     <row r="367" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B367" s="53"/>
-      <c r="AA367" s="54"/>
+      <c r="B367" s="42"/>
+      <c r="AA367" s="43"/>
     </row>
     <row r="368" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B368" s="53"/>
-      <c r="AA368" s="54"/>
+      <c r="B368" s="42"/>
+      <c r="AA368" s="43"/>
     </row>
     <row r="369" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B369" s="53"/>
-      <c r="AA369" s="54"/>
+      <c r="B369" s="42"/>
+      <c r="AA369" s="43"/>
     </row>
     <row r="370" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B370" s="53"/>
-      <c r="AA370" s="54"/>
+      <c r="B370" s="42"/>
+      <c r="AA370" s="43"/>
     </row>
     <row r="371" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B371" s="53"/>
-      <c r="AA371" s="54"/>
+      <c r="B371" s="42"/>
+      <c r="AA371" s="43"/>
     </row>
     <row r="372" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B372" s="53"/>
-      <c r="AA372" s="54"/>
+      <c r="B372" s="42"/>
+      <c r="AA372" s="43"/>
     </row>
     <row r="373" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B373" s="53"/>
-      <c r="AA373" s="54"/>
+      <c r="B373" s="42"/>
+      <c r="AA373" s="43"/>
     </row>
     <row r="374" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B374" s="53"/>
-      <c r="AA374" s="54"/>
+      <c r="B374" s="42"/>
+      <c r="AA374" s="43"/>
     </row>
     <row r="375" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B375" s="53"/>
-      <c r="AA375" s="54"/>
+      <c r="B375" s="42"/>
+      <c r="AA375" s="43"/>
     </row>
     <row r="376" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B376" s="53"/>
-      <c r="AA376" s="54"/>
+      <c r="B376" s="42"/>
+      <c r="AA376" s="43"/>
     </row>
     <row r="377" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B377" s="53"/>
-      <c r="AA377" s="54"/>
+      <c r="B377" s="42"/>
+      <c r="AA377" s="43"/>
     </row>
     <row r="378" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B378" s="53"/>
-      <c r="AA378" s="54"/>
+      <c r="B378" s="42"/>
+      <c r="AA378" s="43"/>
     </row>
     <row r="379" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B379" s="53"/>
-      <c r="AA379" s="54"/>
+      <c r="B379" s="42"/>
+      <c r="AA379" s="43"/>
     </row>
     <row r="380" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B380" s="53"/>
-      <c r="AA380" s="54"/>
+      <c r="B380" s="42"/>
+      <c r="AA380" s="43"/>
     </row>
     <row r="381" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B381" s="53"/>
-      <c r="AA381" s="54"/>
+      <c r="B381" s="42"/>
+      <c r="AA381" s="43"/>
     </row>
     <row r="382" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B382" s="53"/>
-      <c r="AA382" s="54"/>
+      <c r="B382" s="42"/>
+      <c r="AA382" s="43"/>
     </row>
     <row r="383" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B383" s="53"/>
-      <c r="AA383" s="54"/>
+      <c r="B383" s="42"/>
+      <c r="AA383" s="43"/>
     </row>
     <row r="384" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B384" s="53"/>
-      <c r="AA384" s="54"/>
+      <c r="B384" s="42"/>
+      <c r="AA384" s="43"/>
     </row>
     <row r="385" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B385" s="53"/>
-      <c r="AA385" s="54"/>
+      <c r="B385" s="42"/>
+      <c r="AA385" s="43"/>
     </row>
     <row r="386" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B386" s="53"/>
-      <c r="AA386" s="54"/>
+      <c r="B386" s="42"/>
+      <c r="AA386" s="43"/>
     </row>
     <row r="387" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B387" s="53"/>
-      <c r="AA387" s="54"/>
+      <c r="B387" s="42"/>
+      <c r="AA387" s="43"/>
     </row>
     <row r="388" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B388" s="53"/>
-      <c r="AA388" s="54"/>
+      <c r="B388" s="42"/>
+      <c r="AA388" s="43"/>
     </row>
     <row r="389" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B389" s="53"/>
-      <c r="AA389" s="54"/>
+      <c r="B389" s="42"/>
+      <c r="AA389" s="43"/>
     </row>
     <row r="390" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B390" s="53"/>
-      <c r="AA390" s="54"/>
+      <c r="B390" s="42"/>
+      <c r="AA390" s="43"/>
     </row>
     <row r="391" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B391" s="53"/>
-      <c r="AA391" s="54"/>
+      <c r="B391" s="42"/>
+      <c r="AA391" s="43"/>
     </row>
     <row r="392" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B392" s="53"/>
-      <c r="AA392" s="54"/>
+      <c r="B392" s="42"/>
+      <c r="AA392" s="43"/>
     </row>
     <row r="393" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B393" s="53"/>
-      <c r="AA393" s="54"/>
+      <c r="B393" s="42"/>
+      <c r="AA393" s="43"/>
     </row>
     <row r="394" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B394" s="53"/>
-      <c r="AA394" s="54"/>
+      <c r="B394" s="42"/>
+      <c r="AA394" s="43"/>
     </row>
     <row r="395" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B395" s="53"/>
-      <c r="AA395" s="54"/>
+      <c r="B395" s="42"/>
+      <c r="AA395" s="43"/>
     </row>
     <row r="396" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B396" s="53"/>
-      <c r="AA396" s="54"/>
+      <c r="B396" s="42"/>
+      <c r="AA396" s="43"/>
     </row>
     <row r="397" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B397" s="53"/>
-      <c r="AA397" s="54"/>
+      <c r="B397" s="42"/>
+      <c r="AA397" s="43"/>
     </row>
     <row r="398" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B398" s="53"/>
-      <c r="AA398" s="54"/>
+      <c r="B398" s="42"/>
+      <c r="AA398" s="43"/>
     </row>
     <row r="399" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B399" s="53"/>
-      <c r="AA399" s="54"/>
+      <c r="B399" s="42"/>
+      <c r="AA399" s="43"/>
     </row>
     <row r="400" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B400" s="53"/>
-      <c r="AA400" s="54"/>
+      <c r="B400" s="42"/>
+      <c r="AA400" s="43"/>
     </row>
     <row r="401" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B401" s="53"/>
-      <c r="AA401" s="54"/>
+      <c r="B401" s="42"/>
+      <c r="AA401" s="43"/>
     </row>
     <row r="402" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B402" s="53"/>
-      <c r="AA402" s="54"/>
+      <c r="B402" s="42"/>
+      <c r="AA402" s="43"/>
     </row>
     <row r="403" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B403" s="53"/>
-      <c r="AA403" s="54"/>
+      <c r="B403" s="42"/>
+      <c r="AA403" s="43"/>
     </row>
     <row r="404" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B404" s="53"/>
-      <c r="AA404" s="54"/>
+      <c r="B404" s="42"/>
+      <c r="AA404" s="43"/>
     </row>
     <row r="405" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B405" s="53"/>
-      <c r="AA405" s="54"/>
+      <c r="B405" s="42"/>
+      <c r="AA405" s="43"/>
     </row>
     <row r="406" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B406" s="53"/>
-      <c r="AA406" s="54"/>
+      <c r="B406" s="42"/>
+      <c r="AA406" s="43"/>
     </row>
     <row r="407" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B407" s="53"/>
-      <c r="AA407" s="54"/>
+      <c r="B407" s="42"/>
+      <c r="AA407" s="43"/>
     </row>
     <row r="408" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B408" s="53"/>
-      <c r="AA408" s="54"/>
+      <c r="B408" s="42"/>
+      <c r="AA408" s="43"/>
     </row>
     <row r="409" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B409" s="53"/>
-      <c r="AA409" s="54"/>
+      <c r="B409" s="42"/>
+      <c r="AA409" s="43"/>
     </row>
     <row r="410" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B410" s="53"/>
-      <c r="AA410" s="54"/>
+      <c r="B410" s="42"/>
+      <c r="AA410" s="43"/>
     </row>
     <row r="411" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B411" s="53"/>
-      <c r="AA411" s="54"/>
+      <c r="B411" s="42"/>
+      <c r="AA411" s="43"/>
     </row>
     <row r="412" spans="2:27" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B412" s="53"/>
-      <c r="AA412" s="54"/>
+      <c r="B412" s="42"/>
+      <c r="AA412" s="43"/>
     </row>
     <row r="413" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B413" s="53"/>
-      <c r="AA413" s="54"/>
+      <c r="B413" s="42"/>
+      <c r="AA413" s="43"/>
     </row>
     <row r="414" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B414" s="53"/>
-      <c r="AA414" s="54"/>
+      <c r="B414" s="42"/>
+      <c r="AA414" s="43"/>
     </row>
     <row r="415" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B415" s="53"/>
-      <c r="AA415" s="54"/>
+      <c r="B415" s="42"/>
+      <c r="AA415" s="43"/>
     </row>
     <row r="416" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B416" s="53"/>
-      <c r="AA416" s="54"/>
+      <c r="B416" s="42"/>
+      <c r="AA416" s="43"/>
     </row>
     <row r="417" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B417" s="53"/>
-      <c r="AA417" s="54"/>
+      <c r="B417" s="42"/>
+      <c r="AA417" s="43"/>
     </row>
     <row r="418" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B418" s="53"/>
-      <c r="AA418" s="54"/>
+      <c r="B418" s="42"/>
+      <c r="AA418" s="43"/>
     </row>
     <row r="419" spans="2:27" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B419" s="55"/>
-      <c r="C419" s="56"/>
-      <c r="D419" s="56"/>
-      <c r="E419" s="56"/>
-      <c r="F419" s="56"/>
-      <c r="G419" s="56"/>
-      <c r="H419" s="56"/>
-      <c r="I419" s="56"/>
-      <c r="J419" s="56"/>
-      <c r="K419" s="56"/>
-      <c r="L419" s="56"/>
-      <c r="M419" s="56"/>
-      <c r="N419" s="56"/>
-      <c r="O419" s="56"/>
-      <c r="P419" s="56"/>
-      <c r="Q419" s="56"/>
-      <c r="R419" s="56"/>
-      <c r="S419" s="56"/>
-      <c r="T419" s="56"/>
-      <c r="U419" s="56"/>
-      <c r="V419" s="56"/>
-      <c r="W419" s="65"/>
-      <c r="X419" s="65"/>
-      <c r="Y419" s="56"/>
-      <c r="Z419" s="56"/>
-      <c r="AA419" s="57"/>
+      <c r="B419" s="44"/>
+      <c r="C419" s="45"/>
+      <c r="D419" s="45"/>
+      <c r="E419" s="45"/>
+      <c r="F419" s="45"/>
+      <c r="G419" s="45"/>
+      <c r="H419" s="45"/>
+      <c r="I419" s="45"/>
+      <c r="J419" s="45"/>
+      <c r="K419" s="45"/>
+      <c r="L419" s="45"/>
+      <c r="M419" s="45"/>
+      <c r="N419" s="45"/>
+      <c r="O419" s="45"/>
+      <c r="P419" s="45"/>
+      <c r="Q419" s="45"/>
+      <c r="R419" s="45"/>
+      <c r="S419" s="45"/>
+      <c r="T419" s="45"/>
+      <c r="U419" s="45"/>
+      <c r="V419" s="45"/>
+      <c r="W419" s="54"/>
+      <c r="X419" s="54"/>
+      <c r="Y419" s="45"/>
+      <c r="Z419" s="45"/>
+      <c r="AA419" s="46"/>
     </row>
   </sheetData>
   <pageMargins left="0.78740157480314965" right="0.78740157480314965" top="0.55118110236220474" bottom="0.98425196850393704" header="0" footer="0"/>
